--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1432">
   <si>
     <t>DT Code*</t>
   </si>
@@ -3895,6 +3895,426 @@
   </si>
   <si>
     <t>62998-6552320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B348C</t>
+  </si>
+  <si>
+    <t>03999610400</t>
+  </si>
+  <si>
+    <t>EMPFA98D4</t>
+  </si>
+  <si>
+    <t>87990-0198960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9ABA7</t>
+  </si>
+  <si>
+    <t>03015767500</t>
+  </si>
+  <si>
+    <t>EMPB75B75</t>
+  </si>
+  <si>
+    <t>87990-1756850-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_81232</t>
+  </si>
+  <si>
+    <t>03018707700</t>
+  </si>
+  <si>
+    <t>EMPBE8419</t>
+  </si>
+  <si>
+    <t>87990-2010190-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_300C7</t>
+  </si>
+  <si>
+    <t>03021739400</t>
+  </si>
+  <si>
+    <t>EMP4AFC03</t>
+  </si>
+  <si>
+    <t>87990-2583520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_96C2C</t>
+  </si>
+  <si>
+    <t>03027680700</t>
+  </si>
+  <si>
+    <t>EMP8C0D71</t>
+  </si>
+  <si>
+    <t>87990-3501680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_99E11</t>
+  </si>
+  <si>
+    <t>03092820300</t>
+  </si>
+  <si>
+    <t>EMPEA9A9E</t>
+  </si>
+  <si>
+    <t>99490-9627640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_19602</t>
+  </si>
+  <si>
+    <t>03111250000</t>
+  </si>
+  <si>
+    <t>EMP50A42C</t>
+  </si>
+  <si>
+    <t>99491-1351950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FE009</t>
+  </si>
+  <si>
+    <t>03117108300</t>
+  </si>
+  <si>
+    <t>EMP6C6A66</t>
+  </si>
+  <si>
+    <t>99491-2032910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_217BD</t>
+  </si>
+  <si>
+    <t>03121295000</t>
+  </si>
+  <si>
+    <t>EMPCD1BBC</t>
+  </si>
+  <si>
+    <t>99491-2221560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9E2F6</t>
+  </si>
+  <si>
+    <t>03123171700</t>
+  </si>
+  <si>
+    <t>EMPB14962</t>
+  </si>
+  <si>
+    <t>99491-2425000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_83BC8</t>
+  </si>
+  <si>
+    <t>03862979000</t>
+  </si>
+  <si>
+    <t>EMP498662</t>
+  </si>
+  <si>
+    <t>47778-6527680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_00662</t>
+  </si>
+  <si>
+    <t>03875478200</t>
+  </si>
+  <si>
+    <t>EMP88D784</t>
+  </si>
+  <si>
+    <t>47778-7700200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0737D</t>
+  </si>
+  <si>
+    <t>03879086000</t>
+  </si>
+  <si>
+    <t>EMPC39851</t>
+  </si>
+  <si>
+    <t>47778-8097240-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B7913</t>
+  </si>
+  <si>
+    <t>03882179000</t>
+  </si>
+  <si>
+    <t>EMPC38F03</t>
+  </si>
+  <si>
+    <t>47778-8361130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F2127</t>
+  </si>
+  <si>
+    <t>03885909600</t>
+  </si>
+  <si>
+    <t>EMP5212D9</t>
+  </si>
+  <si>
+    <t>47778-8827140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FD6FD</t>
+  </si>
+  <si>
+    <t>03703126400</t>
+  </si>
+  <si>
+    <t>EMPED09A1</t>
+  </si>
+  <si>
+    <t>75447-0528870-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_55DD4</t>
+  </si>
+  <si>
+    <t>03718290900</t>
+  </si>
+  <si>
+    <t>EMPE61432</t>
+  </si>
+  <si>
+    <t>75447-1953450-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EA022</t>
+  </si>
+  <si>
+    <t>03720599000</t>
+  </si>
+  <si>
+    <t>EMP9CE161</t>
+  </si>
+  <si>
+    <t>75447-2165330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3619B</t>
+  </si>
+  <si>
+    <t>03723081800</t>
+  </si>
+  <si>
+    <t>EMP13D506</t>
+  </si>
+  <si>
+    <t>75447-2490320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_247C2</t>
+  </si>
+  <si>
+    <t>03726158000</t>
+  </si>
+  <si>
+    <t>EMPD8C533</t>
+  </si>
+  <si>
+    <t>75447-2771790-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3BC37</t>
+  </si>
+  <si>
+    <t>03336344000</t>
+  </si>
+  <si>
+    <t>EMPF95E51</t>
+  </si>
+  <si>
+    <t>87223-3790010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6A561</t>
+  </si>
+  <si>
+    <t>03339011500</t>
+  </si>
+  <si>
+    <t>EMP808F2D</t>
+  </si>
+  <si>
+    <t>87223-3976710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DA24F</t>
+  </si>
+  <si>
+    <t>03340471500</t>
+  </si>
+  <si>
+    <t>EMP943CE8</t>
+  </si>
+  <si>
+    <t>87223-4115360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CCBAE</t>
+  </si>
+  <si>
+    <t>03341847600</t>
+  </si>
+  <si>
+    <t>EMPEE7411</t>
+  </si>
+  <si>
+    <t>87223-4254360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7DE8B</t>
+  </si>
+  <si>
+    <t>03343277800</t>
+  </si>
+  <si>
+    <t>EMP7029A2</t>
+  </si>
+  <si>
+    <t>87223-4405890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C910A</t>
+  </si>
+  <si>
+    <t>03317995300</t>
+  </si>
+  <si>
+    <t>EMPA4271A</t>
+  </si>
+  <si>
+    <t>55263-1962320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_03A45</t>
+  </si>
+  <si>
+    <t>03325887700</t>
+  </si>
+  <si>
+    <t>EMP9CCC48</t>
+  </si>
+  <si>
+    <t>55263-2673980-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_13F84</t>
+  </si>
+  <si>
+    <t>03327715500</t>
+  </si>
+  <si>
+    <t>EMPBC95D4</t>
+  </si>
+  <si>
+    <t>55263-2882170-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F9998</t>
+  </si>
+  <si>
+    <t>03329958100</t>
+  </si>
+  <si>
+    <t>EMP40F83A</t>
+  </si>
+  <si>
+    <t>55263-3068950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_84093</t>
+  </si>
+  <si>
+    <t>03331654900</t>
+  </si>
+  <si>
+    <t>EMP4887FC</t>
+  </si>
+  <si>
+    <t>55263-3255760-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D8AA3</t>
+  </si>
+  <si>
+    <t>03810720900</t>
+  </si>
+  <si>
+    <t>EMPB79889</t>
+  </si>
+  <si>
+    <t>61238-1205100-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E8C70</t>
+  </si>
+  <si>
+    <t>03819024700</t>
+  </si>
+  <si>
+    <t>EMPC4FC62</t>
+  </si>
+  <si>
+    <t>61238-1951890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_762F7</t>
+  </si>
+  <si>
+    <t>03819895400</t>
+  </si>
+  <si>
+    <t>EMP772EEF</t>
+  </si>
+  <si>
+    <t>61238-2025770-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B3FE0</t>
+  </si>
+  <si>
+    <t>03820628700</t>
+  </si>
+  <si>
+    <t>EMP3CEDE3</t>
+  </si>
+  <si>
+    <t>61238-2110600-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2B9D2</t>
+  </si>
+  <si>
+    <t>03821702600</t>
+  </si>
+  <si>
+    <t>EMP3F231B</t>
+  </si>
+  <si>
+    <t>61238-2225970-0</t>
   </si>
 </sst>
 </file>
@@ -4350,16 +4770,16 @@
         <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>1272</v>
+        <v>1412</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>1273</v>
+        <v>1413</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>1274</v>
+        <v>1414</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -4419,7 +4839,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1275</v>
+        <v>1415</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -4445,16 +4865,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>1276</v>
+        <v>1416</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>1277</v>
+        <v>1417</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>1278</v>
+        <v>1418</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -4514,7 +4934,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>1279</v>
+        <v>1419</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -4540,16 +4960,16 @@
         <v>56</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>1280</v>
+        <v>1420</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>1281</v>
+        <v>1421</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>1282</v>
+        <v>1422</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -4609,7 +5029,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>1283</v>
+        <v>1423</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -4635,16 +5055,16 @@
         <v>60</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>1284</v>
+        <v>1424</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>1285</v>
+        <v>1425</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>1286</v>
+        <v>1426</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -4704,7 +5124,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>1287</v>
+        <v>1427</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -4730,16 +5150,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>1288</v>
+        <v>1428</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>1289</v>
+        <v>1429</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>1290</v>
+        <v>1430</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -4799,7 +5219,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1291</v>
+        <v>1431</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>

--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1492">
   <si>
     <t>DT Code*</t>
   </si>
@@ -4315,6 +4315,186 @@
   </si>
   <si>
     <t>61238-2225970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B33D8</t>
+  </si>
+  <si>
+    <t>03398647000</t>
+  </si>
+  <si>
+    <t>EMP80DAEF</t>
+  </si>
+  <si>
+    <t>02934-0072160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_53436</t>
+  </si>
+  <si>
+    <t>03410177800</t>
+  </si>
+  <si>
+    <t>EMP07D48B</t>
+  </si>
+  <si>
+    <t>02934-1126120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CA307</t>
+  </si>
+  <si>
+    <t>03412160000</t>
+  </si>
+  <si>
+    <t>EMPBEC234</t>
+  </si>
+  <si>
+    <t>02934-1325160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8DB17</t>
+  </si>
+  <si>
+    <t>03414214200</t>
+  </si>
+  <si>
+    <t>EMPA65645</t>
+  </si>
+  <si>
+    <t>02934-1521770-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F0AF7</t>
+  </si>
+  <si>
+    <t>03416299500</t>
+  </si>
+  <si>
+    <t>EMP7D6A50</t>
+  </si>
+  <si>
+    <t>02934-1717710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FB38E</t>
+  </si>
+  <si>
+    <t>03970202900</t>
+  </si>
+  <si>
+    <t>EMP091AA4</t>
+  </si>
+  <si>
+    <t>25989-7148070-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_46883</t>
+  </si>
+  <si>
+    <t>03976901900</t>
+  </si>
+  <si>
+    <t>EMPD90798</t>
+  </si>
+  <si>
+    <t>25989-7759630-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B8CB5</t>
+  </si>
+  <si>
+    <t>03978583900</t>
+  </si>
+  <si>
+    <t>EMP3958C7</t>
+  </si>
+  <si>
+    <t>25989-7951930-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_688A6</t>
+  </si>
+  <si>
+    <t>03980129200</t>
+  </si>
+  <si>
+    <t>EMPDF93A6</t>
+  </si>
+  <si>
+    <t>25989-8069110-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B98F5</t>
+  </si>
+  <si>
+    <t>03981863500</t>
+  </si>
+  <si>
+    <t>EMP20F3D9</t>
+  </si>
+  <si>
+    <t>25989-8249010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C8683</t>
+  </si>
+  <si>
+    <t>03003535400</t>
+  </si>
+  <si>
+    <t>EMP059A75</t>
+  </si>
+  <si>
+    <t>28970-0465670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F7D95</t>
+  </si>
+  <si>
+    <t>03010190100</t>
+  </si>
+  <si>
+    <t>EMPB5A442</t>
+  </si>
+  <si>
+    <t>28970-1104780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_911F6</t>
+  </si>
+  <si>
+    <t>03011612000</t>
+  </si>
+  <si>
+    <t>EMP9B2159</t>
+  </si>
+  <si>
+    <t>28970-1211760-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9C1D1</t>
+  </si>
+  <si>
+    <t>03012667400</t>
+  </si>
+  <si>
+    <t>EMP7F2F4E</t>
+  </si>
+  <si>
+    <t>28970-1318140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3FB8F</t>
+  </si>
+  <si>
+    <t>03013707100</t>
+  </si>
+  <si>
+    <t>EMPB0DC03</t>
+  </si>
+  <si>
+    <t>28970-1423330-0</t>
   </si>
 </sst>
 </file>
@@ -4770,16 +4950,16 @@
         <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>1412</v>
+        <v>1472</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>1413</v>
+        <v>1473</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>1414</v>
+        <v>1474</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -4839,7 +5019,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1415</v>
+        <v>1475</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -4865,16 +5045,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>1416</v>
+        <v>1476</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>1417</v>
+        <v>1477</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>1418</v>
+        <v>1478</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -4934,7 +5114,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>1419</v>
+        <v>1479</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -4960,16 +5140,16 @@
         <v>56</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>1420</v>
+        <v>1480</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>1421</v>
+        <v>1481</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>1422</v>
+        <v>1482</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -5029,7 +5209,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>1423</v>
+        <v>1483</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -5055,16 +5235,16 @@
         <v>60</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>1424</v>
+        <v>1484</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>1425</v>
+        <v>1485</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>1426</v>
+        <v>1486</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -5124,7 +5304,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>1427</v>
+        <v>1487</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -5150,16 +5330,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>1428</v>
+        <v>1488</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>1429</v>
+        <v>1489</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>1430</v>
+        <v>1490</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -5219,7 +5399,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1431</v>
+        <v>1491</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>

--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="1532">
   <si>
     <t>DT Code*</t>
   </si>
@@ -4495,6 +4495,126 @@
   </si>
   <si>
     <t>28970-1423330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_57565</t>
+  </si>
+  <si>
+    <t>03477332800</t>
+  </si>
+  <si>
+    <t>EMP90EE0D</t>
+  </si>
+  <si>
+    <t>38134-7878400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_336A5</t>
+  </si>
+  <si>
+    <t>03483858300</t>
+  </si>
+  <si>
+    <t>EMP9DC9A6</t>
+  </si>
+  <si>
+    <t>38134-8457510-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8E871</t>
+  </si>
+  <si>
+    <t>03485341000</t>
+  </si>
+  <si>
+    <t>EMPE40013</t>
+  </si>
+  <si>
+    <t>38134-8609570-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_88F07</t>
+  </si>
+  <si>
+    <t>03486857900</t>
+  </si>
+  <si>
+    <t>EMPD2B7DC</t>
+  </si>
+  <si>
+    <t>38134-8764590-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_14626</t>
+  </si>
+  <si>
+    <t>03488439000</t>
+  </si>
+  <si>
+    <t>EMP1BD165</t>
+  </si>
+  <si>
+    <t>38134-8926810-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DFE1B</t>
+  </si>
+  <si>
+    <t>03018240500</t>
+  </si>
+  <si>
+    <t>EMP667753</t>
+  </si>
+  <si>
+    <t>6975019312400</t>
+  </si>
+  <si>
+    <t>AUTODSR_532DB</t>
+  </si>
+  <si>
+    <t>03023586000</t>
+  </si>
+  <si>
+    <t>EMP85E16E</t>
+  </si>
+  <si>
+    <t>6975024190600</t>
+  </si>
+  <si>
+    <t>AUTODSR_275E5</t>
+  </si>
+  <si>
+    <t>03024827500</t>
+  </si>
+  <si>
+    <t>EMPD76A85</t>
+  </si>
+  <si>
+    <t>6975025663600</t>
+  </si>
+  <si>
+    <t>AUTODSR_2DC29</t>
+  </si>
+  <si>
+    <t>03026239900</t>
+  </si>
+  <si>
+    <t>EMP5EBDCA</t>
+  </si>
+  <si>
+    <t>6975026834700</t>
+  </si>
+  <si>
+    <t>AUTODSR_B6036</t>
+  </si>
+  <si>
+    <t>03027404000</t>
+  </si>
+  <si>
+    <t>EMP2FE79D</t>
+  </si>
+  <si>
+    <t>6975027924200</t>
   </si>
 </sst>
 </file>
@@ -4950,16 +5070,16 @@
         <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>1472</v>
+        <v>1512</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>1473</v>
+        <v>1513</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>1474</v>
+        <v>1514</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -5019,7 +5139,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1475</v>
+        <v>1515</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -5045,16 +5165,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>1476</v>
+        <v>1516</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>1477</v>
+        <v>1517</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>1478</v>
+        <v>1518</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -5114,7 +5234,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>1479</v>
+        <v>1519</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -5140,16 +5260,16 @@
         <v>56</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>1481</v>
+        <v>1521</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>1482</v>
+        <v>1522</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -5209,7 +5329,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>1483</v>
+        <v>1523</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -5235,16 +5355,16 @@
         <v>60</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>1484</v>
+        <v>1524</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>1485</v>
+        <v>1525</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>1486</v>
+        <v>1526</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -5304,7 +5424,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>1487</v>
+        <v>1527</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -5330,16 +5450,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>1488</v>
+        <v>1528</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>1489</v>
+        <v>1529</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>1490</v>
+        <v>1530</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -5399,7 +5519,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1491</v>
+        <v>1531</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>

--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="1972">
   <si>
     <t>DT Code*</t>
   </si>
@@ -4615,6 +4615,1326 @@
   </si>
   <si>
     <t>6975027924200</t>
+  </si>
+  <si>
+    <t>AUTODSR_32D98</t>
+  </si>
+  <si>
+    <t>03500884600</t>
+  </si>
+  <si>
+    <t>EMP197190</t>
+  </si>
+  <si>
+    <t>78395-0209200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_73261</t>
+  </si>
+  <si>
+    <t>03503279100</t>
+  </si>
+  <si>
+    <t>EMPD593B5</t>
+  </si>
+  <si>
+    <t>78395-0386330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_25C5B</t>
+  </si>
+  <si>
+    <t>03504432800</t>
+  </si>
+  <si>
+    <t>EMPEE4B28</t>
+  </si>
+  <si>
+    <t>78395-0494170-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5E6DD</t>
+  </si>
+  <si>
+    <t>03505421000</t>
+  </si>
+  <si>
+    <t>EMP5542A1</t>
+  </si>
+  <si>
+    <t>78395-0590830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_270A2</t>
+  </si>
+  <si>
+    <t>03512550400</t>
+  </si>
+  <si>
+    <t>EMP8FBF0B</t>
+  </si>
+  <si>
+    <t>78395-1304300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4791E</t>
+  </si>
+  <si>
+    <t>03836739200</t>
+  </si>
+  <si>
+    <t>EMP0ABA31</t>
+  </si>
+  <si>
+    <t>84848-3816390-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F6995</t>
+  </si>
+  <si>
+    <t>03838974300</t>
+  </si>
+  <si>
+    <t>EMP93642F</t>
+  </si>
+  <si>
+    <t>84848-3939410-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_237B8</t>
+  </si>
+  <si>
+    <t>03839899700</t>
+  </si>
+  <si>
+    <t>EMP6FB8E8</t>
+  </si>
+  <si>
+    <t>84848-4372300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_916F8</t>
+  </si>
+  <si>
+    <t>03844260700</t>
+  </si>
+  <si>
+    <t>EMPF710B8</t>
+  </si>
+  <si>
+    <t>84848-4504270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8A4BF</t>
+  </si>
+  <si>
+    <t>03845464300</t>
+  </si>
+  <si>
+    <t>EMP57AAB4</t>
+  </si>
+  <si>
+    <t>84848-4684420-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_ECD77</t>
+  </si>
+  <si>
+    <t>03170715800</t>
+  </si>
+  <si>
+    <t>EMP00C1ED</t>
+  </si>
+  <si>
+    <t>92921-7386030-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E89A1</t>
+  </si>
+  <si>
+    <t>03175165600</t>
+  </si>
+  <si>
+    <t>EMP18FF18</t>
+  </si>
+  <si>
+    <t>92921-7565310-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DEC02</t>
+  </si>
+  <si>
+    <t>03176131600</t>
+  </si>
+  <si>
+    <t>EMP45B731</t>
+  </si>
+  <si>
+    <t>92921-7656930-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_69CA8</t>
+  </si>
+  <si>
+    <t>03177067800</t>
+  </si>
+  <si>
+    <t>EMP46D194</t>
+  </si>
+  <si>
+    <t>92921-7757630-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA7A2</t>
+  </si>
+  <si>
+    <t>03178059900</t>
+  </si>
+  <si>
+    <t>EMP17F32B</t>
+  </si>
+  <si>
+    <t>92921-7850370-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FB0A9</t>
+  </si>
+  <si>
+    <t>03460407800</t>
+  </si>
+  <si>
+    <t>EMP82C13C</t>
+  </si>
+  <si>
+    <t>22194-6151620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_14A1E</t>
+  </si>
+  <si>
+    <t>03462391300</t>
+  </si>
+  <si>
+    <t>EMPB26C4A</t>
+  </si>
+  <si>
+    <t>22194-6292720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_74E28</t>
+  </si>
+  <si>
+    <t>03463406800</t>
+  </si>
+  <si>
+    <t>EMP94B5B1</t>
+  </si>
+  <si>
+    <t>22194-6390750-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B5C1F</t>
+  </si>
+  <si>
+    <t>03464346500</t>
+  </si>
+  <si>
+    <t>EMPAD7832</t>
+  </si>
+  <si>
+    <t>22194-6481790-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_85740</t>
+  </si>
+  <si>
+    <t>03465286900</t>
+  </si>
+  <si>
+    <t>EMPA812E2</t>
+  </si>
+  <si>
+    <t>22194-6576490-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_64833</t>
+  </si>
+  <si>
+    <t>03846590000</t>
+  </si>
+  <si>
+    <t>EMPB5E926</t>
+  </si>
+  <si>
+    <t>49808-4965900-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_36E46</t>
+  </si>
+  <si>
+    <t>03851071400</t>
+  </si>
+  <si>
+    <t>EMPBCB4E4</t>
+  </si>
+  <si>
+    <t>49808-5679190-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1D052</t>
+  </si>
+  <si>
+    <t>03859295500</t>
+  </si>
+  <si>
+    <t>EMPE47296</t>
+  </si>
+  <si>
+    <t>49808-5997750-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_242AD</t>
+  </si>
+  <si>
+    <t>03860703100</t>
+  </si>
+  <si>
+    <t>EMP8C50C3</t>
+  </si>
+  <si>
+    <t>49808-6284310-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B2BB5</t>
+  </si>
+  <si>
+    <t>03863394200</t>
+  </si>
+  <si>
+    <t>EMPD9F1D7</t>
+  </si>
+  <si>
+    <t>49808-6493910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8A195</t>
+  </si>
+  <si>
+    <t>03358614800</t>
+  </si>
+  <si>
+    <t>EMPB69199</t>
+  </si>
+  <si>
+    <t>13233-6033260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E612B</t>
+  </si>
+  <si>
+    <t>03361750800</t>
+  </si>
+  <si>
+    <t>EMPE93427</t>
+  </si>
+  <si>
+    <t>13233-6514290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DA6FB</t>
+  </si>
+  <si>
+    <t>03366694400</t>
+  </si>
+  <si>
+    <t>EMP6FF60F</t>
+  </si>
+  <si>
+    <t>13233-6717680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7EC6C</t>
+  </si>
+  <si>
+    <t>03367974000</t>
+  </si>
+  <si>
+    <t>EMPD0FFCC</t>
+  </si>
+  <si>
+    <t>13233-6864910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_646DE</t>
+  </si>
+  <si>
+    <t>03369306000</t>
+  </si>
+  <si>
+    <t>EMP65F312</t>
+  </si>
+  <si>
+    <t>13233-7011380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4357C</t>
+  </si>
+  <si>
+    <t>03424498400</t>
+  </si>
+  <si>
+    <t>EMPF29D09</t>
+  </si>
+  <si>
+    <t>15654-2721950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_37B31</t>
+  </si>
+  <si>
+    <t>03429078200</t>
+  </si>
+  <si>
+    <t>EMP8E1C44</t>
+  </si>
+  <si>
+    <t>15654-3019670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DAB3E</t>
+  </si>
+  <si>
+    <t>03431044000</t>
+  </si>
+  <si>
+    <t>EMP5777DC</t>
+  </si>
+  <si>
+    <t>15654-3151520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_952EA</t>
+  </si>
+  <si>
+    <t>03433619500</t>
+  </si>
+  <si>
+    <t>EMP87CC92</t>
+  </si>
+  <si>
+    <t>15654-3430130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5894F</t>
+  </si>
+  <si>
+    <t>03435078400</t>
+  </si>
+  <si>
+    <t>EMPD73643</t>
+  </si>
+  <si>
+    <t>15654-3570720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4C411</t>
+  </si>
+  <si>
+    <t>03349183999</t>
+  </si>
+  <si>
+    <t>EMP93B80E</t>
+  </si>
+  <si>
+    <t>14673-5255909-9</t>
+  </si>
+  <si>
+    <t>AUTODSR_33CE5</t>
+  </si>
+  <si>
+    <t>03355678800</t>
+  </si>
+  <si>
+    <t>EMP5EDAB2</t>
+  </si>
+  <si>
+    <t>14673-6022560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CADDB</t>
+  </si>
+  <si>
+    <t>03371243499</t>
+  </si>
+  <si>
+    <t>EMP304FB1</t>
+  </si>
+  <si>
+    <t>14673-7189220-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F1EC0</t>
+  </si>
+  <si>
+    <t>03374130700</t>
+  </si>
+  <si>
+    <t>EMPACD185</t>
+  </si>
+  <si>
+    <t>14673-7527260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_71C5C</t>
+  </si>
+  <si>
+    <t>03376154000</t>
+  </si>
+  <si>
+    <t>EMPCB0DE2</t>
+  </si>
+  <si>
+    <t>14673-7654970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_14DB7</t>
+  </si>
+  <si>
+    <t>03660175800</t>
+  </si>
+  <si>
+    <t>EMPB84E51</t>
+  </si>
+  <si>
+    <t>35146-6134239-9</t>
+  </si>
+  <si>
+    <t>AUTODSR_18627</t>
+  </si>
+  <si>
+    <t>03662897700</t>
+  </si>
+  <si>
+    <t>EMP124D8E</t>
+  </si>
+  <si>
+    <t>35146-6584250-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_66D96</t>
+  </si>
+  <si>
+    <t>03666413500</t>
+  </si>
+  <si>
+    <t>EMP73E5FD</t>
+  </si>
+  <si>
+    <t>35146-6695260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4AF06</t>
+  </si>
+  <si>
+    <t>03667370999</t>
+  </si>
+  <si>
+    <t>EMP384EEE</t>
+  </si>
+  <si>
+    <t>35146-6780290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B5725</t>
+  </si>
+  <si>
+    <t>03668192300</t>
+  </si>
+  <si>
+    <t>EMP92222C</t>
+  </si>
+  <si>
+    <t>35146-7072220-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E3538</t>
+  </si>
+  <si>
+    <t>03290097700</t>
+  </si>
+  <si>
+    <t>EMPFD6A7B</t>
+  </si>
+  <si>
+    <t>59742-9126270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1FB07</t>
+  </si>
+  <si>
+    <t>03292062700</t>
+  </si>
+  <si>
+    <t>EMPED3371</t>
+  </si>
+  <si>
+    <t>59742-9252700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_08594</t>
+  </si>
+  <si>
+    <t>03292953000</t>
+  </si>
+  <si>
+    <t>EMP637D19</t>
+  </si>
+  <si>
+    <t>59742-9336490-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_89697</t>
+  </si>
+  <si>
+    <t>03293756500</t>
+  </si>
+  <si>
+    <t>EMPAEAD87</t>
+  </si>
+  <si>
+    <t>59742-9440480-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9C5E4</t>
+  </si>
+  <si>
+    <t>03294885000</t>
+  </si>
+  <si>
+    <t>EMPB85E92</t>
+  </si>
+  <si>
+    <t>59742-9541360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_64CAF</t>
+  </si>
+  <si>
+    <t>03803881200</t>
+  </si>
+  <si>
+    <t>EMP2007B7</t>
+  </si>
+  <si>
+    <t>60908-0615920-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0703F</t>
+  </si>
+  <si>
+    <t>03807764500</t>
+  </si>
+  <si>
+    <t>EMP133C01</t>
+  </si>
+  <si>
+    <t>60908-1147600-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_060EA</t>
+  </si>
+  <si>
+    <t>03814331900</t>
+  </si>
+  <si>
+    <t>EMPCB51D1</t>
+  </si>
+  <si>
+    <t>60908-1480760-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D2C25</t>
+  </si>
+  <si>
+    <t>03815512900</t>
+  </si>
+  <si>
+    <t>EMPEACC20</t>
+  </si>
+  <si>
+    <t>60908-1596260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DC669</t>
+  </si>
+  <si>
+    <t>03816502800</t>
+  </si>
+  <si>
+    <t>EMPF0C215</t>
+  </si>
+  <si>
+    <t>60908-1707280-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DA5C2</t>
+  </si>
+  <si>
+    <t>03577713100</t>
+  </si>
+  <si>
+    <t>EMP1E5F6C</t>
+  </si>
+  <si>
+    <t>08515-7978250-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2431B</t>
+  </si>
+  <si>
+    <t>03580979700</t>
+  </si>
+  <si>
+    <t>EMP7D5FC1</t>
+  </si>
+  <si>
+    <t>08515-8223010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_95C36</t>
+  </si>
+  <si>
+    <t>03582761000</t>
+  </si>
+  <si>
+    <t>EMPA1CA7B</t>
+  </si>
+  <si>
+    <t>08515-8326640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F81DD</t>
+  </si>
+  <si>
+    <t>03583726900</t>
+  </si>
+  <si>
+    <t>EMP2BF3EC</t>
+  </si>
+  <si>
+    <t>08515-8421970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EB893</t>
+  </si>
+  <si>
+    <t>03590246600</t>
+  </si>
+  <si>
+    <t>EMP1FF4EA</t>
+  </si>
+  <si>
+    <t>08515-9247520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8D1B1</t>
+  </si>
+  <si>
+    <t>03298691500</t>
+  </si>
+  <si>
+    <t>EMPE7D33E</t>
+  </si>
+  <si>
+    <t>20182-9976510-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BC616</t>
+  </si>
+  <si>
+    <t>03300518600</t>
+  </si>
+  <si>
+    <t>EMP19988E</t>
+  </si>
+  <si>
+    <t>20183-0094840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_242B4</t>
+  </si>
+  <si>
+    <t>03301393400</t>
+  </si>
+  <si>
+    <t>EMP7E8E05</t>
+  </si>
+  <si>
+    <t>20183-0183250-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_280DA</t>
+  </si>
+  <si>
+    <t>03302240700</t>
+  </si>
+  <si>
+    <t>EMP805054</t>
+  </si>
+  <si>
+    <t>20183-0265400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_89E34</t>
+  </si>
+  <si>
+    <t>03303055300</t>
+  </si>
+  <si>
+    <t>EMPC5DCA9</t>
+  </si>
+  <si>
+    <t>20183-0345670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6EA4E</t>
+  </si>
+  <si>
+    <t>03777342700</t>
+  </si>
+  <si>
+    <t>EMP4695A0</t>
+  </si>
+  <si>
+    <t>32397-8199040-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_787C1</t>
+  </si>
+  <si>
+    <t>03786176100</t>
+  </si>
+  <si>
+    <t>EMP9924C2</t>
+  </si>
+  <si>
+    <t>32397-8926700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4C1F5</t>
+  </si>
+  <si>
+    <t>03792564000</t>
+  </si>
+  <si>
+    <t>EMPAE8EFE</t>
+  </si>
+  <si>
+    <t>32397-9312000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_429B0</t>
+  </si>
+  <si>
+    <t>03793731800</t>
+  </si>
+  <si>
+    <t>EMP8EBF00</t>
+  </si>
+  <si>
+    <t>32397-9420970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C6598</t>
+  </si>
+  <si>
+    <t>03794649000</t>
+  </si>
+  <si>
+    <t>EMP870EE8</t>
+  </si>
+  <si>
+    <t>32397-9523760-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4DDC7</t>
+  </si>
+  <si>
+    <t>03970243300</t>
+  </si>
+  <si>
+    <t>EMP4B4CD1</t>
+  </si>
+  <si>
+    <t>64479-7194830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_53858</t>
+  </si>
+  <si>
+    <t>03973052900</t>
+  </si>
+  <si>
+    <t>EMPBC287A</t>
+  </si>
+  <si>
+    <t>64479-8005020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F772A</t>
+  </si>
+  <si>
+    <t>03980854900</t>
+  </si>
+  <si>
+    <t>EMPFD83AD</t>
+  </si>
+  <si>
+    <t>64479-8281750-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_31DB8</t>
+  </si>
+  <si>
+    <t>03988416600</t>
+  </si>
+  <si>
+    <t>EMP625536</t>
+  </si>
+  <si>
+    <t>64479-8947120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_83A9E</t>
+  </si>
+  <si>
+    <t>03990490600</t>
+  </si>
+  <si>
+    <t>EMP9FBCA2</t>
+  </si>
+  <si>
+    <t>64479-9115200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_170F9</t>
+  </si>
+  <si>
+    <t>03323707900</t>
+  </si>
+  <si>
+    <t>EMP702EF6</t>
+  </si>
+  <si>
+    <t>35833-2553810-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FB542</t>
+  </si>
+  <si>
+    <t>03333393900</t>
+  </si>
+  <si>
+    <t>EMP762BB3</t>
+  </si>
+  <si>
+    <t>35833-3446060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_829F3</t>
+  </si>
+  <si>
+    <t>03335337800</t>
+  </si>
+  <si>
+    <t>EMPC50267</t>
+  </si>
+  <si>
+    <t>35833-3639270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0E9ED</t>
+  </si>
+  <si>
+    <t>03337430300</t>
+  </si>
+  <si>
+    <t>EMPCD0664</t>
+  </si>
+  <si>
+    <t>35833-3832240-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3D874</t>
+  </si>
+  <si>
+    <t>03339184000</t>
+  </si>
+  <si>
+    <t>EMP86DC15</t>
+  </si>
+  <si>
+    <t>35833-3988230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_566E4</t>
+  </si>
+  <si>
+    <t>03958654600</t>
+  </si>
+  <si>
+    <t>EMP7C42E1</t>
+  </si>
+  <si>
+    <t>92299-6034280-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8D5B1</t>
+  </si>
+  <si>
+    <t>03964877300</t>
+  </si>
+  <si>
+    <t>EMP82632F</t>
+  </si>
+  <si>
+    <t>92299-6574050-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B9AEA</t>
+  </si>
+  <si>
+    <t>03966337800</t>
+  </si>
+  <si>
+    <t>EMPE9E2BB</t>
+  </si>
+  <si>
+    <t>92299-6689040-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_79BE2</t>
+  </si>
+  <si>
+    <t>03967481300</t>
+  </si>
+  <si>
+    <t>EMP2F7316</t>
+  </si>
+  <si>
+    <t>92299-6801590-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_21D4A</t>
+  </si>
+  <si>
+    <t>03968607700</t>
+  </si>
+  <si>
+    <t>EMPAC8ED1</t>
+  </si>
+  <si>
+    <t>92299-6917290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EABCE</t>
+  </si>
+  <si>
+    <t>03130842800</t>
+  </si>
+  <si>
+    <t>EMP0A2220</t>
+  </si>
+  <si>
+    <t>24811-3261900-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8FC85</t>
+  </si>
+  <si>
+    <t>03142954500</t>
+  </si>
+  <si>
+    <t>EMPE40DA7</t>
+  </si>
+  <si>
+    <t>24811-4388860-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9DD14</t>
+  </si>
+  <si>
+    <t>03144772000</t>
+  </si>
+  <si>
+    <t>EMP284CCC</t>
+  </si>
+  <si>
+    <t>24811-4556050-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_917AA</t>
+  </si>
+  <si>
+    <t>03146420800</t>
+  </si>
+  <si>
+    <t>EMP508243</t>
+  </si>
+  <si>
+    <t>24811-4732330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0567D</t>
+  </si>
+  <si>
+    <t>03148515300</t>
+  </si>
+  <si>
+    <t>EMP725CA0</t>
+  </si>
+  <si>
+    <t>24811-4940180-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1543D</t>
+  </si>
+  <si>
+    <t>03169901400</t>
+  </si>
+  <si>
+    <t>EMP4E6DDA</t>
+  </si>
+  <si>
+    <t>33111-7072830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1CABD</t>
+  </si>
+  <si>
+    <t>03174984800</t>
+  </si>
+  <si>
+    <t>EMP2F814A</t>
+  </si>
+  <si>
+    <t>33111-7574970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E815C</t>
+  </si>
+  <si>
+    <t>03176665200</t>
+  </si>
+  <si>
+    <t>EMPD92C67</t>
+  </si>
+  <si>
+    <t>33111-7717300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB7BF</t>
+  </si>
+  <si>
+    <t>03177659300</t>
+  </si>
+  <si>
+    <t>EMP54C4E6</t>
+  </si>
+  <si>
+    <t>33111-7803490-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4586A</t>
+  </si>
+  <si>
+    <t>03178367000</t>
+  </si>
+  <si>
+    <t>EMP9B70DE</t>
+  </si>
+  <si>
+    <t>33111-7870720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_18D25</t>
+  </si>
+  <si>
+    <t>03844008000</t>
+  </si>
+  <si>
+    <t>EMPFFC902</t>
+  </si>
+  <si>
+    <t>41208-4576500-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B258</t>
+  </si>
+  <si>
+    <t>03853919100</t>
+  </si>
+  <si>
+    <t>EMPE625F5</t>
+  </si>
+  <si>
+    <t>41208-5475290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CB291</t>
+  </si>
+  <si>
+    <t>03855585300</t>
+  </si>
+  <si>
+    <t>EMPA87C4C</t>
+  </si>
+  <si>
+    <t>41208-5684640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB527</t>
+  </si>
+  <si>
+    <t>03858204600</t>
+  </si>
+  <si>
+    <t>EMPB574F2</t>
+  </si>
+  <si>
+    <t>41208-5948330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4418D</t>
+  </si>
+  <si>
+    <t>03860249700</t>
+  </si>
+  <si>
+    <t>EMPA01816</t>
+  </si>
+  <si>
+    <t>41208-6090770-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E9116</t>
+  </si>
+  <si>
+    <t>03401617300</t>
+  </si>
+  <si>
+    <t>EMPAC5222</t>
+  </si>
+  <si>
+    <t>55654-0336080-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1E7A0</t>
+  </si>
+  <si>
+    <t>03411963100</t>
+  </si>
+  <si>
+    <t>EMP987963</t>
+  </si>
+  <si>
+    <t>55654-1282130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CE45A</t>
+  </si>
+  <si>
+    <t>03413671900</t>
+  </si>
+  <si>
+    <t>EMP264B43</t>
+  </si>
+  <si>
+    <t>55654-1505740-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_01E92</t>
+  </si>
+  <si>
+    <t>03416552200</t>
+  </si>
+  <si>
+    <t>EMP26A520</t>
+  </si>
+  <si>
+    <t>55654-1751540-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AD320</t>
+  </si>
+  <si>
+    <t>03418378500</t>
+  </si>
+  <si>
+    <t>EMP232788</t>
+  </si>
+  <si>
+    <t>55654-1925960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C641E</t>
+  </si>
+  <si>
+    <t>03335633200</t>
+  </si>
+  <si>
+    <t>EMP5D29EA</t>
+  </si>
+  <si>
+    <t>67393-3667230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6F126</t>
+  </si>
+  <si>
+    <t>03343759300</t>
+  </si>
+  <si>
+    <t>EMP8D4E3B</t>
+  </si>
+  <si>
+    <t>67393-4472350-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C4B72</t>
+  </si>
+  <si>
+    <t>03345529900</t>
+  </si>
+  <si>
+    <t>EMP460682</t>
+  </si>
+  <si>
+    <t>67393-4616910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_65BBE</t>
+  </si>
+  <si>
+    <t>03346679000</t>
+  </si>
+  <si>
+    <t>EMP56AFA2</t>
+  </si>
+  <si>
+    <t>67393-4726960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5A63D</t>
+  </si>
+  <si>
+    <t>03347908300</t>
+  </si>
+  <si>
+    <t>EMPC8E144</t>
+  </si>
+  <si>
+    <t>67393-4852920-0</t>
   </si>
 </sst>
 </file>
@@ -5070,16 +6390,16 @@
         <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>1512</v>
+        <v>1952</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>1513</v>
+        <v>1953</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>1514</v>
+        <v>1954</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -5139,7 +6459,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1515</v>
+        <v>1955</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -5165,16 +6485,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>1516</v>
+        <v>1956</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>1517</v>
+        <v>1957</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>1518</v>
+        <v>1958</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -5234,7 +6554,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>1519</v>
+        <v>1959</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -5260,16 +6580,16 @@
         <v>56</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>1520</v>
+        <v>1960</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>1521</v>
+        <v>1961</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>1522</v>
+        <v>1962</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -5329,7 +6649,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>1523</v>
+        <v>1963</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -5355,16 +6675,16 @@
         <v>60</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>1524</v>
+        <v>1964</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>1525</v>
+        <v>1965</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>1526</v>
+        <v>1966</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -5424,7 +6744,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>1527</v>
+        <v>1967</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -5450,16 +6770,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>1528</v>
+        <v>1968</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>1529</v>
+        <v>1969</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>1530</v>
+        <v>1970</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -5519,7 +6839,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1531</v>
+        <v>1971</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>

--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="1972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="2292">
   <si>
     <t>DT Code*</t>
   </si>
@@ -5935,6 +5935,966 @@
   </si>
   <si>
     <t>67393-4852920-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9861F</t>
+  </si>
+  <si>
+    <t>03577009600</t>
+  </si>
+  <si>
+    <t>EMPE474FA</t>
+  </si>
+  <si>
+    <t>10225-7823110-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9084F</t>
+  </si>
+  <si>
+    <t>03582815900</t>
+  </si>
+  <si>
+    <t>EMP8EABD1</t>
+  </si>
+  <si>
+    <t>10225-8371870-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7616C</t>
+  </si>
+  <si>
+    <t>03584333500</t>
+  </si>
+  <si>
+    <t>EMP42EFDD</t>
+  </si>
+  <si>
+    <t>10225-8498050-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D8F13</t>
+  </si>
+  <si>
+    <t>03585648800</t>
+  </si>
+  <si>
+    <t>EMP4287C1</t>
+  </si>
+  <si>
+    <t>10225-8639870-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0AA1C</t>
+  </si>
+  <si>
+    <t>03587168600</t>
+  </si>
+  <si>
+    <t>EMP4EA905</t>
+  </si>
+  <si>
+    <t>10225-8779620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_90E03</t>
+  </si>
+  <si>
+    <t>03214586500</t>
+  </si>
+  <si>
+    <t>EMP9545E9</t>
+  </si>
+  <si>
+    <t>11982-1572180-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B7CEA</t>
+  </si>
+  <si>
+    <t>03221503300</t>
+  </si>
+  <si>
+    <t>EMP8291E9</t>
+  </si>
+  <si>
+    <t>11982-2221260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C638E</t>
+  </si>
+  <si>
+    <t>03222883200</t>
+  </si>
+  <si>
+    <t>EMP87FECD</t>
+  </si>
+  <si>
+    <t>11982-2370300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0C78F</t>
+  </si>
+  <si>
+    <t>03224501100</t>
+  </si>
+  <si>
+    <t>EMP918A1E</t>
+  </si>
+  <si>
+    <t>11982-2514940-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9E1FD</t>
+  </si>
+  <si>
+    <t>03225779200</t>
+  </si>
+  <si>
+    <t>EMPAB92E9</t>
+  </si>
+  <si>
+    <t>11982-2636400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3487C</t>
+  </si>
+  <si>
+    <t>03140746600</t>
+  </si>
+  <si>
+    <t>EMP47E2B2</t>
+  </si>
+  <si>
+    <t>16551-4193120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_34074</t>
+  </si>
+  <si>
+    <t>03147154300</t>
+  </si>
+  <si>
+    <t>EMPB0E8AB</t>
+  </si>
+  <si>
+    <t>16551-4769680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_14BC2</t>
+  </si>
+  <si>
+    <t>03148243100</t>
+  </si>
+  <si>
+    <t>EMP4BB0CB</t>
+  </si>
+  <si>
+    <t>16551-4886830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_79E9A</t>
+  </si>
+  <si>
+    <t>03149359800</t>
+  </si>
+  <si>
+    <t>EMP14E015</t>
+  </si>
+  <si>
+    <t>16551-4987950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EB035</t>
+  </si>
+  <si>
+    <t>03150435400</t>
+  </si>
+  <si>
+    <t>EMP11F493</t>
+  </si>
+  <si>
+    <t>16551-5096460-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6F444</t>
+  </si>
+  <si>
+    <t>03042095300</t>
+  </si>
+  <si>
+    <t>EMP55A879</t>
+  </si>
+  <si>
+    <t>88620-4400770-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_486CE</t>
+  </si>
+  <si>
+    <t>03059584700</t>
+  </si>
+  <si>
+    <t>EMP5A99D0</t>
+  </si>
+  <si>
+    <t>88620-6086780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7E237</t>
+  </si>
+  <si>
+    <t>03061809300</t>
+  </si>
+  <si>
+    <t>EMP7A304B</t>
+  </si>
+  <si>
+    <t>88620-6350550-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A71A2</t>
+  </si>
+  <si>
+    <t>03064359700</t>
+  </si>
+  <si>
+    <t>EMP17C7B7</t>
+  </si>
+  <si>
+    <t>88620-7029370-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_33726</t>
+  </si>
+  <si>
+    <t>03073564500</t>
+  </si>
+  <si>
+    <t>EMP9FA54C</t>
+  </si>
+  <si>
+    <t>88620-7500620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A007D</t>
+  </si>
+  <si>
+    <t>03518722900</t>
+  </si>
+  <si>
+    <t>EMP5E971C</t>
+  </si>
+  <si>
+    <t>93115-2071460-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6AAE5</t>
+  </si>
+  <si>
+    <t>03527978300</t>
+  </si>
+  <si>
+    <t>EMP5C9C9D</t>
+  </si>
+  <si>
+    <t>93115-2887940-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2462F</t>
+  </si>
+  <si>
+    <t>03529804400</t>
+  </si>
+  <si>
+    <t>EMPB2F7E9</t>
+  </si>
+  <si>
+    <t>93115-3071060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_871E5</t>
+  </si>
+  <si>
+    <t>03531696200</t>
+  </si>
+  <si>
+    <t>EMPC18C45</t>
+  </si>
+  <si>
+    <t>93115-3244290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A38A2</t>
+  </si>
+  <si>
+    <t>03533571500</t>
+  </si>
+  <si>
+    <t>EMPD89BCC</t>
+  </si>
+  <si>
+    <t>93115-3443150-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BAC6E</t>
+  </si>
+  <si>
+    <t>03430041800</t>
+  </si>
+  <si>
+    <t>EMP6ECA08</t>
+  </si>
+  <si>
+    <t>01574-3128090-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E6595</t>
+  </si>
+  <si>
+    <t>03432291000</t>
+  </si>
+  <si>
+    <t>EMP0AD138</t>
+  </si>
+  <si>
+    <t>01574-3292740-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CC8C6</t>
+  </si>
+  <si>
+    <t>03433490300</t>
+  </si>
+  <si>
+    <t>EMP0CA933</t>
+  </si>
+  <si>
+    <t>01574-3410720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5BC15</t>
+  </si>
+  <si>
+    <t>03434654200</t>
+  </si>
+  <si>
+    <t>EMPF24186</t>
+  </si>
+  <si>
+    <t>01574-3517910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7B115</t>
+  </si>
+  <si>
+    <t>03435735600</t>
+  </si>
+  <si>
+    <t>EMP1BE914</t>
+  </si>
+  <si>
+    <t>01574-3624840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7BDF4</t>
+  </si>
+  <si>
+    <t>03382702300</t>
+  </si>
+  <si>
+    <t>EMP0080B4</t>
+  </si>
+  <si>
+    <t>03663-8363780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E2284</t>
+  </si>
+  <si>
+    <t>03389900300</t>
+  </si>
+  <si>
+    <t>EMP70220A</t>
+  </si>
+  <si>
+    <t>03663-9056100-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_11999</t>
+  </si>
+  <si>
+    <t>03391029500</t>
+  </si>
+  <si>
+    <t>EMPEFD2BF</t>
+  </si>
+  <si>
+    <t>03663-9160710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9AA2D</t>
+  </si>
+  <si>
+    <t>03392212700</t>
+  </si>
+  <si>
+    <t>EMP114393</t>
+  </si>
+  <si>
+    <t>03663-9279530-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_835DD</t>
+  </si>
+  <si>
+    <t>03393380500</t>
+  </si>
+  <si>
+    <t>EMPA5CDCE</t>
+  </si>
+  <si>
+    <t>03663-9384460-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A5DFE</t>
+  </si>
+  <si>
+    <t>03199494900</t>
+  </si>
+  <si>
+    <t>EMP9A2F32</t>
+  </si>
+  <si>
+    <t>79922-0052510-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DBEE9</t>
+  </si>
+  <si>
+    <t>03205325100</t>
+  </si>
+  <si>
+    <t>EMP847415</t>
+  </si>
+  <si>
+    <t>79922-0582450-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_48C18</t>
+  </si>
+  <si>
+    <t>03206269000</t>
+  </si>
+  <si>
+    <t>EMPFDBCEF</t>
+  </si>
+  <si>
+    <t>79922-0688320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2BF7C</t>
+  </si>
+  <si>
+    <t>03207447400</t>
+  </si>
+  <si>
+    <t>EMP75155F</t>
+  </si>
+  <si>
+    <t>79922-0835620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8C096</t>
+  </si>
+  <si>
+    <t>03209125400</t>
+  </si>
+  <si>
+    <t>EMP177A36</t>
+  </si>
+  <si>
+    <t>79922-0970650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_41751</t>
+  </si>
+  <si>
+    <t>03714999300</t>
+  </si>
+  <si>
+    <t>EMP4F3471</t>
+  </si>
+  <si>
+    <t>67997-1852340-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_54E94</t>
+  </si>
+  <si>
+    <t>03726219500</t>
+  </si>
+  <si>
+    <t>EMPC6CAEF</t>
+  </si>
+  <si>
+    <t>67997-2772520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A72D1</t>
+  </si>
+  <si>
+    <t>03728756400</t>
+  </si>
+  <si>
+    <t>EMP5177FA</t>
+  </si>
+  <si>
+    <t>67997-3447000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_54E78</t>
+  </si>
+  <si>
+    <t>03736341700</t>
+  </si>
+  <si>
+    <t>EMPDD8627</t>
+  </si>
+  <si>
+    <t>67997-3740040-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_83F7A</t>
+  </si>
+  <si>
+    <t>03739730400</t>
+  </si>
+  <si>
+    <t>EMP3A3465</t>
+  </si>
+  <si>
+    <t>67997-4097960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_48E54</t>
+  </si>
+  <si>
+    <t>03982544200</t>
+  </si>
+  <si>
+    <t>EMP2EE1E6</t>
+  </si>
+  <si>
+    <t>77789-8432820-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_68A99</t>
+  </si>
+  <si>
+    <t>03986039000</t>
+  </si>
+  <si>
+    <t>EMP139DB5</t>
+  </si>
+  <si>
+    <t>77789-8681250-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AFAD6</t>
+  </si>
+  <si>
+    <t>03987765700</t>
+  </si>
+  <si>
+    <t>EMP371D41</t>
+  </si>
+  <si>
+    <t>77789-8883860-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_99000</t>
+  </si>
+  <si>
+    <t>03989789700</t>
+  </si>
+  <si>
+    <t>EMPB55DB0</t>
+  </si>
+  <si>
+    <t>77789-9085110-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_232BA</t>
+  </si>
+  <si>
+    <t>03993232000</t>
+  </si>
+  <si>
+    <t>EMPC8A269</t>
+  </si>
+  <si>
+    <t>77789-9467890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C7F11</t>
+  </si>
+  <si>
+    <t>03672547700</t>
+  </si>
+  <si>
+    <t>EMP5C05FC</t>
+  </si>
+  <si>
+    <t>93826-7464200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0D1BD</t>
+  </si>
+  <si>
+    <t>03680279900</t>
+  </si>
+  <si>
+    <t>EMP047530</t>
+  </si>
+  <si>
+    <t>93826-8097800-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8E124</t>
+  </si>
+  <si>
+    <t>03681712200</t>
+  </si>
+  <si>
+    <t>EMPC66A19</t>
+  </si>
+  <si>
+    <t>93826-8234880-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1D24F</t>
+  </si>
+  <si>
+    <t>03682982100</t>
+  </si>
+  <si>
+    <t>EMP12A8E6</t>
+  </si>
+  <si>
+    <t>93826-8355140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA5D3</t>
+  </si>
+  <si>
+    <t>03684144400</t>
+  </si>
+  <si>
+    <t>EMPB8FE62</t>
+  </si>
+  <si>
+    <t>93826-8472690-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5D8DA</t>
+  </si>
+  <si>
+    <t>03828111300</t>
+  </si>
+  <si>
+    <t>EMPBA7C4F</t>
+  </si>
+  <si>
+    <t>09358-2936160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_67674</t>
+  </si>
+  <si>
+    <t>03835206700</t>
+  </si>
+  <si>
+    <t>EMP5441C6</t>
+  </si>
+  <si>
+    <t>09358-3584380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5844E</t>
+  </si>
+  <si>
+    <t>03836456100</t>
+  </si>
+  <si>
+    <t>EMPD35585</t>
+  </si>
+  <si>
+    <t>09358-3698020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DAA06</t>
+  </si>
+  <si>
+    <t>03837723200</t>
+  </si>
+  <si>
+    <t>EMP3A0769</t>
+  </si>
+  <si>
+    <t>09358-3829940-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8E317</t>
+  </si>
+  <si>
+    <t>03839084200</t>
+  </si>
+  <si>
+    <t>EMP5D86C6</t>
+  </si>
+  <si>
+    <t>09358-3985370-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F66BA</t>
+  </si>
+  <si>
+    <t>03500746900</t>
+  </si>
+  <si>
+    <t>EMP173449</t>
+  </si>
+  <si>
+    <t>14135-0179100-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_117DC</t>
+  </si>
+  <si>
+    <t>03507090100</t>
+  </si>
+  <si>
+    <t>EMP460877</t>
+  </si>
+  <si>
+    <t>14135-0763990-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B735E</t>
+  </si>
+  <si>
+    <t>03508141900</t>
+  </si>
+  <si>
+    <t>EMP12523A</t>
+  </si>
+  <si>
+    <t>14135-0858020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_18408</t>
+  </si>
+  <si>
+    <t>03509115900</t>
+  </si>
+  <si>
+    <t>EMP9C86C8</t>
+  </si>
+  <si>
+    <t>14135-0952120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A3058</t>
+  </si>
+  <si>
+    <t>03509972700</t>
+  </si>
+  <si>
+    <t>EMP7CDB3D</t>
+  </si>
+  <si>
+    <t>14135-1036410-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F54ED</t>
+  </si>
+  <si>
+    <t>03974254500</t>
+  </si>
+  <si>
+    <t>EMP3CF38A</t>
+  </si>
+  <si>
+    <t>17679-7550560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DEEE2</t>
+  </si>
+  <si>
+    <t>03980659500</t>
+  </si>
+  <si>
+    <t>EMPF165F8</t>
+  </si>
+  <si>
+    <t>17679-8126290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C8882</t>
+  </si>
+  <si>
+    <t>03982092800</t>
+  </si>
+  <si>
+    <t>EMP04DF8E</t>
+  </si>
+  <si>
+    <t>17679-8278620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A77EA</t>
+  </si>
+  <si>
+    <t>03983684800</t>
+  </si>
+  <si>
+    <t>EMP44BB28</t>
+  </si>
+  <si>
+    <t>17679-8441930-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_55FDF</t>
+  </si>
+  <si>
+    <t>03985000400</t>
+  </si>
+  <si>
+    <t>EMPFF16E1</t>
+  </si>
+  <si>
+    <t>17679-8564940-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_299B7</t>
+  </si>
+  <si>
+    <t>03692642300</t>
+  </si>
+  <si>
+    <t>EMPA53AAD</t>
+  </si>
+  <si>
+    <t>26476-9396680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_557B1</t>
+  </si>
+  <si>
+    <t>03698456500</t>
+  </si>
+  <si>
+    <t>EMP0E208A</t>
+  </si>
+  <si>
+    <t>26476-9916560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CC022</t>
+  </si>
+  <si>
+    <t>03699983100</t>
+  </si>
+  <si>
+    <t>EMP849C8A</t>
+  </si>
+  <si>
+    <t>26477-0050860-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6EBE0</t>
+  </si>
+  <si>
+    <t>03700971200</t>
+  </si>
+  <si>
+    <t>EMP00B7BE</t>
+  </si>
+  <si>
+    <t>26477-0148790-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1FE92</t>
+  </si>
+  <si>
+    <t>03702026200</t>
+  </si>
+  <si>
+    <t>EMPCEA6E9</t>
+  </si>
+  <si>
+    <t>26477-0257570-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_40D6F</t>
+  </si>
+  <si>
+    <t>03897412800</t>
+  </si>
+  <si>
+    <t>EMP720C76</t>
+  </si>
+  <si>
+    <t>29378-9847360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A454D</t>
+  </si>
+  <si>
+    <t>03905516100</t>
+  </si>
+  <si>
+    <t>EMP2242F5</t>
+  </si>
+  <si>
+    <t>29379-0611850-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F6A91</t>
+  </si>
+  <si>
+    <t>03906740100</t>
+  </si>
+  <si>
+    <t>EMPF1B79B</t>
+  </si>
+  <si>
+    <t>29379-0731470-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_13DB3</t>
+  </si>
+  <si>
+    <t>03907874600</t>
+  </si>
+  <si>
+    <t>EMP1C7BB6</t>
+  </si>
+  <si>
+    <t>29379-0839710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2F18F</t>
+  </si>
+  <si>
+    <t>03908908400</t>
+  </si>
+  <si>
+    <t>EMPD943F9</t>
+  </si>
+  <si>
+    <t>29379-0995960-0</t>
   </si>
 </sst>
 </file>
@@ -6390,16 +7350,16 @@
         <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>1952</v>
+        <v>2272</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>1953</v>
+        <v>2273</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>1954</v>
+        <v>2274</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -6459,7 +7419,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1955</v>
+        <v>2275</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -6485,16 +7445,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>1956</v>
+        <v>2276</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>1957</v>
+        <v>2277</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>1958</v>
+        <v>2278</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -6554,7 +7514,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>1959</v>
+        <v>2279</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -6580,16 +7540,16 @@
         <v>56</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>1960</v>
+        <v>2280</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>1961</v>
+        <v>2281</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>1962</v>
+        <v>2282</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -6649,7 +7609,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>1963</v>
+        <v>2283</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -6675,16 +7635,16 @@
         <v>60</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>1964</v>
+        <v>2284</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>1965</v>
+        <v>2285</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>1966</v>
+        <v>2286</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -6744,7 +7704,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>1967</v>
+        <v>2287</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -6770,16 +7730,16 @@
         <v>62</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>1968</v>
+        <v>2288</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>1969</v>
+        <v>2289</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>1970</v>
+        <v>2290</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -6839,7 +7799,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1971</v>
+        <v>2291</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>

--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="2292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4820" uniqueCount="4725">
   <si>
     <t>DT Code*</t>
   </si>
@@ -6895,6 +6895,7305 @@
   </si>
   <si>
     <t>29379-0995960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6ABAB</t>
+  </si>
+  <si>
+    <t>03535182500</t>
+  </si>
+  <si>
+    <t>EMP870D74</t>
+  </si>
+  <si>
+    <t>44175-3613640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D7A5D</t>
+  </si>
+  <si>
+    <t>03541494200</t>
+  </si>
+  <si>
+    <t>EMP1CF911</t>
+  </si>
+  <si>
+    <t>44175-4208760-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F0092</t>
+  </si>
+  <si>
+    <t>03542679100</t>
+  </si>
+  <si>
+    <t>EMP21E1AB</t>
+  </si>
+  <si>
+    <t>44175-4324140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0B27B</t>
+  </si>
+  <si>
+    <t>03543725200</t>
+  </si>
+  <si>
+    <t>EMPA869ED</t>
+  </si>
+  <si>
+    <t>44175-4425210-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_88779</t>
+  </si>
+  <si>
+    <t>03544695000</t>
+  </si>
+  <si>
+    <t>EMPE1D9F1</t>
+  </si>
+  <si>
+    <t>44175-4502020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB4D7</t>
+  </si>
+  <si>
+    <t>03647795700</t>
+  </si>
+  <si>
+    <t>EMPE43B72</t>
+  </si>
+  <si>
+    <t>46956-4878450-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A3F4A</t>
+  </si>
+  <si>
+    <t>03653654900</t>
+  </si>
+  <si>
+    <t>EMP36DD4E</t>
+  </si>
+  <si>
+    <t>46956-5438590-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA32D</t>
+  </si>
+  <si>
+    <t>03654950100</t>
+  </si>
+  <si>
+    <t>EMPDAB7C1</t>
+  </si>
+  <si>
+    <t>46956-5536970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8EB3E</t>
+  </si>
+  <si>
+    <t>03655882200</t>
+  </si>
+  <si>
+    <t>EMP9DC621</t>
+  </si>
+  <si>
+    <t>46956-5650300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B322F</t>
+  </si>
+  <si>
+    <t>03657012700</t>
+  </si>
+  <si>
+    <t>EMP5CFE90</t>
+  </si>
+  <si>
+    <t>46956-5745020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_38CDD</t>
+  </si>
+  <si>
+    <t>03527168900</t>
+  </si>
+  <si>
+    <t>EMP3EDDB8</t>
+  </si>
+  <si>
+    <t>48215-2841660-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB7C7</t>
+  </si>
+  <si>
+    <t>03532625900</t>
+  </si>
+  <si>
+    <t>EMP8DF7B1</t>
+  </si>
+  <si>
+    <t>48215-3323880-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2E4FB</t>
+  </si>
+  <si>
+    <t>03533807000</t>
+  </si>
+  <si>
+    <t>EMPB369C4</t>
+  </si>
+  <si>
+    <t>48215-4107060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6E7C6</t>
+  </si>
+  <si>
+    <t>03541607400</t>
+  </si>
+  <si>
+    <t>EMP16AB22</t>
+  </si>
+  <si>
+    <t>48215-4209750-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_43967</t>
+  </si>
+  <si>
+    <t>03542563500</t>
+  </si>
+  <si>
+    <t>EMPEA7E4F</t>
+  </si>
+  <si>
+    <t>48215-4306870-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B01FD</t>
+  </si>
+  <si>
+    <t>03877795100</t>
+  </si>
+  <si>
+    <t>EMP71BE3E</t>
+  </si>
+  <si>
+    <t>51258-7878360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4FA50</t>
+  </si>
+  <si>
+    <t>03883205900</t>
+  </si>
+  <si>
+    <t>EMPEB3DD8</t>
+  </si>
+  <si>
+    <t>51258-8391550-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA115</t>
+  </si>
+  <si>
+    <t>03884655100</t>
+  </si>
+  <si>
+    <t>EMP945F5C</t>
+  </si>
+  <si>
+    <t>51258-8532680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_33099</t>
+  </si>
+  <si>
+    <t>03886160800</t>
+  </si>
+  <si>
+    <t>EMPCCFD2E</t>
+  </si>
+  <si>
+    <t>51258-8664590-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_19E85</t>
+  </si>
+  <si>
+    <t>03887093200</t>
+  </si>
+  <si>
+    <t>EMP032315</t>
+  </si>
+  <si>
+    <t>51258-8769090-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C2D42</t>
+  </si>
+  <si>
+    <t>03653055600</t>
+  </si>
+  <si>
+    <t>EMP630E5F</t>
+  </si>
+  <si>
+    <t>52386-5594220-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_58089</t>
+  </si>
+  <si>
+    <t>03660338700</t>
+  </si>
+  <si>
+    <t>EMP0E6A1E</t>
+  </si>
+  <si>
+    <t>52386-6116790-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_54F49</t>
+  </si>
+  <si>
+    <t>03661612500</t>
+  </si>
+  <si>
+    <t>EMP613C70</t>
+  </si>
+  <si>
+    <t>52386-6204120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1ADE3</t>
+  </si>
+  <si>
+    <t>03662721700</t>
+  </si>
+  <si>
+    <t>EMP6F2E3B</t>
+  </si>
+  <si>
+    <t>52386-6356440-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_87893</t>
+  </si>
+  <si>
+    <t>03664419900</t>
+  </si>
+  <si>
+    <t>EMP2D27B3</t>
+  </si>
+  <si>
+    <t>52386-6506270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_56237</t>
+  </si>
+  <si>
+    <t>03092821500</t>
+  </si>
+  <si>
+    <t>EMPCA3DAB</t>
+  </si>
+  <si>
+    <t>53990-9410700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_40BD9</t>
+  </si>
+  <si>
+    <t>03095033300</t>
+  </si>
+  <si>
+    <t>EMP6CA514</t>
+  </si>
+  <si>
+    <t>53990-9581010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6FC87</t>
+  </si>
+  <si>
+    <t>03096411100</t>
+  </si>
+  <si>
+    <t>EMP01905A</t>
+  </si>
+  <si>
+    <t>53990-9738030-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FDD55</t>
+  </si>
+  <si>
+    <t>03097960600</t>
+  </si>
+  <si>
+    <t>EMP55240E</t>
+  </si>
+  <si>
+    <t>53990-9855640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FC744</t>
+  </si>
+  <si>
+    <t>03099369100</t>
+  </si>
+  <si>
+    <t>EMP29FB98</t>
+  </si>
+  <si>
+    <t>53991-0012420-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9F1AC</t>
+  </si>
+  <si>
+    <t>03879431900</t>
+  </si>
+  <si>
+    <t>EMP43A2BF</t>
+  </si>
+  <si>
+    <t>56098-8079190-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5CD2D</t>
+  </si>
+  <si>
+    <t>03886116800</t>
+  </si>
+  <si>
+    <t>EMP6E3DF2</t>
+  </si>
+  <si>
+    <t>56098-8671370-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8263D</t>
+  </si>
+  <si>
+    <t>03887242200</t>
+  </si>
+  <si>
+    <t>EMP770C5C</t>
+  </si>
+  <si>
+    <t>56098-8828650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FDBB7</t>
+  </si>
+  <si>
+    <t>03889084100</t>
+  </si>
+  <si>
+    <t>EMP74AAE4</t>
+  </si>
+  <si>
+    <t>56098-8985780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_70A55</t>
+  </si>
+  <si>
+    <t>03890943800</t>
+  </si>
+  <si>
+    <t>EMPBB2F12</t>
+  </si>
+  <si>
+    <t>56098-9171100-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DE307</t>
+  </si>
+  <si>
+    <t>03862119400</t>
+  </si>
+  <si>
+    <t>EMPB1E677</t>
+  </si>
+  <si>
+    <t>48078-6323200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C2E95</t>
+  </si>
+  <si>
+    <t>03869586700</t>
+  </si>
+  <si>
+    <t>EMPBECDE5</t>
+  </si>
+  <si>
+    <t>48078-7047520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_20B98</t>
+  </si>
+  <si>
+    <t>03871313600</t>
+  </si>
+  <si>
+    <t>EMPCEFA50</t>
+  </si>
+  <si>
+    <t>48078-7200130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_859AF</t>
+  </si>
+  <si>
+    <t>03872471900</t>
+  </si>
+  <si>
+    <t>EMP0115ED</t>
+  </si>
+  <si>
+    <t>48078-7342210-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F87B1</t>
+  </si>
+  <si>
+    <t>03874282100</t>
+  </si>
+  <si>
+    <t>EMP1F69AE</t>
+  </si>
+  <si>
+    <t>48078-7504710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4D80E</t>
+  </si>
+  <si>
+    <t>03878131000</t>
+  </si>
+  <si>
+    <t>EMPDC4EED</t>
+  </si>
+  <si>
+    <t>54068-7932720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FE8B5</t>
+  </si>
+  <si>
+    <t>03884836500</t>
+  </si>
+  <si>
+    <t>EMP6E049A</t>
+  </si>
+  <si>
+    <t>54068-8554030-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_053CB</t>
+  </si>
+  <si>
+    <t>03886321800</t>
+  </si>
+  <si>
+    <t>EMPDF89DD</t>
+  </si>
+  <si>
+    <t>54068-8693920-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B5A34</t>
+  </si>
+  <si>
+    <t>03887556500</t>
+  </si>
+  <si>
+    <t>EMP763E82</t>
+  </si>
+  <si>
+    <t>54068-8808710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6777B</t>
+  </si>
+  <si>
+    <t>03888629800</t>
+  </si>
+  <si>
+    <t>EMP970590</t>
+  </si>
+  <si>
+    <t>54068-8931640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_09133</t>
+  </si>
+  <si>
+    <t>03531542500</t>
+  </si>
+  <si>
+    <t>EMP15CDAD</t>
+  </si>
+  <si>
+    <t>57235-3318450-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_655CB</t>
+  </si>
+  <si>
+    <t>03537662100</t>
+  </si>
+  <si>
+    <t>EMP133D56</t>
+  </si>
+  <si>
+    <t>57235-3828160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BB40B</t>
+  </si>
+  <si>
+    <t>03538826000</t>
+  </si>
+  <si>
+    <t>EMPFAD313</t>
+  </si>
+  <si>
+    <t>57235-3931640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_70EA4</t>
+  </si>
+  <si>
+    <t>03539828000</t>
+  </si>
+  <si>
+    <t>EMPD5E9C5</t>
+  </si>
+  <si>
+    <t>57235-4036510-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A9B13</t>
+  </si>
+  <si>
+    <t>03540951200</t>
+  </si>
+  <si>
+    <t>EMPD1B1C3</t>
+  </si>
+  <si>
+    <t>57235-4134430-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_446BA</t>
+  </si>
+  <si>
+    <t>03739190000</t>
+  </si>
+  <si>
+    <t>EMP50CE00</t>
+  </si>
+  <si>
+    <t>58957-4074080-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C10DF</t>
+  </si>
+  <si>
+    <t>03747076000</t>
+  </si>
+  <si>
+    <t>EMP4BE6CE</t>
+  </si>
+  <si>
+    <t>58957-4911080-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D5BBE</t>
+  </si>
+  <si>
+    <t>03751193200</t>
+  </si>
+  <si>
+    <t>EMPAE706A</t>
+  </si>
+  <si>
+    <t>58957-5341910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E1359</t>
+  </si>
+  <si>
+    <t>03754639100</t>
+  </si>
+  <si>
+    <t>EMP9F76CD</t>
+  </si>
+  <si>
+    <t>58957-5538620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EE859</t>
+  </si>
+  <si>
+    <t>03756095200</t>
+  </si>
+  <si>
+    <t>EMPF36B29</t>
+  </si>
+  <si>
+    <t>58957-5661590-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7D2D9</t>
+  </si>
+  <si>
+    <t>03028149700</t>
+  </si>
+  <si>
+    <t>EMP15EB79</t>
+  </si>
+  <si>
+    <t>61790-2941490-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DEA58</t>
+  </si>
+  <si>
+    <t>03033818200</t>
+  </si>
+  <si>
+    <t>EMPC18CB7</t>
+  </si>
+  <si>
+    <t>61790-3522660-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_42DF7</t>
+  </si>
+  <si>
+    <t>03036177200</t>
+  </si>
+  <si>
+    <t>EMPFD8AA1</t>
+  </si>
+  <si>
+    <t>61790-3669300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_577D6</t>
+  </si>
+  <si>
+    <t>03037154300</t>
+  </si>
+  <si>
+    <t>EMPD6CD27</t>
+  </si>
+  <si>
+    <t>61790-3772680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6671A</t>
+  </si>
+  <si>
+    <t>03038616800</t>
+  </si>
+  <si>
+    <t>EMP5EF14A</t>
+  </si>
+  <si>
+    <t>61790-3937950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_738FE</t>
+  </si>
+  <si>
+    <t>03600265300</t>
+  </si>
+  <si>
+    <t>EMP673D45</t>
+  </si>
+  <si>
+    <t>65886-0150380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D104A</t>
+  </si>
+  <si>
+    <t>03605975400</t>
+  </si>
+  <si>
+    <t>EMP138F70</t>
+  </si>
+  <si>
+    <t>65886-0661400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2B29A</t>
+  </si>
+  <si>
+    <t>03607339300</t>
+  </si>
+  <si>
+    <t>EMP4B607B</t>
+  </si>
+  <si>
+    <t>65886-0821560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E3C11</t>
+  </si>
+  <si>
+    <t>03608896400</t>
+  </si>
+  <si>
+    <t>EMP5DA6D3</t>
+  </si>
+  <si>
+    <t>65886-0951520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2F120</t>
+  </si>
+  <si>
+    <t>03610289900</t>
+  </si>
+  <si>
+    <t>EMPE3A4D8</t>
+  </si>
+  <si>
+    <t>65886-1102830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_97112</t>
+  </si>
+  <si>
+    <t>03470320400</t>
+  </si>
+  <si>
+    <t>EMP0FDB91</t>
+  </si>
+  <si>
+    <t>68524-7173820-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D5FE7</t>
+  </si>
+  <si>
+    <t>03476218200</t>
+  </si>
+  <si>
+    <t>EMP4148EE</t>
+  </si>
+  <si>
+    <t>68524-7696250-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_72DA6</t>
+  </si>
+  <si>
+    <t>03477465300</t>
+  </si>
+  <si>
+    <t>EMPF11B1F</t>
+  </si>
+  <si>
+    <t>68524-7784140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D75D5</t>
+  </si>
+  <si>
+    <t>03478274800</t>
+  </si>
+  <si>
+    <t>EMP940B84</t>
+  </si>
+  <si>
+    <t>68524-7863840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FCEC4</t>
+  </si>
+  <si>
+    <t>03478971900</t>
+  </si>
+  <si>
+    <t>EMP500C0B</t>
+  </si>
+  <si>
+    <t>68524-7929890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_063C3</t>
+  </si>
+  <si>
+    <t>03521139100</t>
+  </si>
+  <si>
+    <t>EMP467128</t>
+  </si>
+  <si>
+    <t>79185-2229650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D6063</t>
+  </si>
+  <si>
+    <t>03526401800</t>
+  </si>
+  <si>
+    <t>EMP17FA06</t>
+  </si>
+  <si>
+    <t>79185-2705400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FFDAE</t>
+  </si>
+  <si>
+    <t>03527657600</t>
+  </si>
+  <si>
+    <t>EMPB77CEA</t>
+  </si>
+  <si>
+    <t>79185-2832440-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D6996</t>
+  </si>
+  <si>
+    <t>03528985300</t>
+  </si>
+  <si>
+    <t>EMP8E450C</t>
+  </si>
+  <si>
+    <t>79185-2955000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E3CFA</t>
+  </si>
+  <si>
+    <t>03530162700</t>
+  </si>
+  <si>
+    <t>EMPD4E2C5</t>
+  </si>
+  <si>
+    <t>79185-3086810-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_161EB</t>
+  </si>
+  <si>
+    <t>03640038900</t>
+  </si>
+  <si>
+    <t>EMPBE1BA1</t>
+  </si>
+  <si>
+    <t>80826-4136910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F6D0F</t>
+  </si>
+  <si>
+    <t>03647180800</t>
+  </si>
+  <si>
+    <t>EMP475720</t>
+  </si>
+  <si>
+    <t>80826-4778690-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2A62D</t>
+  </si>
+  <si>
+    <t>03648413100</t>
+  </si>
+  <si>
+    <t>EMPD841DF</t>
+  </si>
+  <si>
+    <t>80826-4910000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FE957</t>
+  </si>
+  <si>
+    <t>03649722500</t>
+  </si>
+  <si>
+    <t>EMP5307CF</t>
+  </si>
+  <si>
+    <t>80826-5030160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_92168</t>
+  </si>
+  <si>
+    <t>03651058200</t>
+  </si>
+  <si>
+    <t>EMP5E3F95</t>
+  </si>
+  <si>
+    <t>80826-5165320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BDC47</t>
+  </si>
+  <si>
+    <t>03963406200</t>
+  </si>
+  <si>
+    <t>EMP64B8EA</t>
+  </si>
+  <si>
+    <t>88019-6458840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1E666</t>
+  </si>
+  <si>
+    <t>03968959000</t>
+  </si>
+  <si>
+    <t>EMP6EAAFF</t>
+  </si>
+  <si>
+    <t>88019-7083700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6C01E</t>
+  </si>
+  <si>
+    <t>03972847300</t>
+  </si>
+  <si>
+    <t>EMP433134</t>
+  </si>
+  <si>
+    <t>88019-7366970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9CB02</t>
+  </si>
+  <si>
+    <t>03974326900</t>
+  </si>
+  <si>
+    <t>EMP8044C0</t>
+  </si>
+  <si>
+    <t>88019-7499650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6281A</t>
+  </si>
+  <si>
+    <t>03975568700</t>
+  </si>
+  <si>
+    <t>EMP2A3E73</t>
+  </si>
+  <si>
+    <t>88019-7595060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_917F4</t>
+  </si>
+  <si>
+    <t>03177962500</t>
+  </si>
+  <si>
+    <t>EMPBB5D66</t>
+  </si>
+  <si>
+    <t>04141-7924340-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DC1D2</t>
+  </si>
+  <si>
+    <t>03184066600</t>
+  </si>
+  <si>
+    <t>EMPA6C0D9</t>
+  </si>
+  <si>
+    <t>04141-8480980-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA3AE</t>
+  </si>
+  <si>
+    <t>03191957600</t>
+  </si>
+  <si>
+    <t>EMP67C3DA</t>
+  </si>
+  <si>
+    <t>04141-9261330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A0E3D</t>
+  </si>
+  <si>
+    <t>03193347500</t>
+  </si>
+  <si>
+    <t>EMP2DEB2B</t>
+  </si>
+  <si>
+    <t>04141-9395140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9FC72</t>
+  </si>
+  <si>
+    <t>03194544200</t>
+  </si>
+  <si>
+    <t>EMPCC70D7</t>
+  </si>
+  <si>
+    <t>04141-9492060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A0DEA</t>
+  </si>
+  <si>
+    <t>03736539700</t>
+  </si>
+  <si>
+    <t>EMP97740B</t>
+  </si>
+  <si>
+    <t>15157-3780320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_058A3</t>
+  </si>
+  <si>
+    <t>03743159800</t>
+  </si>
+  <si>
+    <t>EMP02C17F</t>
+  </si>
+  <si>
+    <t>15157-4392330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_98D42</t>
+  </si>
+  <si>
+    <t>03744693600</t>
+  </si>
+  <si>
+    <t>EMP809026</t>
+  </si>
+  <si>
+    <t>15157-4541630-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6B5ED</t>
+  </si>
+  <si>
+    <t>03746227600</t>
+  </si>
+  <si>
+    <t>EMPF1E4BF</t>
+  </si>
+  <si>
+    <t>15157-4683630-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_60905</t>
+  </si>
+  <si>
+    <t>03747464400</t>
+  </si>
+  <si>
+    <t>EMP5CD6E8</t>
+  </si>
+  <si>
+    <t>15157-4816620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6A7E7</t>
+  </si>
+  <si>
+    <t>03796712900</t>
+  </si>
+  <si>
+    <t>EMPBC3DDD</t>
+  </si>
+  <si>
+    <t>16337-9809480-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A29FA</t>
+  </si>
+  <si>
+    <t>03802766800</t>
+  </si>
+  <si>
+    <t>EMP5EFF66</t>
+  </si>
+  <si>
+    <t>16338-0339360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_42A0E</t>
+  </si>
+  <si>
+    <t>03804055500</t>
+  </si>
+  <si>
+    <t>EMP208F58</t>
+  </si>
+  <si>
+    <t>16338-0466190-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C2627</t>
+  </si>
+  <si>
+    <t>03805372700</t>
+  </si>
+  <si>
+    <t>EMP91DC67</t>
+  </si>
+  <si>
+    <t>16338-0602570-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F6143</t>
+  </si>
+  <si>
+    <t>03806517500</t>
+  </si>
+  <si>
+    <t>EMPA32FAE</t>
+  </si>
+  <si>
+    <t>16338-0688830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7FAB3</t>
+  </si>
+  <si>
+    <t>03838808200</t>
+  </si>
+  <si>
+    <t>EMP14D9A1</t>
+  </si>
+  <si>
+    <t>19968-3983500-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A9E92</t>
+  </si>
+  <si>
+    <t>03844257400</t>
+  </si>
+  <si>
+    <t>EMPE0C4C6</t>
+  </si>
+  <si>
+    <t>19968-4491310-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_78966</t>
+  </si>
+  <si>
+    <t>03845483600</t>
+  </si>
+  <si>
+    <t>EMP8092E5</t>
+  </si>
+  <si>
+    <t>19968-4601940-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DFA10</t>
+  </si>
+  <si>
+    <t>03846657400</t>
+  </si>
+  <si>
+    <t>EMP7FB909</t>
+  </si>
+  <si>
+    <t>19968-4714910-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8C98C</t>
+  </si>
+  <si>
+    <t>03847604600</t>
+  </si>
+  <si>
+    <t>EMP7BAB9B</t>
+  </si>
+  <si>
+    <t>19968-4829090-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_106C5</t>
+  </si>
+  <si>
+    <t>03691778800</t>
+  </si>
+  <si>
+    <t>EMP6EA63F</t>
+  </si>
+  <si>
+    <t>21826-9298810-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B85E</t>
+  </si>
+  <si>
+    <t>03697921400</t>
+  </si>
+  <si>
+    <t>EMPF5827D</t>
+  </si>
+  <si>
+    <t>21826-9876660-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EA7D2</t>
+  </si>
+  <si>
+    <t>03699733300</t>
+  </si>
+  <si>
+    <t>EMP87FC89</t>
+  </si>
+  <si>
+    <t>21827-0038980-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_318D2</t>
+  </si>
+  <si>
+    <t>03700854600</t>
+  </si>
+  <si>
+    <t>EMPA6CABB</t>
+  </si>
+  <si>
+    <t>21827-0131290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D4E66</t>
+  </si>
+  <si>
+    <t>03701800800</t>
+  </si>
+  <si>
+    <t>EMPC3945D</t>
+  </si>
+  <si>
+    <t>21827-0274660-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E6530</t>
+  </si>
+  <si>
+    <t>03805549100</t>
+  </si>
+  <si>
+    <t>EMPCD43CB</t>
+  </si>
+  <si>
+    <t>24628-0663200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EB647</t>
+  </si>
+  <si>
+    <t>03811024800</t>
+  </si>
+  <si>
+    <t>EMPEE2D76</t>
+  </si>
+  <si>
+    <t>24628-1146770-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_11C50</t>
+  </si>
+  <si>
+    <t>03811896000</t>
+  </si>
+  <si>
+    <t>EMP80A00C</t>
+  </si>
+  <si>
+    <t>24628-1254500-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_39E90</t>
+  </si>
+  <si>
+    <t>03813110100</t>
+  </si>
+  <si>
+    <t>EMP03D6A1</t>
+  </si>
+  <si>
+    <t>24628-1362450-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_070AA</t>
+  </si>
+  <si>
+    <t>03814200300</t>
+  </si>
+  <si>
+    <t>EMP47B1F8</t>
+  </si>
+  <si>
+    <t>24628-1496650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8CADA</t>
+  </si>
+  <si>
+    <t>03066365600</t>
+  </si>
+  <si>
+    <t>EMP027B55</t>
+  </si>
+  <si>
+    <t>26860-6770850-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_30FE8</t>
+  </si>
+  <si>
+    <t>03072107800</t>
+  </si>
+  <si>
+    <t>EMP60FC05</t>
+  </si>
+  <si>
+    <t>26860-7301000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4D31E</t>
+  </si>
+  <si>
+    <t>03073932900</t>
+  </si>
+  <si>
+    <t>EMPBD953B</t>
+  </si>
+  <si>
+    <t>26860-7450010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7ED44</t>
+  </si>
+  <si>
+    <t>03075335800</t>
+  </si>
+  <si>
+    <t>EMPADCD92</t>
+  </si>
+  <si>
+    <t>26860-7597670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F74DE</t>
+  </si>
+  <si>
+    <t>03076614700</t>
+  </si>
+  <si>
+    <t>EMP636D68</t>
+  </si>
+  <si>
+    <t>26860-7751670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A4CAC</t>
+  </si>
+  <si>
+    <t>03681624000</t>
+  </si>
+  <si>
+    <t>EMP15F30B</t>
+  </si>
+  <si>
+    <t>28426-8272390-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_ABF06</t>
+  </si>
+  <si>
+    <t>03687304400</t>
+  </si>
+  <si>
+    <t>EMPBACC68</t>
+  </si>
+  <si>
+    <t>28426-8812590-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5EE8A</t>
+  </si>
+  <si>
+    <t>03688639600</t>
+  </si>
+  <si>
+    <t>EMPDA5B47</t>
+  </si>
+  <si>
+    <t>28426-8903700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1590E</t>
+  </si>
+  <si>
+    <t>03689464000</t>
+  </si>
+  <si>
+    <t>EMPD268C3</t>
+  </si>
+  <si>
+    <t>28426-8983120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BB31F</t>
+  </si>
+  <si>
+    <t>03690187900</t>
+  </si>
+  <si>
+    <t>EMPE7BDC0</t>
+  </si>
+  <si>
+    <t>28426-9068710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FB2FD</t>
+  </si>
+  <si>
+    <t>03151589900</t>
+  </si>
+  <si>
+    <t>EMPCF6D4A</t>
+  </si>
+  <si>
+    <t>33251-5306150-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_37EF2</t>
+  </si>
+  <si>
+    <t>03157314900</t>
+  </si>
+  <si>
+    <t>EMPC7646C</t>
+  </si>
+  <si>
+    <t>33251-5792360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_82FD1</t>
+  </si>
+  <si>
+    <t>03158524500</t>
+  </si>
+  <si>
+    <t>EMPEB8AB9</t>
+  </si>
+  <si>
+    <t>33251-5904980-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F8171</t>
+  </si>
+  <si>
+    <t>03159558200</t>
+  </si>
+  <si>
+    <t>EMPE11DE7</t>
+  </si>
+  <si>
+    <t>33251-5999650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_31798</t>
+  </si>
+  <si>
+    <t>03160476700</t>
+  </si>
+  <si>
+    <t>EMP8E5BCC</t>
+  </si>
+  <si>
+    <t>33251-6125130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_920EB</t>
+  </si>
+  <si>
+    <t>03126823300</t>
+  </si>
+  <si>
+    <t>EMP0AF75A</t>
+  </si>
+  <si>
+    <t>36891-2815120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5F45E</t>
+  </si>
+  <si>
+    <t>03137544800</t>
+  </si>
+  <si>
+    <t>EMP9AFE0E</t>
+  </si>
+  <si>
+    <t>36891-3832010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_03743</t>
+  </si>
+  <si>
+    <t>03138954500</t>
+  </si>
+  <si>
+    <t>EMP98E40D</t>
+  </si>
+  <si>
+    <t>36891-3933330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2A645</t>
+  </si>
+  <si>
+    <t>03139863800</t>
+  </si>
+  <si>
+    <t>EMPA646AC</t>
+  </si>
+  <si>
+    <t>36891-4048870-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CFBFB</t>
+  </si>
+  <si>
+    <t>03141149000</t>
+  </si>
+  <si>
+    <t>EMP8C565C</t>
+  </si>
+  <si>
+    <t>36891-4206650-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E0467</t>
+  </si>
+  <si>
+    <t>03666317800</t>
+  </si>
+  <si>
+    <t>EMP2AD3D2</t>
+  </si>
+  <si>
+    <t>48256-6734600-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F8BC9</t>
+  </si>
+  <si>
+    <t>03672141800</t>
+  </si>
+  <si>
+    <t>EMP5C3C3B</t>
+  </si>
+  <si>
+    <t>48256-7282380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A34DE</t>
+  </si>
+  <si>
+    <t>03673452300</t>
+  </si>
+  <si>
+    <t>EMP30F16B</t>
+  </si>
+  <si>
+    <t>48256-7395370-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CECD6</t>
+  </si>
+  <si>
+    <t>03674559200</t>
+  </si>
+  <si>
+    <t>EMPB5CA36</t>
+  </si>
+  <si>
+    <t>48256-7505350-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_74E2E</t>
+  </si>
+  <si>
+    <t>03675524900</t>
+  </si>
+  <si>
+    <t>EMPF29857</t>
+  </si>
+  <si>
+    <t>48256-7604300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_04F21</t>
+  </si>
+  <si>
+    <t>03250109900</t>
+  </si>
+  <si>
+    <t>EMP9F13F6</t>
+  </si>
+  <si>
+    <t>51572-5133600-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9CF34</t>
+  </si>
+  <si>
+    <t>03255686300</t>
+  </si>
+  <si>
+    <t>EMP4E7B62</t>
+  </si>
+  <si>
+    <t>51572-5624000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5B338</t>
+  </si>
+  <si>
+    <t>03256783800</t>
+  </si>
+  <si>
+    <t>EMP095518</t>
+  </si>
+  <si>
+    <t>51572-5727480-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C8EF7</t>
+  </si>
+  <si>
+    <t>03257908900</t>
+  </si>
+  <si>
+    <t>EMPBE69FF</t>
+  </si>
+  <si>
+    <t>51572-5846890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D624F</t>
+  </si>
+  <si>
+    <t>03259059000</t>
+  </si>
+  <si>
+    <t>EMP7D7FC5</t>
+  </si>
+  <si>
+    <t>51572-5964550-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A3EF2</t>
+  </si>
+  <si>
+    <t>03786702900</t>
+  </si>
+  <si>
+    <t>EMPFFF067</t>
+  </si>
+  <si>
+    <t>53777-8777730-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4D64E</t>
+  </si>
+  <si>
+    <t>03794304000</t>
+  </si>
+  <si>
+    <t>EMP17BBCD</t>
+  </si>
+  <si>
+    <t>53777-9493230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1FE3C</t>
+  </si>
+  <si>
+    <t>03795703300</t>
+  </si>
+  <si>
+    <t>EMP0D36D2</t>
+  </si>
+  <si>
+    <t>53777-9615820-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AD20F</t>
+  </si>
+  <si>
+    <t>03796757300</t>
+  </si>
+  <si>
+    <t>EMPAE3BCD</t>
+  </si>
+  <si>
+    <t>53777-9749710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_02466</t>
+  </si>
+  <si>
+    <t>03798004100</t>
+  </si>
+  <si>
+    <t>EMP16C811</t>
+  </si>
+  <si>
+    <t>53777-9836850-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D2F11</t>
+  </si>
+  <si>
+    <t>03062036900</t>
+  </si>
+  <si>
+    <t>EMPCD2EF1</t>
+  </si>
+  <si>
+    <t>54910-6341280-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C649A</t>
+  </si>
+  <si>
+    <t>03067463200</t>
+  </si>
+  <si>
+    <t>EMP329FA2</t>
+  </si>
+  <si>
+    <t>54910-6839970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_17447</t>
+  </si>
+  <si>
+    <t>03069090700</t>
+  </si>
+  <si>
+    <t>EMP39C0C0</t>
+  </si>
+  <si>
+    <t>54910-6979140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EB797</t>
+  </si>
+  <si>
+    <t>03070322300</t>
+  </si>
+  <si>
+    <t>EMP2EF710</t>
+  </si>
+  <si>
+    <t>54910-7082060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6B9F2</t>
+  </si>
+  <si>
+    <t>03071636100</t>
+  </si>
+  <si>
+    <t>EMP9CA0A7</t>
+  </si>
+  <si>
+    <t>54910-7234000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_97B8C</t>
+  </si>
+  <si>
+    <t>03189345000</t>
+  </si>
+  <si>
+    <t>EMP71C560</t>
+  </si>
+  <si>
+    <t>94171-9058460-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CD45B</t>
+  </si>
+  <si>
+    <t>03191465400</t>
+  </si>
+  <si>
+    <t>EMP5611CA</t>
+  </si>
+  <si>
+    <t>94171-9197310-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A1BBC</t>
+  </si>
+  <si>
+    <t>03192452300</t>
+  </si>
+  <si>
+    <t>EMPF0EDFD</t>
+  </si>
+  <si>
+    <t>94171-9295500-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9181D</t>
+  </si>
+  <si>
+    <t>03193499100</t>
+  </si>
+  <si>
+    <t>EMP5FF207</t>
+  </si>
+  <si>
+    <t>94171-9394480-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7B60C</t>
+  </si>
+  <si>
+    <t>03194534000</t>
+  </si>
+  <si>
+    <t>EMP5F47D5</t>
+  </si>
+  <si>
+    <t>94171-9508270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4536E</t>
+  </si>
+  <si>
+    <t>03646904400</t>
+  </si>
+  <si>
+    <t>EMP9D3001</t>
+  </si>
+  <si>
+    <t>98866-4805400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DEE54</t>
+  </si>
+  <si>
+    <t>03652380700</t>
+  </si>
+  <si>
+    <t>EMPB19685</t>
+  </si>
+  <si>
+    <t>98866-5317610-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CCA57</t>
+  </si>
+  <si>
+    <t>03654260500</t>
+  </si>
+  <si>
+    <t>EMP259B7C</t>
+  </si>
+  <si>
+    <t>98866-5493190-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CB371</t>
+  </si>
+  <si>
+    <t>03655487500</t>
+  </si>
+  <si>
+    <t>EMP1AF22E</t>
+  </si>
+  <si>
+    <t>98866-5631260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8CF64</t>
+  </si>
+  <si>
+    <t>03657002900</t>
+  </si>
+  <si>
+    <t>EMPA90D54</t>
+  </si>
+  <si>
+    <t>98866-5789200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_62305</t>
+  </si>
+  <si>
+    <t>03504405400</t>
+  </si>
+  <si>
+    <t>EMP2284F9</t>
+  </si>
+  <si>
+    <t>04125-0562750-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_361F8</t>
+  </si>
+  <si>
+    <t>03509993700</t>
+  </si>
+  <si>
+    <t>EMPFDD840</t>
+  </si>
+  <si>
+    <t>04125-1068760-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C6670</t>
+  </si>
+  <si>
+    <t>03511326400</t>
+  </si>
+  <si>
+    <t>EMPA3B68A</t>
+  </si>
+  <si>
+    <t>04125-1193280-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_973C4</t>
+  </si>
+  <si>
+    <t>03512611900</t>
+  </si>
+  <si>
+    <t>EMPDEE7D5</t>
+  </si>
+  <si>
+    <t>04125-1317940-0</t>
+  </si>
+  <si>
+    <t>03513702400</t>
+  </si>
+  <si>
+    <t>EMP50023A</t>
+  </si>
+  <si>
+    <t>04125-1432090-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6F7D5</t>
+  </si>
+  <si>
+    <t>03743429800</t>
+  </si>
+  <si>
+    <t>EMP3015BE</t>
+  </si>
+  <si>
+    <t>06387-4482640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_89558</t>
+  </si>
+  <si>
+    <t>03746005000</t>
+  </si>
+  <si>
+    <t>EMP96F724</t>
+  </si>
+  <si>
+    <t>06387-4673270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C8215</t>
+  </si>
+  <si>
+    <t>03747322000</t>
+  </si>
+  <si>
+    <t>EMP51285D</t>
+  </si>
+  <si>
+    <t>06387-4785230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A8BAB</t>
+  </si>
+  <si>
+    <t>03748366000</t>
+  </si>
+  <si>
+    <t>EMP7A0A98</t>
+  </si>
+  <si>
+    <t>06387-4888660-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B3D16</t>
+  </si>
+  <si>
+    <t>03749424900</t>
+  </si>
+  <si>
+    <t>EMP57E90C</t>
+  </si>
+  <si>
+    <t>06387-5000830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_062B7</t>
+  </si>
+  <si>
+    <t>03880286900</t>
+  </si>
+  <si>
+    <t>EMP4CD8F9</t>
+  </si>
+  <si>
+    <t>66108-8192840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9C8BB</t>
+  </si>
+  <si>
+    <t>03888432200</t>
+  </si>
+  <si>
+    <t>EMP48A05A</t>
+  </si>
+  <si>
+    <t>66108-8901400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A6D1C</t>
+  </si>
+  <si>
+    <t>03889798800</t>
+  </si>
+  <si>
+    <t>EMP247048</t>
+  </si>
+  <si>
+    <t>66108-9042620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_81902</t>
+  </si>
+  <si>
+    <t>03891132400</t>
+  </si>
+  <si>
+    <t>EMP315C06</t>
+  </si>
+  <si>
+    <t>66108-9191780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E2E10</t>
+  </si>
+  <si>
+    <t>03893427000</t>
+  </si>
+  <si>
+    <t>EMP4C29F8</t>
+  </si>
+  <si>
+    <t>66108-9432840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_55F28</t>
+  </si>
+  <si>
+    <t>03750502400</t>
+  </si>
+  <si>
+    <t>EMP1E865A</t>
+  </si>
+  <si>
+    <t>71427-5266310-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_50163</t>
+  </si>
+  <si>
+    <t>03759200800</t>
+  </si>
+  <si>
+    <t>EMPBE7D5C</t>
+  </si>
+  <si>
+    <t>71427-6023960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7D845</t>
+  </si>
+  <si>
+    <t>03761129200</t>
+  </si>
+  <si>
+    <t>EMP6202A7</t>
+  </si>
+  <si>
+    <t>71427-6182400-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8115B</t>
+  </si>
+  <si>
+    <t>03762664400</t>
+  </si>
+  <si>
+    <t>EMP38CD87</t>
+  </si>
+  <si>
+    <t>71427-6369330-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_77EF4</t>
+  </si>
+  <si>
+    <t>03764961300</t>
+  </si>
+  <si>
+    <t>EMPAF92F9</t>
+  </si>
+  <si>
+    <t>71427-6578170-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1D302</t>
+  </si>
+  <si>
+    <t>03840315700</t>
+  </si>
+  <si>
+    <t>EMPBD77A2</t>
+  </si>
+  <si>
+    <t>77148-4161210-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_98C2C</t>
+  </si>
+  <si>
+    <t>03849285900</t>
+  </si>
+  <si>
+    <t>EMP1EE349</t>
+  </si>
+  <si>
+    <t>77148-4985010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8EE20</t>
+  </si>
+  <si>
+    <t>03850237300</t>
+  </si>
+  <si>
+    <t>EMP2A96FB</t>
+  </si>
+  <si>
+    <t>77148-5061040-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_43E47</t>
+  </si>
+  <si>
+    <t>03851146900</t>
+  </si>
+  <si>
+    <t>EMP45CAF6</t>
+  </si>
+  <si>
+    <t>77148-5168110-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9E79F</t>
+  </si>
+  <si>
+    <t>03852589100</t>
+  </si>
+  <si>
+    <t>EMP187EC2</t>
+  </si>
+  <si>
+    <t>77148-5316670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_21E80</t>
+  </si>
+  <si>
+    <t>03946424900</t>
+  </si>
+  <si>
+    <t>EMPAB961D</t>
+  </si>
+  <si>
+    <t>79579-4762900-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BE802</t>
+  </si>
+  <si>
+    <t>03951956600</t>
+  </si>
+  <si>
+    <t>EMPBB3082</t>
+  </si>
+  <si>
+    <t>79579-5251290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_36E99</t>
+  </si>
+  <si>
+    <t>03953051600</t>
+  </si>
+  <si>
+    <t>EMPC9D48E</t>
+  </si>
+  <si>
+    <t>79579-5354660-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_92DE5</t>
+  </si>
+  <si>
+    <t>03954114900</t>
+  </si>
+  <si>
+    <t>EMP302BF4</t>
+  </si>
+  <si>
+    <t>79579-5455720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7EF98</t>
+  </si>
+  <si>
+    <t>03954902800</t>
+  </si>
+  <si>
+    <t>EMP4AE073</t>
+  </si>
+  <si>
+    <t>79579-5567140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_225FB</t>
+  </si>
+  <si>
+    <t>03011345900</t>
+  </si>
+  <si>
+    <t>EMP508016</t>
+  </si>
+  <si>
+    <t>01870-1391700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_40B3A</t>
+  </si>
+  <si>
+    <t>03020110100</t>
+  </si>
+  <si>
+    <t>EMP7C4618</t>
+  </si>
+  <si>
+    <t>01870-2080190-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_734D3</t>
+  </si>
+  <si>
+    <t>03021469000</t>
+  </si>
+  <si>
+    <t>EMPDA282D</t>
+  </si>
+  <si>
+    <t>01870-2849140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A0E4D</t>
+  </si>
+  <si>
+    <t>03029503400</t>
+  </si>
+  <si>
+    <t>EMP35EE1E</t>
+  </si>
+  <si>
+    <t>01870-3033110-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6B903</t>
+  </si>
+  <si>
+    <t>03031187200</t>
+  </si>
+  <si>
+    <t>EMPED5F5B</t>
+  </si>
+  <si>
+    <t>01870-3214420-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4DD32</t>
+  </si>
+  <si>
+    <t>03160163900</t>
+  </si>
+  <si>
+    <t>EMP4B2ECE</t>
+  </si>
+  <si>
+    <t>03891-6132060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E5019</t>
+  </si>
+  <si>
+    <t>03165876800</t>
+  </si>
+  <si>
+    <t>EMPD4F82F</t>
+  </si>
+  <si>
+    <t>03891-6659360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FDEB7</t>
+  </si>
+  <si>
+    <t>03167256000</t>
+  </si>
+  <si>
+    <t>EMP4F35D2</t>
+  </si>
+  <si>
+    <t>03891-6773880-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C7630</t>
+  </si>
+  <si>
+    <t>03168420900</t>
+  </si>
+  <si>
+    <t>EMP47B28E</t>
+  </si>
+  <si>
+    <t>03891-6921600-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A3209</t>
+  </si>
+  <si>
+    <t>03170404000</t>
+  </si>
+  <si>
+    <t>EMP1D0BEE</t>
+  </si>
+  <si>
+    <t>03891-7152690-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0D4C0</t>
+  </si>
+  <si>
+    <t>03807210800</t>
+  </si>
+  <si>
+    <t>EMP3DB780</t>
+  </si>
+  <si>
+    <t>07058-0855090-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E4342</t>
+  </si>
+  <si>
+    <t>03815482400</t>
+  </si>
+  <si>
+    <t>EMP844E9B</t>
+  </si>
+  <si>
+    <t>07058-1635030-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_673BF</t>
+  </si>
+  <si>
+    <t>03816975500</t>
+  </si>
+  <si>
+    <t>EMPABB685</t>
+  </si>
+  <si>
+    <t>07058-1755860-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6CEEC</t>
+  </si>
+  <si>
+    <t>03818036000</t>
+  </si>
+  <si>
+    <t>EMPA706EF</t>
+  </si>
+  <si>
+    <t>07058-1848630-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2EAE0</t>
+  </si>
+  <si>
+    <t>03818901300</t>
+  </si>
+  <si>
+    <t>EMPCE7508</t>
+  </si>
+  <si>
+    <t>07058-1929720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_31C57</t>
+  </si>
+  <si>
+    <t>03669607300</t>
+  </si>
+  <si>
+    <t>EMPADD34A</t>
+  </si>
+  <si>
+    <t>17836-7173920-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_70553</t>
+  </si>
+  <si>
+    <t>03673482100</t>
+  </si>
+  <si>
+    <t>EMPD5CA1C</t>
+  </si>
+  <si>
+    <t>17836-7701800-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C5011</t>
+  </si>
+  <si>
+    <t>03678637300</t>
+  </si>
+  <si>
+    <t>EMPCA49D3</t>
+  </si>
+  <si>
+    <t>17836-7976800-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0BC60</t>
+  </si>
+  <si>
+    <t>03680939600</t>
+  </si>
+  <si>
+    <t>EMP3DDC54</t>
+  </si>
+  <si>
+    <t>17836-8179950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F68C7</t>
+  </si>
+  <si>
+    <t>03682487000</t>
+  </si>
+  <si>
+    <t>EMPA10957</t>
+  </si>
+  <si>
+    <t>17836-8314200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3D586</t>
+  </si>
+  <si>
+    <t>03716610500</t>
+  </si>
+  <si>
+    <t>EMP0F8EA3</t>
+  </si>
+  <si>
+    <t>19577-1884420-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8A95F</t>
+  </si>
+  <si>
+    <t>03725776400</t>
+  </si>
+  <si>
+    <t>EMP6A26DE</t>
+  </si>
+  <si>
+    <t>19577-2647380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_094A2</t>
+  </si>
+  <si>
+    <t>03727087200</t>
+  </si>
+  <si>
+    <t>EMP3C742D</t>
+  </si>
+  <si>
+    <t>19577-2763480-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_875CC</t>
+  </si>
+  <si>
+    <t>03728324000</t>
+  </si>
+  <si>
+    <t>EMPE83F46</t>
+  </si>
+  <si>
+    <t>19577-2896390-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B7D41</t>
+  </si>
+  <si>
+    <t>03729588300</t>
+  </si>
+  <si>
+    <t>EMP2657A1</t>
+  </si>
+  <si>
+    <t>19577-3015060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_47C0F</t>
+  </si>
+  <si>
+    <t>03948012400</t>
+  </si>
+  <si>
+    <t>EMP732971</t>
+  </si>
+  <si>
+    <t>58939-4977140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_757B0</t>
+  </si>
+  <si>
+    <t>03955736300</t>
+  </si>
+  <si>
+    <t>EMPE7A29D</t>
+  </si>
+  <si>
+    <t>58939-5648580-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A6D49</t>
+  </si>
+  <si>
+    <t>03957283000</t>
+  </si>
+  <si>
+    <t>EMP25B0C4</t>
+  </si>
+  <si>
+    <t>58939-5840430-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C8B41</t>
+  </si>
+  <si>
+    <t>03959221500</t>
+  </si>
+  <si>
+    <t>EMP7C22AF</t>
+  </si>
+  <si>
+    <t>58939-5995550-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9FC52</t>
+  </si>
+  <si>
+    <t>03961027700</t>
+  </si>
+  <si>
+    <t>EMPBF8920</t>
+  </si>
+  <si>
+    <t>58939-6176560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5D961</t>
+  </si>
+  <si>
+    <t>03605904100</t>
+  </si>
+  <si>
+    <t>EMPD9BE9F</t>
+  </si>
+  <si>
+    <t>85636-0720030-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_55765</t>
+  </si>
+  <si>
+    <t>03614766300</t>
+  </si>
+  <si>
+    <t>EMPDA37BF</t>
+  </si>
+  <si>
+    <t>85636-1556120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BF17C</t>
+  </si>
+  <si>
+    <t>03616674600</t>
+  </si>
+  <si>
+    <t>EMP9182DD</t>
+  </si>
+  <si>
+    <t>85636-1752320-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_72293</t>
+  </si>
+  <si>
+    <t>03618283200</t>
+  </si>
+  <si>
+    <t>EMP31A09D</t>
+  </si>
+  <si>
+    <t>85636-1900820-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_165F9</t>
+  </si>
+  <si>
+    <t>03619624100</t>
+  </si>
+  <si>
+    <t>EMP60EBFE</t>
+  </si>
+  <si>
+    <t>85636-2033050-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DD682</t>
+  </si>
+  <si>
+    <t>03175210700</t>
+  </si>
+  <si>
+    <t>EMPAE3B82</t>
+  </si>
+  <si>
+    <t>67431-7621080-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EE2B6</t>
+  </si>
+  <si>
+    <t>03182274800</t>
+  </si>
+  <si>
+    <t>EMP7A209B</t>
+  </si>
+  <si>
+    <t>67431-8288000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_70D0D</t>
+  </si>
+  <si>
+    <t>03183510700</t>
+  </si>
+  <si>
+    <t>EMP4DDFBE</t>
+  </si>
+  <si>
+    <t>67431-8417740-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_449ED</t>
+  </si>
+  <si>
+    <t>03184788800</t>
+  </si>
+  <si>
+    <t>EMP7FA016</t>
+  </si>
+  <si>
+    <t>67431-8526630-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E7A1D</t>
+  </si>
+  <si>
+    <t>03185787300</t>
+  </si>
+  <si>
+    <t>EMP273231</t>
+  </si>
+  <si>
+    <t>67431-8641420-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2FCA8</t>
+  </si>
+  <si>
+    <t>03315559700</t>
+  </si>
+  <si>
+    <t>EMP855940</t>
+  </si>
+  <si>
+    <t>79393-1647370-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7361C</t>
+  </si>
+  <si>
+    <t>03320191100</t>
+  </si>
+  <si>
+    <t>EMP138451</t>
+  </si>
+  <si>
+    <t>79393-2060950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8CECC</t>
+  </si>
+  <si>
+    <t>03321102500</t>
+  </si>
+  <si>
+    <t>EMP45AEFC</t>
+  </si>
+  <si>
+    <t>79393-2180240-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6A56F</t>
+  </si>
+  <si>
+    <t>03322329300</t>
+  </si>
+  <si>
+    <t>EMPA5C342</t>
+  </si>
+  <si>
+    <t>79393-2272240-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_812ED</t>
+  </si>
+  <si>
+    <t>03323099500</t>
+  </si>
+  <si>
+    <t>EMPA6C53F</t>
+  </si>
+  <si>
+    <t>79393-2368970-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7220D</t>
+  </si>
+  <si>
+    <t>03000642000</t>
+  </si>
+  <si>
+    <t>EMPC7FCEE</t>
+  </si>
+  <si>
+    <t>06390-0206300-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_EA1F1</t>
+  </si>
+  <si>
+    <t>03008045800</t>
+  </si>
+  <si>
+    <t>EMPEE5C55</t>
+  </si>
+  <si>
+    <t>06390-0883980-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D0884</t>
+  </si>
+  <si>
+    <t>03009542600</t>
+  </si>
+  <si>
+    <t>EMP7669C8</t>
+  </si>
+  <si>
+    <t>06390-1017200-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E58C8</t>
+  </si>
+  <si>
+    <t>03011084600</t>
+  </si>
+  <si>
+    <t>EMP6EC65B</t>
+  </si>
+  <si>
+    <t>06390-1169890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2C0BD</t>
+  </si>
+  <si>
+    <t>03012457600</t>
+  </si>
+  <si>
+    <t>EMPD6B707</t>
+  </si>
+  <si>
+    <t>06390-1307460-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_20FD4</t>
+  </si>
+  <si>
+    <t>03294831500</t>
+  </si>
+  <si>
+    <t>EMPE75F4D</t>
+  </si>
+  <si>
+    <t>07522-9629020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_098BA</t>
+  </si>
+  <si>
+    <t>03301545900</t>
+  </si>
+  <si>
+    <t>EMP1B1D0E</t>
+  </si>
+  <si>
+    <t>07523-0229070-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_043BC</t>
+  </si>
+  <si>
+    <t>03303168300</t>
+  </si>
+  <si>
+    <t>EMPEF12B4</t>
+  </si>
+  <si>
+    <t>07523-0401150-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_360E0</t>
+  </si>
+  <si>
+    <t>03304823200</t>
+  </si>
+  <si>
+    <t>EMPE14CD1</t>
+  </si>
+  <si>
+    <t>07523-0552360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D12A1</t>
+  </si>
+  <si>
+    <t>03306211200</t>
+  </si>
+  <si>
+    <t>EMPDED8FF</t>
+  </si>
+  <si>
+    <t>07523-0699390-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0DE36</t>
+  </si>
+  <si>
+    <t>03645896300</t>
+  </si>
+  <si>
+    <t>EMP4C7859</t>
+  </si>
+  <si>
+    <t>08486-4693680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A88B3</t>
+  </si>
+  <si>
+    <t>03653331600</t>
+  </si>
+  <si>
+    <t>EMP42F946</t>
+  </si>
+  <si>
+    <t>08486-5367980-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2C652</t>
+  </si>
+  <si>
+    <t>03654002400</t>
+  </si>
+  <si>
+    <t>EMPEF092A</t>
+  </si>
+  <si>
+    <t>08486-5457440-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DF389</t>
+  </si>
+  <si>
+    <t>03655108600</t>
+  </si>
+  <si>
+    <t>EMP345F95</t>
+  </si>
+  <si>
+    <t>08486-5567710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3641E</t>
+  </si>
+  <si>
+    <t>03656253500</t>
+  </si>
+  <si>
+    <t>EMP4935D8</t>
+  </si>
+  <si>
+    <t>08486-5679350-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F0B08</t>
+  </si>
+  <si>
+    <t>03235469900</t>
+  </si>
+  <si>
+    <t>EMP017F22</t>
+  </si>
+  <si>
+    <t>10812-3826020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5EE12</t>
+  </si>
+  <si>
+    <t>03248671700</t>
+  </si>
+  <si>
+    <t>EMPCB947B</t>
+  </si>
+  <si>
+    <t>10812-4947990-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_37916</t>
+  </si>
+  <si>
+    <t>03250358900</t>
+  </si>
+  <si>
+    <t>EMP4285AD</t>
+  </si>
+  <si>
+    <t>10812-5102960-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D2168</t>
+  </si>
+  <si>
+    <t>03252016400</t>
+  </si>
+  <si>
+    <t>EMP31BD7D</t>
+  </si>
+  <si>
+    <t>10812-5394890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5452A</t>
+  </si>
+  <si>
+    <t>03255169700</t>
+  </si>
+  <si>
+    <t>EMP817765</t>
+  </si>
+  <si>
+    <t>10812-5625690-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C656E</t>
+  </si>
+  <si>
+    <t>03072749700</t>
+  </si>
+  <si>
+    <t>EMP32BBC6</t>
+  </si>
+  <si>
+    <t>17080-7389810-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B4B79</t>
+  </si>
+  <si>
+    <t>03079508800</t>
+  </si>
+  <si>
+    <t>EMP3813B8</t>
+  </si>
+  <si>
+    <t>17080-7994010-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_525E0</t>
+  </si>
+  <si>
+    <t>03080327100</t>
+  </si>
+  <si>
+    <t>EMP8270F0</t>
+  </si>
+  <si>
+    <t>17080-8092460-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_74043</t>
+  </si>
+  <si>
+    <t>03081704800</t>
+  </si>
+  <si>
+    <t>EMP62B4AF</t>
+  </si>
+  <si>
+    <t>17080-8227150-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B1C38</t>
+  </si>
+  <si>
+    <t>03082820800</t>
+  </si>
+  <si>
+    <t>EMP8F60CE</t>
+  </si>
+  <si>
+    <t>17080-8341730-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_64AE7</t>
+  </si>
+  <si>
+    <t>03592252500</t>
+  </si>
+  <si>
+    <t>EMP3EF471</t>
+  </si>
+  <si>
+    <t>25305-9338180-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_94E4E</t>
+  </si>
+  <si>
+    <t>03598134700</t>
+  </si>
+  <si>
+    <t>EMP5503FF</t>
+  </si>
+  <si>
+    <t>25305-9858620-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0537D</t>
+  </si>
+  <si>
+    <t>03599176600</t>
+  </si>
+  <si>
+    <t>EMP82C1AD</t>
+  </si>
+  <si>
+    <t>25305-9970950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5E8FA</t>
+  </si>
+  <si>
+    <t>03600341900</t>
+  </si>
+  <si>
+    <t>EMP4F5222</t>
+  </si>
+  <si>
+    <t>25306-0092060-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_303B0</t>
+  </si>
+  <si>
+    <t>03601306200</t>
+  </si>
+  <si>
+    <t>EMP2BBB05</t>
+  </si>
+  <si>
+    <t>25306-0181020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BDBC4</t>
+  </si>
+  <si>
+    <t>03772805500</t>
+  </si>
+  <si>
+    <t>EMPF66918</t>
+  </si>
+  <si>
+    <t>25827-7409360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_238E5</t>
+  </si>
+  <si>
+    <t>03780067200</t>
+  </si>
+  <si>
+    <t>EMP5695C4</t>
+  </si>
+  <si>
+    <t>25827-8063680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E56DA</t>
+  </si>
+  <si>
+    <t>03781339600</t>
+  </si>
+  <si>
+    <t>EMP37B115</t>
+  </si>
+  <si>
+    <t>25827-8254210-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2C378</t>
+  </si>
+  <si>
+    <t>03783159600</t>
+  </si>
+  <si>
+    <t>EMPD3B942</t>
+  </si>
+  <si>
+    <t>25827-8397540-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F5A87</t>
+  </si>
+  <si>
+    <t>03784675700</t>
+  </si>
+  <si>
+    <t>EMPFA6918</t>
+  </si>
+  <si>
+    <t>25827-8515160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1ED55</t>
+  </si>
+  <si>
+    <t>03081350200</t>
+  </si>
+  <si>
+    <t>EMP94425E</t>
+  </si>
+  <si>
+    <t>28010-8241680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DE05D</t>
+  </si>
+  <si>
+    <t>03087478700</t>
+  </si>
+  <si>
+    <t>EMPFE198D</t>
+  </si>
+  <si>
+    <t>28010-8797410-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_B115E</t>
+  </si>
+  <si>
+    <t>03088634300</t>
+  </si>
+  <si>
+    <t>EMP63A872</t>
+  </si>
+  <si>
+    <t>28010-8919680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BAA44</t>
+  </si>
+  <si>
+    <t>03089688900</t>
+  </si>
+  <si>
+    <t>EMP0F386C</t>
+  </si>
+  <si>
+    <t>28010-9036740-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9FF96</t>
+  </si>
+  <si>
+    <t>03090957600</t>
+  </si>
+  <si>
+    <t>EMP46CEFE</t>
+  </si>
+  <si>
+    <t>28010-9138020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BF4EC</t>
+  </si>
+  <si>
+    <t>03006713300</t>
+  </si>
+  <si>
+    <t>EMPA60839</t>
+  </si>
+  <si>
+    <t>06090-1060000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F5AE6</t>
+  </si>
+  <si>
+    <t>03020254300</t>
+  </si>
+  <si>
+    <t>EMPB7F05A</t>
+  </si>
+  <si>
+    <t>06090-2088470-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_324A5</t>
+  </si>
+  <si>
+    <t>03021530600</t>
+  </si>
+  <si>
+    <t>EMP17E2E7</t>
+  </si>
+  <si>
+    <t>06090-2299720-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7418A</t>
+  </si>
+  <si>
+    <t>03024367800</t>
+  </si>
+  <si>
+    <t>EMP9E6F27</t>
+  </si>
+  <si>
+    <t>06090-2511020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8675C</t>
+  </si>
+  <si>
+    <t>03025628800</t>
+  </si>
+  <si>
+    <t>EMPC04F86</t>
+  </si>
+  <si>
+    <t>06090-2625420-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_672E8</t>
+  </si>
+  <si>
+    <t>03296177700</t>
+  </si>
+  <si>
+    <t>EMPC9AE76</t>
+  </si>
+  <si>
+    <t>87682-9747130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D4430</t>
+  </si>
+  <si>
+    <t>03302883300</t>
+  </si>
+  <si>
+    <t>EMP532FB2</t>
+  </si>
+  <si>
+    <t>87683-0361230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C4887</t>
+  </si>
+  <si>
+    <t>03304359200</t>
+  </si>
+  <si>
+    <t>EMP08276E</t>
+  </si>
+  <si>
+    <t>87683-0490020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8D77A</t>
+  </si>
+  <si>
+    <t>03305623800</t>
+  </si>
+  <si>
+    <t>EMP1E8395</t>
+  </si>
+  <si>
+    <t>87683-0628130-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4463D</t>
+  </si>
+  <si>
+    <t>03306903600</t>
+  </si>
+  <si>
+    <t>EMPB3A2D9</t>
+  </si>
+  <si>
+    <t>87683-0749340-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_92AEC</t>
+  </si>
+  <si>
+    <t>03150439400</t>
+  </si>
+  <si>
+    <t>EMP022AF5</t>
+  </si>
+  <si>
+    <t>96871-5180430-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2D21A</t>
+  </si>
+  <si>
+    <t>03157563200</t>
+  </si>
+  <si>
+    <t>EMP0BBB0D</t>
+  </si>
+  <si>
+    <t>96871-5821380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_92A0D</t>
+  </si>
+  <si>
+    <t>03159178100</t>
+  </si>
+  <si>
+    <t>EMP9ED082</t>
+  </si>
+  <si>
+    <t>96871-6029390-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_17FAC</t>
+  </si>
+  <si>
+    <t>03161225400</t>
+  </si>
+  <si>
+    <t>EMP6D4256</t>
+  </si>
+  <si>
+    <t>96871-6186780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F7092</t>
+  </si>
+  <si>
+    <t>03162513800</t>
+  </si>
+  <si>
+    <t>EMPCD4AF2</t>
+  </si>
+  <si>
+    <t>96871-6312020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8A766</t>
+  </si>
+  <si>
+    <t>03578362900</t>
+  </si>
+  <si>
+    <t>EMP2C2629</t>
+  </si>
+  <si>
+    <t>97755-7970520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9B27C</t>
+  </si>
+  <si>
+    <t>03584788200</t>
+  </si>
+  <si>
+    <t>EMPBAF66E</t>
+  </si>
+  <si>
+    <t>97755-8534430-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CDFD5</t>
+  </si>
+  <si>
+    <t>03586377200</t>
+  </si>
+  <si>
+    <t>EMP93A81D</t>
+  </si>
+  <si>
+    <t>97755-8710160-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_70F4A</t>
+  </si>
+  <si>
+    <t>03587965800</t>
+  </si>
+  <si>
+    <t>EMPC22A5C</t>
+  </si>
+  <si>
+    <t>97755-8932670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3376B</t>
+  </si>
+  <si>
+    <t>03590160000</t>
+  </si>
+  <si>
+    <t>EMPEFC250</t>
+  </si>
+  <si>
+    <t>97755-9103820-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9D3AC</t>
+  </si>
+  <si>
+    <t>03200388300</t>
+  </si>
+  <si>
+    <t>EMP7F2408</t>
+  </si>
+  <si>
+    <t>40402-0145730-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D99F9</t>
+  </si>
+  <si>
+    <t>03206371900</t>
+  </si>
+  <si>
+    <t>EMPC0FEF4</t>
+  </si>
+  <si>
+    <t>40402-0691360-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB9C5</t>
+  </si>
+  <si>
+    <t>03207491500</t>
+  </si>
+  <si>
+    <t>EMP263D7B</t>
+  </si>
+  <si>
+    <t>40402-0805230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9C363</t>
+  </si>
+  <si>
+    <t>03208605900</t>
+  </si>
+  <si>
+    <t>EMP53507F</t>
+  </si>
+  <si>
+    <t>40402-0905920-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AD04C</t>
+  </si>
+  <si>
+    <t>03209656100</t>
+  </si>
+  <si>
+    <t>EMP55B722</t>
+  </si>
+  <si>
+    <t>40402-1030100-0</t>
+  </si>
+  <si>
+    <t>03868671600</t>
+  </si>
+  <si>
+    <t>EMP12A990</t>
+  </si>
+  <si>
+    <t>26798-7032260-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6369B</t>
+  </si>
+  <si>
+    <t>03882128500</t>
+  </si>
+  <si>
+    <t>EMPEC338E</t>
+  </si>
+  <si>
+    <t>26798-8376030-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D9131</t>
+  </si>
+  <si>
+    <t>03885311600</t>
+  </si>
+  <si>
+    <t>EMP257459</t>
+  </si>
+  <si>
+    <t>26798-8640540-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8F25A</t>
+  </si>
+  <si>
+    <t>03887184000</t>
+  </si>
+  <si>
+    <t>EMP3483AE</t>
+  </si>
+  <si>
+    <t>26798-8791220-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_061D5</t>
+  </si>
+  <si>
+    <t>03889333300</t>
+  </si>
+  <si>
+    <t>EMP3B00F1</t>
+  </si>
+  <si>
+    <t>26798-9012830-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_27D4F</t>
+  </si>
+  <si>
+    <t>03064960400</t>
+  </si>
+  <si>
+    <t>EMP539536</t>
+  </si>
+  <si>
+    <t>31500-6599560-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6362D</t>
+  </si>
+  <si>
+    <t>03071101800</t>
+  </si>
+  <si>
+    <t>EMP1EB7E5</t>
+  </si>
+  <si>
+    <t>31500-7174710-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_42C00</t>
+  </si>
+  <si>
+    <t>03072777600</t>
+  </si>
+  <si>
+    <t>EMPB37B48</t>
+  </si>
+  <si>
+    <t>31500-7361470-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9F65F</t>
+  </si>
+  <si>
+    <t>03074294900</t>
+  </si>
+  <si>
+    <t>EMP0ADE6E</t>
+  </si>
+  <si>
+    <t>31500-7476140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_44670</t>
+  </si>
+  <si>
+    <t>03075403500</t>
+  </si>
+  <si>
+    <t>EMP4E1BAD</t>
+  </si>
+  <si>
+    <t>31500-7598080-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_27A06</t>
+  </si>
+  <si>
+    <t>03651689900</t>
+  </si>
+  <si>
+    <t>EMPEB0737</t>
+  </si>
+  <si>
+    <t>38096-5284100-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1A39C</t>
+  </si>
+  <si>
+    <t>03658343900</t>
+  </si>
+  <si>
+    <t>EMP66930A</t>
+  </si>
+  <si>
+    <t>38096-5914670-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D5F02</t>
+  </si>
+  <si>
+    <t>03660061200</t>
+  </si>
+  <si>
+    <t>EMP3EE3DE</t>
+  </si>
+  <si>
+    <t>38096-6074610-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_476D7</t>
+  </si>
+  <si>
+    <t>03661212200</t>
+  </si>
+  <si>
+    <t>EMP0E27FB</t>
+  </si>
+  <si>
+    <t>38096-6170550-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0F370</t>
+  </si>
+  <si>
+    <t>03662414900</t>
+  </si>
+  <si>
+    <t>EMP6ADB67</t>
+  </si>
+  <si>
+    <t>38096-6279700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_86ACA</t>
+  </si>
+  <si>
+    <t>03161127600</t>
+  </si>
+  <si>
+    <t>EMP3D21A4</t>
+  </si>
+  <si>
+    <t>51191-6250880-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_E3608</t>
+  </si>
+  <si>
+    <t>03166895900</t>
+  </si>
+  <si>
+    <t>EMP192C1A</t>
+  </si>
+  <si>
+    <t>51191-6750210-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A6F68</t>
+  </si>
+  <si>
+    <t>03168092900</t>
+  </si>
+  <si>
+    <t>EMP141060</t>
+  </si>
+  <si>
+    <t>51191-6869570-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5CA06</t>
+  </si>
+  <si>
+    <t>03169356800</t>
+  </si>
+  <si>
+    <t>EMP3833E3</t>
+  </si>
+  <si>
+    <t>51191-6987270-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0337C</t>
+  </si>
+  <si>
+    <t>03170351000</t>
+  </si>
+  <si>
+    <t>EMPED6FEC</t>
+  </si>
+  <si>
+    <t>51191-7078490-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8BA48</t>
+  </si>
+  <si>
+    <t>03704975400</t>
+  </si>
+  <si>
+    <t>EMP49FFA7</t>
+  </si>
+  <si>
+    <t>59277-0691640-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_32D0A</t>
+  </si>
+  <si>
+    <t>03713773700</t>
+  </si>
+  <si>
+    <t>EMP007783</t>
+  </si>
+  <si>
+    <t>59277-1455890-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FD67F</t>
+  </si>
+  <si>
+    <t>03715376500</t>
+  </si>
+  <si>
+    <t>EMP0DCBC8</t>
+  </si>
+  <si>
+    <t>59277-1604690-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D3CA1</t>
+  </si>
+  <si>
+    <t>03716724900</t>
+  </si>
+  <si>
+    <t>EMP50D1B3</t>
+  </si>
+  <si>
+    <t>59277-1744780-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB114</t>
+  </si>
+  <si>
+    <t>03718127100</t>
+  </si>
+  <si>
+    <t>EMP38FC65</t>
+  </si>
+  <si>
+    <t>59277-1881990-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3BA66</t>
+  </si>
+  <si>
+    <t>03548446100</t>
+  </si>
+  <si>
+    <t>EMP3A8DC6</t>
+  </si>
+  <si>
+    <t>63485-5008520-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C1242</t>
+  </si>
+  <si>
+    <t>03556594700</t>
+  </si>
+  <si>
+    <t>EMPC1D24E</t>
+  </si>
+  <si>
+    <t>63485-5713140-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9B55F</t>
+  </si>
+  <si>
+    <t>03557593200</t>
+  </si>
+  <si>
+    <t>EMPC962C9</t>
+  </si>
+  <si>
+    <t>63485-5812530-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DB5B3</t>
+  </si>
+  <si>
+    <t>03558615200</t>
+  </si>
+  <si>
+    <t>EMP180DF2</t>
+  </si>
+  <si>
+    <t>63485-5912380-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8DC4A</t>
+  </si>
+  <si>
+    <t>03559558800</t>
+  </si>
+  <si>
+    <t>EMP190868</t>
+  </si>
+  <si>
+    <t>63485-6013580-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_F4EFC</t>
+  </si>
+  <si>
+    <t>03883010800</t>
+  </si>
+  <si>
+    <t>EMP24721B</t>
+  </si>
+  <si>
+    <t>75118-8435290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_8753D</t>
+  </si>
+  <si>
+    <t>03888710100</t>
+  </si>
+  <si>
+    <t>EMPF1780F</t>
+  </si>
+  <si>
+    <t>75118-8929100-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_727D8</t>
+  </si>
+  <si>
+    <t>03889891900</t>
+  </si>
+  <si>
+    <t>EMP4A1993</t>
+  </si>
+  <si>
+    <t>75118-9031680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_BF1DF</t>
+  </si>
+  <si>
+    <t>03890765100</t>
+  </si>
+  <si>
+    <t>EMP7A77A3</t>
+  </si>
+  <si>
+    <t>75118-9128290-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_6AB45</t>
+  </si>
+  <si>
+    <t>03891991300</t>
+  </si>
+  <si>
+    <t>EMPA6ACBB</t>
+  </si>
+  <si>
+    <t>75118-9263860-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A99B5</t>
+  </si>
+  <si>
+    <t>03649149900</t>
+  </si>
+  <si>
+    <t>EMP0D6B16</t>
+  </si>
+  <si>
+    <t>32786-5069430-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_59FF2</t>
+  </si>
+  <si>
+    <t>03657532500</t>
+  </si>
+  <si>
+    <t>EMPECFE9D</t>
+  </si>
+  <si>
+    <t>32786-5850470-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CD435</t>
+  </si>
+  <si>
+    <t>03660834600</t>
+  </si>
+  <si>
+    <t>EMP205B21</t>
+  </si>
+  <si>
+    <t>32786-6168220-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0AC87</t>
+  </si>
+  <si>
+    <t>03662796300</t>
+  </si>
+  <si>
+    <t>EMPB6172E</t>
+  </si>
+  <si>
+    <t>32786-6364470-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_2CD3E</t>
+  </si>
+  <si>
+    <t>03664561900</t>
+  </si>
+  <si>
+    <t>EMP9F0C32</t>
+  </si>
+  <si>
+    <t>32786-6549490-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_69E4F</t>
+  </si>
+  <si>
+    <t>03745234300</t>
+  </si>
+  <si>
+    <t>EMP740F82</t>
+  </si>
+  <si>
+    <t>49357-4682790-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_762EF</t>
+  </si>
+  <si>
+    <t>03752250500</t>
+  </si>
+  <si>
+    <t>EMP86269D</t>
+  </si>
+  <si>
+    <t>49357-5306820-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_7730D</t>
+  </si>
+  <si>
+    <t>03754071300</t>
+  </si>
+  <si>
+    <t>EMP1F3943</t>
+  </si>
+  <si>
+    <t>49357-5489120-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_4656A</t>
+  </si>
+  <si>
+    <t>03755395200</t>
+  </si>
+  <si>
+    <t>EMP0C1BFD</t>
+  </si>
+  <si>
+    <t>49357-5602000-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C1E11</t>
+  </si>
+  <si>
+    <t>03756713000</t>
+  </si>
+  <si>
+    <t>EMP2B468F</t>
+  </si>
+  <si>
+    <t>49357-5727180-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D49D6</t>
+  </si>
+  <si>
+    <t>03455788800</t>
+  </si>
+  <si>
+    <t>EMP164657</t>
+  </si>
+  <si>
+    <t>29644-5704020-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C0635</t>
+  </si>
+  <si>
+    <t>03462897200</t>
+  </si>
+  <si>
+    <t>EMPE4F94D</t>
+  </si>
+  <si>
+    <t>29644-6354230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_A2544</t>
+  </si>
+  <si>
+    <t>03464251500</t>
+  </si>
+  <si>
+    <t>EMPE5C30E</t>
+  </si>
+  <si>
+    <t>29644-6497350-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B2E8</t>
+  </si>
+  <si>
+    <t>03465628900</t>
+  </si>
+  <si>
+    <t>EMPAFFB73</t>
+  </si>
+  <si>
+    <t>29644-6627770-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_D75DF</t>
+  </si>
+  <si>
+    <t>03466918100</t>
+  </si>
+  <si>
+    <t>EMP296611</t>
+  </si>
+  <si>
+    <t>29644-6751840-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_69B11</t>
+  </si>
+  <si>
+    <t>03156559700</t>
+  </si>
+  <si>
+    <t>EMPA60504</t>
+  </si>
+  <si>
+    <t>57951-5767050-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C9FAD</t>
+  </si>
+  <si>
+    <t>03164383000</t>
+  </si>
+  <si>
+    <t>EMPE9B4C0</t>
+  </si>
+  <si>
+    <t>57951-6579750-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FDB72</t>
+  </si>
+  <si>
+    <t>03167010400</t>
+  </si>
+  <si>
+    <t>EMPBC27F4</t>
+  </si>
+  <si>
+    <t>57951-6779510-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_DC8C7</t>
+  </si>
+  <si>
+    <t>03168742800</t>
+  </si>
+  <si>
+    <t>EMPD50FAE</t>
+  </si>
+  <si>
+    <t>57951-6958230-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_FBF8A</t>
+  </si>
+  <si>
+    <t>03170372800</t>
+  </si>
+  <si>
+    <t>EMP8C43FB</t>
+  </si>
+  <si>
+    <t>57951-7112950-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_78681</t>
+  </si>
+  <si>
+    <t>03919801400</t>
+  </si>
+  <si>
+    <t>EMP066CD8</t>
+  </si>
+  <si>
+    <t>67069-2091080-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_5F7E2</t>
+  </si>
+  <si>
+    <t>03926416600</t>
+  </si>
+  <si>
+    <t>EMPBA835B</t>
+  </si>
+  <si>
+    <t>67069-2711700-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_0DA08</t>
+  </si>
+  <si>
+    <t>03927821100</t>
+  </si>
+  <si>
+    <t>EMPE12E46</t>
+  </si>
+  <si>
+    <t>67069-2862510-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_C642E</t>
+  </si>
+  <si>
+    <t>03929259400</t>
+  </si>
+  <si>
+    <t>EMP6686EF</t>
+  </si>
+  <si>
+    <t>67069-2979680-0</t>
+  </si>
+  <si>
+    <t>AUTODSR_CD1E3</t>
+  </si>
+  <si>
+    <t>03930591800</t>
+  </si>
+  <si>
+    <t>EMP8D38E4</t>
+  </si>
+  <si>
+    <t>67069-3127310-0</t>
+  </si>
+  <si>
+    <t>DSR_64E3F</t>
+  </si>
+  <si>
+    <t>AUTODSR_1A691</t>
+  </si>
+  <si>
+    <t>03781451600</t>
+  </si>
+  <si>
+    <t>EMP74D47C</t>
+  </si>
+  <si>
+    <t>51267-8283930-0</t>
+  </si>
+  <si>
+    <t>DSR_04266</t>
+  </si>
+  <si>
+    <t>AUTODSR_1D9FB</t>
+  </si>
+  <si>
+    <t>03787759900</t>
+  </si>
+  <si>
+    <t>EMPEFF75E</t>
+  </si>
+  <si>
+    <t>51267-8821990-0</t>
+  </si>
+  <si>
+    <t>DSR_C3EBC</t>
+  </si>
+  <si>
+    <t>AUTODSR_65738</t>
+  </si>
+  <si>
+    <t>03789044400</t>
+  </si>
+  <si>
+    <t>EMPB0A226</t>
+  </si>
+  <si>
+    <t>51267-8953130-0</t>
+  </si>
+  <si>
+    <t>DSR_CADFF</t>
+  </si>
+  <si>
+    <t>AUTODSR_78DB1</t>
+  </si>
+  <si>
+    <t>03790206100</t>
+  </si>
+  <si>
+    <t>EMP9C8884</t>
+  </si>
+  <si>
+    <t>51267-9066310-0</t>
+  </si>
+  <si>
+    <t>DSR_A2099</t>
+  </si>
+  <si>
+    <t>AUTODSR_A788C</t>
+  </si>
+  <si>
+    <t>03791384100</t>
+  </si>
+  <si>
+    <t>EMPC59ACE</t>
+  </si>
+  <si>
+    <t>51267-9173460-0</t>
+  </si>
+  <si>
+    <t>DSR_24E72</t>
+  </si>
+  <si>
+    <t>AUTODSR_F7AD8</t>
+  </si>
+  <si>
+    <t>03208419500</t>
+  </si>
+  <si>
+    <t>EMPD05C12</t>
+  </si>
+  <si>
+    <t>54642-0919230-0</t>
+  </si>
+  <si>
+    <t>DSR_A88D3</t>
+  </si>
+  <si>
+    <t>AUTODSR_3AE9B</t>
+  </si>
+  <si>
+    <t>03213730300</t>
+  </si>
+  <si>
+    <t>EMPBC1396</t>
+  </si>
+  <si>
+    <t>54642-1421630-0</t>
+  </si>
+  <si>
+    <t>DSR_0388E</t>
+  </si>
+  <si>
+    <t>AUTODSR_58044</t>
+  </si>
+  <si>
+    <t>03215032700</t>
+  </si>
+  <si>
+    <t>EMPB438C2</t>
+  </si>
+  <si>
+    <t>54642-1550610-0</t>
+  </si>
+  <si>
+    <t>DSR_4E501</t>
+  </si>
+  <si>
+    <t>AUTODSR_56184</t>
+  </si>
+  <si>
+    <t>03216209200</t>
+  </si>
+  <si>
+    <t>EMPED31B3</t>
+  </si>
+  <si>
+    <t>54642-1667310-0</t>
+  </si>
+  <si>
+    <t>DSR_DC39D</t>
+  </si>
+  <si>
+    <t>AUTODSR_8CD9C</t>
+  </si>
+  <si>
+    <t>03217302000</t>
+  </si>
+  <si>
+    <t>EMPBBAF55</t>
+  </si>
+  <si>
+    <t>54642-1781290-0</t>
+  </si>
+  <si>
+    <t>DSR_6B2D6</t>
+  </si>
+  <si>
+    <t>AUTODSR_BC5B3</t>
+  </si>
+  <si>
+    <t>03714018200</t>
+  </si>
+  <si>
+    <t>EMP492ABC</t>
+  </si>
+  <si>
+    <t>56567-1494010-0</t>
+  </si>
+  <si>
+    <t>DSR_D7F5F</t>
+  </si>
+  <si>
+    <t>AUTODSR_C7DFE</t>
+  </si>
+  <si>
+    <t>03720587100</t>
+  </si>
+  <si>
+    <t>EMP16E21D</t>
+  </si>
+  <si>
+    <t>56567-2115450-0</t>
+  </si>
+  <si>
+    <t>DSR_9C7FE</t>
+  </si>
+  <si>
+    <t>AUTODSR_957D4</t>
+  </si>
+  <si>
+    <t>03722062400</t>
+  </si>
+  <si>
+    <t>EMPE02204</t>
+  </si>
+  <si>
+    <t>56567-2258840-0</t>
+  </si>
+  <si>
+    <t>DSR_B0908</t>
+  </si>
+  <si>
+    <t>AUTODSR_738BC</t>
+  </si>
+  <si>
+    <t>03723332500</t>
+  </si>
+  <si>
+    <t>EMP5A0680</t>
+  </si>
+  <si>
+    <t>56567-2384000-0</t>
+  </si>
+  <si>
+    <t>DSR_FC53E</t>
+  </si>
+  <si>
+    <t>AUTODSR_54083</t>
+  </si>
+  <si>
+    <t>03724613500</t>
+  </si>
+  <si>
+    <t>EMP27F350</t>
+  </si>
+  <si>
+    <t>56567-2518700-0</t>
+  </si>
+  <si>
+    <t>DSR_A243E</t>
+  </si>
+  <si>
+    <t>AUTODSR_8887F</t>
+  </si>
+  <si>
+    <t>03525607000</t>
+  </si>
+  <si>
+    <t>EMP76918D</t>
+  </si>
+  <si>
+    <t>58265-2707840-0</t>
+  </si>
+  <si>
+    <t>DSR_11136</t>
+  </si>
+  <si>
+    <t>AUTODSR_69796</t>
+  </si>
+  <si>
+    <t>03532150100</t>
+  </si>
+  <si>
+    <t>EMP61CE23</t>
+  </si>
+  <si>
+    <t>58265-3274950-0</t>
+  </si>
+  <si>
+    <t>DSR_D591C</t>
+  </si>
+  <si>
+    <t>AUTODSR_D22AE</t>
+  </si>
+  <si>
+    <t>03533726300</t>
+  </si>
+  <si>
+    <t>EMPD6EE6C</t>
+  </si>
+  <si>
+    <t>58265-3429770-0</t>
+  </si>
+  <si>
+    <t>DSR_00B2C</t>
+  </si>
+  <si>
+    <t>AUTODSR_10C48</t>
+  </si>
+  <si>
+    <t>03535077800</t>
+  </si>
+  <si>
+    <t>EMPE62B24</t>
+  </si>
+  <si>
+    <t>58265-3551480-0</t>
+  </si>
+  <si>
+    <t>DSR_46563</t>
+  </si>
+  <si>
+    <t>AUTODSR_BD0AA</t>
+  </si>
+  <si>
+    <t>03536846700</t>
+  </si>
+  <si>
+    <t>EMPC408F3</t>
+  </si>
+  <si>
+    <t>58265-3758660-0</t>
+  </si>
+  <si>
+    <t>DSR_0AF0F</t>
+  </si>
+  <si>
+    <t>AUTODSR_17779</t>
+  </si>
+  <si>
+    <t>03506554700</t>
+  </si>
+  <si>
+    <t>EMPA816C1</t>
+  </si>
+  <si>
+    <t>61885-0734750-0</t>
+  </si>
+  <si>
+    <t>DSR_BBD4E</t>
+  </si>
+  <si>
+    <t>AUTODSR_5474A</t>
+  </si>
+  <si>
+    <t>03512147600</t>
+  </si>
+  <si>
+    <t>EMPCC524B</t>
+  </si>
+  <si>
+    <t>61885-1293190-0</t>
+  </si>
+  <si>
+    <t>DSR_77931</t>
+  </si>
+  <si>
+    <t>AUTODSR_DF2E3</t>
+  </si>
+  <si>
+    <t>03513634700</t>
+  </si>
+  <si>
+    <t>EMP9836A6</t>
+  </si>
+  <si>
+    <t>61885-1406530-0</t>
+  </si>
+  <si>
+    <t>DSR_7A3BD</t>
+  </si>
+  <si>
+    <t>AUTODSR_3A2DE</t>
+  </si>
+  <si>
+    <t>03514699200</t>
+  </si>
+  <si>
+    <t>EMPB93379</t>
+  </si>
+  <si>
+    <t>61885-1515270-0</t>
+  </si>
+  <si>
+    <t>DSR_DA392</t>
+  </si>
+  <si>
+    <t>AUTODSR_1EFD0</t>
+  </si>
+  <si>
+    <t>03516126500</t>
+  </si>
+  <si>
+    <t>EMP71DDD8</t>
+  </si>
+  <si>
+    <t>61885-1676060-0</t>
+  </si>
+  <si>
+    <t>DSR_A6AA1</t>
+  </si>
+  <si>
+    <t>AUTODSR_12949</t>
+  </si>
+  <si>
+    <t>03169415800</t>
+  </si>
+  <si>
+    <t>EMP740517</t>
+  </si>
+  <si>
+    <t>62211-6985340-0</t>
+  </si>
+  <si>
+    <t>DSR_EFF6D</t>
+  </si>
+  <si>
+    <t>AUTODSR_044ED</t>
+  </si>
+  <si>
+    <t>03170604100</t>
+  </si>
+  <si>
+    <t>EMPF0D3EA</t>
+  </si>
+  <si>
+    <t>62211-7105780-0</t>
+  </si>
+  <si>
+    <t>DSR_87E43</t>
+  </si>
+  <si>
+    <t>AUTODSR_2DD55</t>
+  </si>
+  <si>
+    <t>03171697900</t>
+  </si>
+  <si>
+    <t>EMP32EC61</t>
+  </si>
+  <si>
+    <t>62211-7208400-0</t>
+  </si>
+  <si>
+    <t>DSR_83D19</t>
+  </si>
+  <si>
+    <t>AUTODSR_83505</t>
+  </si>
+  <si>
+    <t>03172810400</t>
+  </si>
+  <si>
+    <t>EMPE0D30F</t>
+  </si>
+  <si>
+    <t>62211-7321500-0</t>
+  </si>
+  <si>
+    <t>DSR_0BB83</t>
+  </si>
+  <si>
+    <t>AUTODSR_063E3</t>
+  </si>
+  <si>
+    <t>03173785800</t>
+  </si>
+  <si>
+    <t>EMP40180B</t>
+  </si>
+  <si>
+    <t>62211-7422020-0</t>
+  </si>
+  <si>
+    <t>DSR_E8759</t>
+  </si>
+  <si>
+    <t>AUTODSR_2553F</t>
+  </si>
+  <si>
+    <t>03859967400</t>
+  </si>
+  <si>
+    <t>EMP6E9A62</t>
+  </si>
+  <si>
+    <t>63798-6086410-0</t>
+  </si>
+  <si>
+    <t>DSR_24885</t>
+  </si>
+  <si>
+    <t>AUTODSR_358DB</t>
+  </si>
+  <si>
+    <t>03864421200</t>
+  </si>
+  <si>
+    <t>EMPC80CB8</t>
+  </si>
+  <si>
+    <t>63798-6480020-0</t>
+  </si>
+  <si>
+    <t>DSR_9EB15</t>
+  </si>
+  <si>
+    <t>AUTODSR_A1311</t>
+  </si>
+  <si>
+    <t>03865549500</t>
+  </si>
+  <si>
+    <t>EMPF8CC05</t>
+  </si>
+  <si>
+    <t>63798-6601710-0</t>
+  </si>
+  <si>
+    <t>DSR_6C191</t>
+  </si>
+  <si>
+    <t>AUTODSR_F0C1C</t>
+  </si>
+  <si>
+    <t>03866503600</t>
+  </si>
+  <si>
+    <t>EMP7789DA</t>
+  </si>
+  <si>
+    <t>63798-6710200-0</t>
+  </si>
+  <si>
+    <t>DSR_27638</t>
+  </si>
+  <si>
+    <t>AUTODSR_5A9AB</t>
+  </si>
+  <si>
+    <t>03868197300</t>
+  </si>
+  <si>
+    <t>EMPCE3E0A</t>
+  </si>
+  <si>
+    <t>63798-6859460-0</t>
+  </si>
+  <si>
+    <t>DSR_8B292</t>
+  </si>
+  <si>
+    <t>AUTODSR_3EA5C</t>
+  </si>
+  <si>
+    <t>03290290900</t>
+  </si>
+  <si>
+    <t>EMPBF3F77</t>
+  </si>
+  <si>
+    <t>64122-9074170-0</t>
+  </si>
+  <si>
+    <t>DSR_95C71</t>
+  </si>
+  <si>
+    <t>AUTODSR_0FB38</t>
+  </si>
+  <si>
+    <t>03291491000</t>
+  </si>
+  <si>
+    <t>EMP82AB73</t>
+  </si>
+  <si>
+    <t>64122-9189750-0</t>
+  </si>
+  <si>
+    <t>DSR_1F175</t>
+  </si>
+  <si>
+    <t>AUTODSR_476F6</t>
+  </si>
+  <si>
+    <t>03292529700</t>
+  </si>
+  <si>
+    <t>EMPA9D14D</t>
+  </si>
+  <si>
+    <t>64122-9289140-0</t>
+  </si>
+  <si>
+    <t>DSR_FDBCD</t>
+  </si>
+  <si>
+    <t>AUTODSR_F5492</t>
+  </si>
+  <si>
+    <t>03293495400</t>
+  </si>
+  <si>
+    <t>EMP6A9555</t>
+  </si>
+  <si>
+    <t>64122-9391450-0</t>
+  </si>
+  <si>
+    <t>DSR_C4F8E</t>
+  </si>
+  <si>
+    <t>AUTODSR_E286E</t>
+  </si>
+  <si>
+    <t>03294493600</t>
+  </si>
+  <si>
+    <t>EMP0E964A</t>
+  </si>
+  <si>
+    <t>64122-9489600-0</t>
+  </si>
+  <si>
+    <t>DSR_831F3</t>
+  </si>
+  <si>
+    <t>AUTODSR_08BE2</t>
+  </si>
+  <si>
+    <t>03361934300</t>
+  </si>
+  <si>
+    <t>EMPE860AD</t>
+  </si>
+  <si>
+    <t>88683-6386210-0</t>
+  </si>
+  <si>
+    <t>DSR_DEE18</t>
+  </si>
+  <si>
+    <t>AUTODSR_14D37</t>
+  </si>
+  <si>
+    <t>03365875800</t>
+  </si>
+  <si>
+    <t>EMP2E947A</t>
+  </si>
+  <si>
+    <t>88683-6655000-0</t>
+  </si>
+  <si>
+    <t>DSR_F988F</t>
+  </si>
+  <si>
+    <t>AUTODSR_D41CD</t>
+  </si>
+  <si>
+    <t>03367986300</t>
+  </si>
+  <si>
+    <t>EMPBC50A3</t>
+  </si>
+  <si>
+    <t>88683-6859590-0</t>
+  </si>
+  <si>
+    <t>DSR_3723F</t>
+  </si>
+  <si>
+    <t>AUTODSR_C057E</t>
+  </si>
+  <si>
+    <t>03370020300</t>
+  </si>
+  <si>
+    <t>EMP1F4109</t>
+  </si>
+  <si>
+    <t>88683-7062080-0</t>
+  </si>
+  <si>
+    <t>DSR_C7BA1</t>
+  </si>
+  <si>
+    <t>AUTODSR_32471</t>
+  </si>
+  <si>
+    <t>03371993400</t>
+  </si>
+  <si>
+    <t>EMP907507</t>
+  </si>
+  <si>
+    <t>88683-7268930-0</t>
+  </si>
+  <si>
+    <t>DSR_1F101</t>
+  </si>
+  <si>
+    <t>AUTODSR_E360B</t>
+  </si>
+  <si>
+    <t>03511678700</t>
+  </si>
+  <si>
+    <t>EMP44A621</t>
+  </si>
+  <si>
+    <t>89065-1301550-0</t>
+  </si>
+  <si>
+    <t>DSR_06B92</t>
+  </si>
+  <si>
+    <t>AUTODSR_3C69E</t>
+  </si>
+  <si>
+    <t>03514632700</t>
+  </si>
+  <si>
+    <t>EMP40261F</t>
+  </si>
+  <si>
+    <t>89065-1545170-0</t>
+  </si>
+  <si>
+    <t>DSR_E75AC</t>
+  </si>
+  <si>
+    <t>AUTODSR_485F6</t>
+  </si>
+  <si>
+    <t>03517182900</t>
+  </si>
+  <si>
+    <t>EMPA27B10</t>
+  </si>
+  <si>
+    <t>89065-1798470-0</t>
+  </si>
+  <si>
+    <t>DSR_2C5AE</t>
+  </si>
+  <si>
+    <t>AUTODSR_A6CCF</t>
+  </si>
+  <si>
+    <t>03519291500</t>
+  </si>
+  <si>
+    <t>EMP04BA48</t>
+  </si>
+  <si>
+    <t>89065-1981500-0</t>
+  </si>
+  <si>
+    <t>DSR_30777</t>
+  </si>
+  <si>
+    <t>AUTODSR_4B4AE</t>
+  </si>
+  <si>
+    <t>03520633500</t>
+  </si>
+  <si>
+    <t>EMPE7A84F</t>
+  </si>
+  <si>
+    <t>89065-2135420-0</t>
+  </si>
+  <si>
+    <t>DSR_A9F33</t>
+  </si>
+  <si>
+    <t>AUTODSR_8B474</t>
+  </si>
+  <si>
+    <t>03162409800</t>
+  </si>
+  <si>
+    <t>EMPA750A3</t>
+  </si>
+  <si>
+    <t>90701-6441710-0</t>
+  </si>
+  <si>
+    <t>DSR_22545</t>
+  </si>
+  <si>
+    <t>AUTODSR_01089</t>
+  </si>
+  <si>
+    <t>03166356300</t>
+  </si>
+  <si>
+    <t>EMP36E0D1</t>
+  </si>
+  <si>
+    <t>90701-6723250-0</t>
+  </si>
+  <si>
+    <t>DSR_84E65</t>
+  </si>
+  <si>
+    <t>AUTODSR_3CC4A</t>
+  </si>
+  <si>
+    <t>03168726800</t>
+  </si>
+  <si>
+    <t>EMPA1F20C</t>
+  </si>
+  <si>
+    <t>90701-6956580-0</t>
+  </si>
+  <si>
+    <t>DSR_EF464</t>
+  </si>
+  <si>
+    <t>AUTODSR_53AA0</t>
+  </si>
+  <si>
+    <t>03170886500</t>
+  </si>
+  <si>
+    <t>EMP2CB4E8</t>
+  </si>
+  <si>
+    <t>90701-7168730-0</t>
+  </si>
+  <si>
+    <t>DSR_1056D</t>
+  </si>
+  <si>
+    <t>AUTODSR_44FDA</t>
+  </si>
+  <si>
+    <t>03173007600</t>
+  </si>
+  <si>
+    <t>EMP52AD78</t>
+  </si>
+  <si>
+    <t>90701-7381830-0</t>
+  </si>
+  <si>
+    <t>DSR_49260</t>
+  </si>
+  <si>
+    <t>AUTODSR_736B9</t>
+  </si>
+  <si>
+    <t>03096244900</t>
+  </si>
+  <si>
+    <t>EMPC9EF09</t>
+  </si>
+  <si>
+    <t>91130-9770320-0</t>
+  </si>
+  <si>
+    <t>DSR_2035D</t>
+  </si>
+  <si>
+    <t>AUTODSR_826E6</t>
+  </si>
+  <si>
+    <t>03099786300</t>
+  </si>
+  <si>
+    <t>EMPE02BBD</t>
+  </si>
+  <si>
+    <t>91131-0085040-0</t>
+  </si>
+  <si>
+    <t>DSR_E601F</t>
+  </si>
+  <si>
+    <t>AUTODSR_0DCEC</t>
+  </si>
+  <si>
+    <t>03102385600</t>
+  </si>
+  <si>
+    <t>EMP3C993E</t>
+  </si>
+  <si>
+    <t>91131-0335430-0</t>
+  </si>
+  <si>
+    <t>DSR_D438A</t>
+  </si>
+  <si>
+    <t>AUTODSR_476CC</t>
+  </si>
+  <si>
+    <t>03104879900</t>
+  </si>
+  <si>
+    <t>EMPDB6E28</t>
+  </si>
+  <si>
+    <t>91131-0575690-0</t>
+  </si>
+  <si>
+    <t>DSR_8D729</t>
+  </si>
+  <si>
+    <t>AUTODSR_D0333</t>
+  </si>
+  <si>
+    <t>03107119200</t>
+  </si>
+  <si>
+    <t>EMP852AD1</t>
+  </si>
+  <si>
+    <t>91131-0804740-0</t>
+  </si>
+  <si>
+    <t>DSR_45D05</t>
+  </si>
+  <si>
+    <t>AUTODSR_75E14</t>
+  </si>
+  <si>
+    <t>03737691800</t>
+  </si>
+  <si>
+    <t>EMP502A55</t>
+  </si>
+  <si>
+    <t>34497-4168460-0</t>
+  </si>
+  <si>
+    <t>DSR_2C191</t>
+  </si>
+  <si>
+    <t>AUTODSR_5AA52</t>
+  </si>
+  <si>
+    <t>03754957800</t>
+  </si>
+  <si>
+    <t>EMP17919C</t>
+  </si>
+  <si>
+    <t>34497-5596500-0</t>
+  </si>
+  <si>
+    <t>DSR_27080</t>
+  </si>
+  <si>
+    <t>AUTODSR_566C9</t>
+  </si>
+  <si>
+    <t>03757809000</t>
+  </si>
+  <si>
+    <t>EMPB35500</t>
+  </si>
+  <si>
+    <t>34497-5895570-0</t>
+  </si>
+  <si>
+    <t>DSR_C9A55</t>
+  </si>
+  <si>
+    <t>AUTODSR_46AD0</t>
+  </si>
+  <si>
+    <t>03760609200</t>
+  </si>
+  <si>
+    <t>EMP7E5FAF</t>
+  </si>
+  <si>
+    <t>34497-6176420-0</t>
+  </si>
+  <si>
+    <t>DSR_CB23A</t>
+  </si>
+  <si>
+    <t>AUTODSR_9C6BA</t>
+  </si>
+  <si>
+    <t>03763443500</t>
+  </si>
+  <si>
+    <t>EMP4F1BB7</t>
+  </si>
+  <si>
+    <t>34497-6439750-0</t>
+  </si>
+  <si>
+    <t>DSR_1162C</t>
+  </si>
+  <si>
+    <t>AUTODSR_0E6AF</t>
+  </si>
+  <si>
+    <t>03035890900</t>
+  </si>
+  <si>
+    <t>EMPF75BC5</t>
+  </si>
+  <si>
+    <t>44600-3833310-0</t>
+  </si>
+  <si>
+    <t>DSR_0B1EA</t>
+  </si>
+  <si>
+    <t>AUTODSR_43487</t>
+  </si>
+  <si>
+    <t>03053258800</t>
+  </si>
+  <si>
+    <t>EMPA59766</t>
+  </si>
+  <si>
+    <t>44600-5477290-0</t>
+  </si>
+  <si>
+    <t>DSR_9150E</t>
+  </si>
+  <si>
+    <t>AUTODSR_C6EAB</t>
+  </si>
+  <si>
+    <t>03056902900</t>
+  </si>
+  <si>
+    <t>EMPE83329</t>
+  </si>
+  <si>
+    <t>44600-5811740-0</t>
+  </si>
+  <si>
+    <t>DSR_7AF24</t>
+  </si>
+  <si>
+    <t>AUTODSR_937D9</t>
+  </si>
+  <si>
+    <t>03060188800</t>
+  </si>
+  <si>
+    <t>EMP3AB9A8</t>
+  </si>
+  <si>
+    <t>44600-6153360-0</t>
+  </si>
+  <si>
+    <t>DSR_60698</t>
+  </si>
+  <si>
+    <t>AUTODSR_90541</t>
+  </si>
+  <si>
+    <t>03064630000</t>
+  </si>
+  <si>
+    <t>EMP99844D</t>
+  </si>
+  <si>
+    <t>44600-6729960-0</t>
+  </si>
+  <si>
+    <t>DSR_893AA</t>
+  </si>
+  <si>
+    <t>AUTODSR_92E52</t>
+  </si>
+  <si>
+    <t>03560014200</t>
+  </si>
+  <si>
+    <t>EMPE70BDF</t>
+  </si>
+  <si>
+    <t>54855-6272140-0</t>
+  </si>
+  <si>
+    <t>DSR_B9F2A</t>
+  </si>
+  <si>
+    <t>AUTODSR_32B79</t>
+  </si>
+  <si>
+    <t>03575343500</t>
+  </si>
+  <si>
+    <t>EMP36267F</t>
+  </si>
+  <si>
+    <t>54855-7649380-0</t>
+  </si>
+  <si>
+    <t>DSR_C6735</t>
+  </si>
+  <si>
+    <t>AUTODSR_542FB</t>
+  </si>
+  <si>
+    <t>03578369700</t>
+  </si>
+  <si>
+    <t>EMPE1133C</t>
+  </si>
+  <si>
+    <t>54855-7937790-0</t>
+  </si>
+  <si>
+    <t>DSR_105A0</t>
+  </si>
+  <si>
+    <t>AUTODSR_9BD86</t>
+  </si>
+  <si>
+    <t>03581103000</t>
+  </si>
+  <si>
+    <t>EMP0EBE04</t>
+  </si>
+  <si>
+    <t>54855-8226960-0</t>
+  </si>
+  <si>
+    <t>DSR_E85CD</t>
+  </si>
+  <si>
+    <t>AUTODSR_423BF</t>
+  </si>
+  <si>
+    <t>03583980300</t>
+  </si>
+  <si>
+    <t>EMPEDF289</t>
+  </si>
+  <si>
+    <t>54855-8518170-0</t>
+  </si>
+  <si>
+    <t>DSR_D3984</t>
+  </si>
+  <si>
+    <t>AUTODSR_A19FE</t>
+  </si>
+  <si>
+    <t>03892641000</t>
+  </si>
+  <si>
+    <t>EMP615D43</t>
+  </si>
+  <si>
+    <t>78898-9459850-0</t>
+  </si>
+  <si>
+    <t>DSR_AC468</t>
+  </si>
+  <si>
+    <t>AUTODSR_31C64</t>
+  </si>
+  <si>
+    <t>03896987100</t>
+  </si>
+  <si>
+    <t>EMP5E097A</t>
+  </si>
+  <si>
+    <t>78898-9808110-0</t>
+  </si>
+  <si>
+    <t>DSR_246CF</t>
+  </si>
+  <si>
+    <t>AUTODSR_8CDA5</t>
+  </si>
+  <si>
+    <t>03899924600</t>
+  </si>
+  <si>
+    <t>EMP9568F7</t>
+  </si>
+  <si>
+    <t>78899-0442510-0</t>
+  </si>
+  <si>
+    <t>DSR_28923</t>
+  </si>
+  <si>
+    <t>AUTODSR_C2236</t>
+  </si>
+  <si>
+    <t>03906638400</t>
+  </si>
+  <si>
+    <t>EMPD3A188</t>
+  </si>
+  <si>
+    <t>78899-0760900-0</t>
+  </si>
+  <si>
+    <t>DSR_BC144</t>
+  </si>
+  <si>
+    <t>AUTODSR_7C7C6</t>
+  </si>
+  <si>
+    <t>03909425200</t>
+  </si>
+  <si>
+    <t>EMP5BC484</t>
+  </si>
+  <si>
+    <t>78899-1063750-0</t>
+  </si>
+  <si>
+    <t>DSR_C028A</t>
+  </si>
+  <si>
+    <t>AUTODSR_BFAA6</t>
+  </si>
+  <si>
+    <t>03162251800</t>
+  </si>
+  <si>
+    <t>EMP5F1775</t>
+  </si>
+  <si>
+    <t>24801-6323900-0</t>
+  </si>
+  <si>
+    <t>DSR_68B69</t>
+  </si>
+  <si>
+    <t>AUTODSR_A7EDB</t>
+  </si>
+  <si>
+    <t>03164543300</t>
+  </si>
+  <si>
+    <t>EMPF2FD10</t>
+  </si>
+  <si>
+    <t>24801-6510320-0</t>
+  </si>
+  <si>
+    <t>DSR_6842B</t>
+  </si>
+  <si>
+    <t>AUTODSR_1FF20</t>
+  </si>
+  <si>
+    <t>03165876600</t>
+  </si>
+  <si>
+    <t>EMP384DFC</t>
+  </si>
+  <si>
+    <t>24801-6639890-0</t>
+  </si>
+  <si>
+    <t>DSR_F5146</t>
+  </si>
+  <si>
+    <t>AUTODSR_67271</t>
+  </si>
+  <si>
+    <t>03167281900</t>
+  </si>
+  <si>
+    <t>EMP5151AD</t>
+  </si>
+  <si>
+    <t>24801-6776840-0</t>
+  </si>
+  <si>
+    <t>DSR_22998</t>
+  </si>
+  <si>
+    <t>AUTODSR_A589B</t>
+  </si>
+  <si>
+    <t>03168545800</t>
+  </si>
+  <si>
+    <t>EMP2C0EE6</t>
+  </si>
+  <si>
+    <t>24801-6895730-0</t>
+  </si>
+  <si>
+    <t>DSR_42E2E</t>
+  </si>
+  <si>
+    <t>AUTODSR_9358B</t>
+  </si>
+  <si>
+    <t>03855257400</t>
+  </si>
+  <si>
+    <t>EMPB1B0ED</t>
+  </si>
+  <si>
+    <t>32038-5616970-0</t>
+  </si>
+  <si>
+    <t>DSR_F1AB2</t>
+  </si>
+  <si>
+    <t>AUTODSR_3F5D0</t>
+  </si>
+  <si>
+    <t>03857357000</t>
+  </si>
+  <si>
+    <t>EMP693702</t>
+  </si>
+  <si>
+    <t>32038-5800360-0</t>
+  </si>
+  <si>
+    <t>DSR_64729</t>
+  </si>
+  <si>
+    <t>AUTODSR_AE6E9</t>
+  </si>
+  <si>
+    <t>03859072400</t>
+  </si>
+  <si>
+    <t>EMP2CA0EB</t>
+  </si>
+  <si>
+    <t>32038-5971290-0</t>
+  </si>
+  <si>
+    <t>DSR_1A611</t>
+  </si>
+  <si>
+    <t>AUTODSR_799E4</t>
+  </si>
+  <si>
+    <t>03860583400</t>
+  </si>
+  <si>
+    <t>EMP354031</t>
+  </si>
+  <si>
+    <t>32038-6110960-0</t>
+  </si>
+  <si>
+    <t>DSR_70853</t>
+  </si>
+  <si>
+    <t>AUTODSR_7F50A</t>
+  </si>
+  <si>
+    <t>03861952800</t>
+  </si>
+  <si>
+    <t>EMP7335F6</t>
+  </si>
+  <si>
+    <t>32038-6250770-0</t>
+  </si>
+  <si>
+    <t>DSR_E3EEC</t>
+  </si>
+  <si>
+    <t>AUTODSR_8ADBD</t>
+  </si>
+  <si>
+    <t>03024395900</t>
+  </si>
+  <si>
+    <t>EMP92C284</t>
+  </si>
+  <si>
+    <t>43910-2563220-0</t>
+  </si>
+  <si>
+    <t>DSR_55E85</t>
+  </si>
+  <si>
+    <t>AUTODSR_59BF8</t>
+  </si>
+  <si>
+    <t>03027334700</t>
+  </si>
+  <si>
+    <t>EMPF9C000</t>
+  </si>
+  <si>
+    <t>43910-2822340-0</t>
+  </si>
+  <si>
+    <t>DSR_478C7</t>
+  </si>
+  <si>
+    <t>AUTODSR_E3F33</t>
+  </si>
+  <si>
+    <t>03030541500</t>
+  </si>
+  <si>
+    <t>EMP161549</t>
+  </si>
+  <si>
+    <t>43910-3187690-0</t>
+  </si>
+  <si>
+    <t>DSR_2B344</t>
+  </si>
+  <si>
+    <t>AUTODSR_6A087</t>
+  </si>
+  <si>
+    <t>03033088800</t>
+  </si>
+  <si>
+    <t>EMP9AA362</t>
+  </si>
+  <si>
+    <t>43910-3354580-0</t>
+  </si>
+  <si>
+    <t>DSR_62F9D</t>
+  </si>
+  <si>
+    <t>AUTODSR_3E516</t>
+  </si>
+  <si>
+    <t>03034486200</t>
+  </si>
+  <si>
+    <t>EMP160989</t>
+  </si>
+  <si>
+    <t>43910-3512800-0</t>
+  </si>
+  <si>
+    <t>DSR_DFA4E</t>
+  </si>
+  <si>
+    <t>AUTODSR_C6672</t>
+  </si>
+  <si>
+    <t>03087208000</t>
+  </si>
+  <si>
+    <t>EMPCD598F</t>
+  </si>
+  <si>
+    <t>50800-8814880-0</t>
+  </si>
+  <si>
+    <t>DSR_30316</t>
+  </si>
+  <si>
+    <t>AUTODSR_B7741</t>
+  </si>
+  <si>
+    <t>03089310500</t>
+  </si>
+  <si>
+    <t>EMP9042A8</t>
+  </si>
+  <si>
+    <t>50800-8983140-0</t>
+  </si>
+  <si>
+    <t>DSR_AD76E</t>
+  </si>
+  <si>
+    <t>AUTODSR_48FCD</t>
+  </si>
+  <si>
+    <t>03090692000</t>
+  </si>
+  <si>
+    <t>EMP8E8212</t>
+  </si>
+  <si>
+    <t>50800-9123260-0</t>
+  </si>
+  <si>
+    <t>DSR_677E0</t>
+  </si>
+  <si>
+    <t>AUTODSR_52DE6</t>
+  </si>
+  <si>
+    <t>03092021400</t>
+  </si>
+  <si>
+    <t>EMP3F6034</t>
+  </si>
+  <si>
+    <t>50800-9256200-0</t>
+  </si>
+  <si>
+    <t>DSR_92DE3</t>
+  </si>
+  <si>
+    <t>AUTODSR_CB838</t>
+  </si>
+  <si>
+    <t>03093231200</t>
+  </si>
+  <si>
+    <t>EMP893A47</t>
+  </si>
+  <si>
+    <t>50800-9355560-0</t>
+  </si>
+  <si>
+    <t>DSR_D573B</t>
+  </si>
+  <si>
+    <t>AUTODSR_45721</t>
+  </si>
+  <si>
+    <t>03452853800</t>
+  </si>
+  <si>
+    <t>EMPF9DCA9</t>
+  </si>
+  <si>
+    <t>52254-5359380-0</t>
+  </si>
+  <si>
+    <t>DSR_F9026</t>
+  </si>
+  <si>
+    <t>AUTODSR_14A96</t>
+  </si>
+  <si>
+    <t>03454578100</t>
+  </si>
+  <si>
+    <t>EMP0261CB</t>
+  </si>
+  <si>
+    <t>52254-5508090-0</t>
+  </si>
+  <si>
+    <t>DSR_929B6</t>
+  </si>
+  <si>
+    <t>AUTODSR_35244</t>
+  </si>
+  <si>
+    <t>03455756900</t>
+  </si>
+  <si>
+    <t>EMP9934D6</t>
+  </si>
+  <si>
+    <t>52254-5619560-0</t>
+  </si>
+  <si>
+    <t>DSR_4287E</t>
+  </si>
+  <si>
+    <t>AUTODSR_4371C</t>
+  </si>
+  <si>
+    <t>03456938700</t>
+  </si>
+  <si>
+    <t>EMP48C4CC</t>
+  </si>
+  <si>
+    <t>52254-5730480-0</t>
+  </si>
+  <si>
+    <t>DSR_D6B27</t>
+  </si>
+  <si>
+    <t>AUTODSR_EF55A</t>
+  </si>
+  <si>
+    <t>03458061200</t>
+  </si>
+  <si>
+    <t>EMPA98C9D</t>
+  </si>
+  <si>
+    <t>52254-5856030-0</t>
+  </si>
+  <si>
+    <t>DSR_3FC83</t>
+  </si>
+  <si>
+    <t>AUTODSR_71FFB</t>
+  </si>
+  <si>
+    <t>03310535500</t>
+  </si>
+  <si>
+    <t>EMP72626B</t>
+  </si>
+  <si>
+    <t>53783-1126520-0</t>
+  </si>
+  <si>
+    <t>DSR_3645E</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B1F8</t>
+  </si>
+  <si>
+    <t>03312047500</t>
+  </si>
+  <si>
+    <t>EMPF42C6A</t>
+  </si>
+  <si>
+    <t>53783-1255430-0</t>
+  </si>
+  <si>
+    <t>DSR_2457C</t>
+  </si>
+  <si>
+    <t>AUTODSR_475F0</t>
+  </si>
+  <si>
+    <t>03313516700</t>
+  </si>
+  <si>
+    <t>EMP700D7A</t>
+  </si>
+  <si>
+    <t>53783-1386860-0</t>
+  </si>
+  <si>
+    <t>DSR_0D17C</t>
+  </si>
+  <si>
+    <t>AUTODSR_F3F64</t>
+  </si>
+  <si>
+    <t>03314472300</t>
+  </si>
+  <si>
+    <t>EMP97B893</t>
+  </si>
+  <si>
+    <t>53783-1496370-0</t>
+  </si>
+  <si>
+    <t>DSR_D9922</t>
+  </si>
+  <si>
+    <t>AUTODSR_DC1F7</t>
+  </si>
+  <si>
+    <t>03315670800</t>
+  </si>
+  <si>
+    <t>EMP4CC4F1</t>
+  </si>
+  <si>
+    <t>53783-1614230-0</t>
+  </si>
+  <si>
+    <t>DSR_1EA74</t>
+  </si>
+  <si>
+    <t>AUTODSR_125E5</t>
+  </si>
+  <si>
+    <t>03594004000</t>
+  </si>
+  <si>
+    <t>EMP31F9AA</t>
+  </si>
+  <si>
+    <t>56395-9525940-0</t>
+  </si>
+  <si>
+    <t>DSR_CD693</t>
+  </si>
+  <si>
+    <t>AUTODSR_62374</t>
+  </si>
+  <si>
+    <t>03596722100</t>
+  </si>
+  <si>
+    <t>EMP0EF8A4</t>
+  </si>
+  <si>
+    <t>56395-9731470-0</t>
+  </si>
+  <si>
+    <t>DSR_9C03C</t>
+  </si>
+  <si>
+    <t>AUTODSR_6AFF6</t>
+  </si>
+  <si>
+    <t>03598178400</t>
+  </si>
+  <si>
+    <t>EMP242391</t>
+  </si>
+  <si>
+    <t>56395-9868780-0</t>
+  </si>
+  <si>
+    <t>DSR_BC334</t>
+  </si>
+  <si>
+    <t>AUTODSR_93766</t>
+  </si>
+  <si>
+    <t>03599481400</t>
+  </si>
+  <si>
+    <t>EMPF46D3B</t>
+  </si>
+  <si>
+    <t>56395-9999460-0</t>
+  </si>
+  <si>
+    <t>DSR_DCF41</t>
+  </si>
+  <si>
+    <t>AUTODSR_F4DE8</t>
+  </si>
+  <si>
+    <t>03600878200</t>
+  </si>
+  <si>
+    <t>EMPC1B611</t>
+  </si>
+  <si>
+    <t>56396-0125420-0</t>
+  </si>
+  <si>
+    <t>DSR_29BC8</t>
+  </si>
+  <si>
+    <t>AUTODSR_FD966</t>
+  </si>
+  <si>
+    <t>03439668200</t>
+  </si>
+  <si>
+    <t>EMP5CA9EA</t>
+  </si>
+  <si>
+    <t>95944-4047250-0</t>
+  </si>
+  <si>
+    <t>DSR_2327D</t>
+  </si>
+  <si>
+    <t>AUTODSR_090AD</t>
+  </si>
+  <si>
+    <t>03441468200</t>
+  </si>
+  <si>
+    <t>EMPD73BE3</t>
+  </si>
+  <si>
+    <t>95944-4192190-0</t>
+  </si>
+  <si>
+    <t>DSR_8D0B5</t>
+  </si>
+  <si>
+    <t>AUTODSR_F5F19</t>
+  </si>
+  <si>
+    <t>03442589100</t>
+  </si>
+  <si>
+    <t>EMPFA4AA9</t>
+  </si>
+  <si>
+    <t>95944-4301950-0</t>
+  </si>
+  <si>
+    <t>DSR_08104</t>
+  </si>
+  <si>
+    <t>AUTODSR_EC839</t>
+  </si>
+  <si>
+    <t>03444128100</t>
+  </si>
+  <si>
+    <t>EMP6A1FFC</t>
+  </si>
+  <si>
+    <t>95944-4458730-0</t>
+  </si>
+  <si>
+    <t>DSR_B0284</t>
+  </si>
+  <si>
+    <t>AUTODSR_B203F</t>
+  </si>
+  <si>
+    <t>03445315400</t>
+  </si>
+  <si>
+    <t>EMPA6FAA7</t>
+  </si>
+  <si>
+    <t>95944-4562890-0</t>
+  </si>
+  <si>
+    <t>DSR_68F4A</t>
+  </si>
+  <si>
+    <t>AUTODSR_7FFC4</t>
+  </si>
+  <si>
+    <t>03851261100</t>
+  </si>
+  <si>
+    <t>EMPBA2E09</t>
+  </si>
+  <si>
+    <t>97608-5252640-0</t>
+  </si>
+  <si>
+    <t>DSR_177FC</t>
+  </si>
+  <si>
+    <t>AUTODSR_02113</t>
+  </si>
+  <si>
+    <t>03853754600</t>
+  </si>
+  <si>
+    <t>EMPAE6948</t>
+  </si>
+  <si>
+    <t>97608-5431010-0</t>
+  </si>
+  <si>
+    <t>DSR_7A841</t>
+  </si>
+  <si>
+    <t>AUTODSR_BD91E</t>
+  </si>
+  <si>
+    <t>03855160800</t>
+  </si>
+  <si>
+    <t>EMP565445</t>
+  </si>
+  <si>
+    <t>97608-5550060-0</t>
+  </si>
+  <si>
+    <t>DSR_1253F</t>
+  </si>
+  <si>
+    <t>AUTODSR_3FEFB</t>
+  </si>
+  <si>
+    <t>03856163500</t>
+  </si>
+  <si>
+    <t>EMPCCE26E</t>
+  </si>
+  <si>
+    <t>97608-5665040-0</t>
+  </si>
+  <si>
+    <t>DSR_865C5</t>
+  </si>
+  <si>
+    <t>AUTODSR_B45DD</t>
+  </si>
+  <si>
+    <t>03857514800</t>
+  </si>
+  <si>
+    <t>EMPBCDD3C</t>
+  </si>
+  <si>
+    <t>97608-5787700-0</t>
+  </si>
+  <si>
+    <t>DSR_BA241</t>
+  </si>
+  <si>
+    <t>AUTODSR_96CF2</t>
+  </si>
+  <si>
+    <t>03230609900</t>
+  </si>
+  <si>
+    <t>EMP8151D6</t>
+  </si>
+  <si>
+    <t>00192-3151280-0</t>
+  </si>
+  <si>
+    <t>DSR_EA203</t>
+  </si>
+  <si>
+    <t>AUTODSR_11EC7</t>
+  </si>
+  <si>
+    <t>03232641000</t>
+  </si>
+  <si>
+    <t>EMP888AC7</t>
+  </si>
+  <si>
+    <t>00192-3306920-0</t>
+  </si>
+  <si>
+    <t>DSR_B06C2</t>
+  </si>
+  <si>
+    <t>AUTODSR_B695A</t>
+  </si>
+  <si>
+    <t>03234028400</t>
+  </si>
+  <si>
+    <t>EMPD10C38</t>
+  </si>
+  <si>
+    <t>00192-3465790-0</t>
+  </si>
+  <si>
+    <t>DSR_BA205</t>
+  </si>
+  <si>
+    <t>AUTODSR_0E678</t>
+  </si>
+  <si>
+    <t>03235419700</t>
+  </si>
+  <si>
+    <t>EMP43341E</t>
+  </si>
+  <si>
+    <t>00192-3597980-0</t>
+  </si>
+  <si>
+    <t>DSR_0A8E1</t>
+  </si>
+  <si>
+    <t>AUTODSR_92BE6</t>
+  </si>
+  <si>
+    <t>03236862100</t>
+  </si>
+  <si>
+    <t>EMPA4FB48</t>
+  </si>
+  <si>
+    <t>00192-3736690-0</t>
+  </si>
+  <si>
+    <t>DSR_2551F</t>
+  </si>
+  <si>
+    <t>AUTODSR_D72CC</t>
+  </si>
+  <si>
+    <t>03065638000</t>
+  </si>
+  <si>
+    <t>EMPFBA2C9</t>
+  </si>
+  <si>
+    <t>02560-6655890-0</t>
+  </si>
+  <si>
+    <t>DSR_034B5</t>
+  </si>
+  <si>
+    <t>AUTODSR_CC621</t>
+  </si>
+  <si>
+    <t>03067638600</t>
+  </si>
+  <si>
+    <t>EMP0C5643</t>
+  </si>
+  <si>
+    <t>02560-6805440-0</t>
+  </si>
+  <si>
+    <t>DSR_AE7CB</t>
+  </si>
+  <si>
+    <t>AUTODSR_1D78D</t>
+  </si>
+  <si>
+    <t>03068831800</t>
+  </si>
+  <si>
+    <t>EMP7A5E88</t>
+  </si>
+  <si>
+    <t>02560-6936940-0</t>
+  </si>
+  <si>
+    <t>DSR_66C77</t>
+  </si>
+  <si>
+    <t>AUTODSR_B0E73</t>
+  </si>
+  <si>
+    <t>03070023800</t>
+  </si>
+  <si>
+    <t>EMP70ADFF</t>
+  </si>
+  <si>
+    <t>02560-7049950-0</t>
+  </si>
+  <si>
+    <t>DSR_0687B</t>
+  </si>
+  <si>
+    <t>AUTODSR_AA92B</t>
+  </si>
+  <si>
+    <t>03071172200</t>
+  </si>
+  <si>
+    <t>EMP842664</t>
+  </si>
+  <si>
+    <t>02560-7161250-0</t>
+  </si>
+  <si>
+    <t>DSR_B67A9</t>
+  </si>
+  <si>
+    <t>AUTODSR_CF422</t>
+  </si>
+  <si>
+    <t>03390902000</t>
+  </si>
+  <si>
+    <t>EMP20F434</t>
+  </si>
+  <si>
+    <t>07633-9179680-0</t>
+  </si>
+  <si>
+    <t>DSR_1B894</t>
+  </si>
+  <si>
+    <t>AUTODSR_1F2B8</t>
+  </si>
+  <si>
+    <t>03392838500</t>
+  </si>
+  <si>
+    <t>EMP5A1AAB</t>
+  </si>
+  <si>
+    <t>07633-9321260-0</t>
+  </si>
+  <si>
+    <t>DSR_5A5E5</t>
+  </si>
+  <si>
+    <t>AUTODSR_0C686</t>
+  </si>
+  <si>
+    <t>03393915700</t>
+  </si>
+  <si>
+    <t>EMP47EEB2</t>
+  </si>
+  <si>
+    <t>07633-9435110-0</t>
+  </si>
+  <si>
+    <t>DSR_E9FF0</t>
+  </si>
+  <si>
+    <t>AUTODSR_37E13</t>
+  </si>
+  <si>
+    <t>03394974400</t>
+  </si>
+  <si>
+    <t>EMP02F341</t>
+  </si>
+  <si>
+    <t>07633-9532460-0</t>
+  </si>
+  <si>
+    <t>DSR_68D74</t>
+  </si>
+  <si>
+    <t>AUTODSR_12730</t>
+  </si>
+  <si>
+    <t>03395976900</t>
+  </si>
+  <si>
+    <t>EMP6CBE00</t>
+  </si>
+  <si>
+    <t>07633-9641280-0</t>
+  </si>
+  <si>
+    <t>DSR_F74A5</t>
+  </si>
+  <si>
+    <t>AUTODSR_1A585</t>
+  </si>
+  <si>
+    <t>03416199400</t>
+  </si>
+  <si>
+    <t>EMP1DC268</t>
+  </si>
+  <si>
+    <t>08514-1733060-0</t>
+  </si>
+  <si>
+    <t>DSR_AE40A</t>
+  </si>
+  <si>
+    <t>AUTODSR_01E01</t>
+  </si>
+  <si>
+    <t>03418603700</t>
+  </si>
+  <si>
+    <t>EMPF4E285</t>
+  </si>
+  <si>
+    <t>08514-1917340-0</t>
+  </si>
+  <si>
+    <t>DSR_FA4B5</t>
+  </si>
+  <si>
+    <t>AUTODSR_A29CF</t>
+  </si>
+  <si>
+    <t>03420602100</t>
+  </si>
+  <si>
+    <t>EMPA20085</t>
+  </si>
+  <si>
+    <t>08514-2112820-0</t>
+  </si>
+  <si>
+    <t>DSR_0D2FD</t>
+  </si>
+  <si>
+    <t>AUTODSR_64186</t>
+  </si>
+  <si>
+    <t>03422027400</t>
+  </si>
+  <si>
+    <t>EMP04CBCA</t>
+  </si>
+  <si>
+    <t>08514-2247960-0</t>
+  </si>
+  <si>
+    <t>DSR_1BC61</t>
+  </si>
+  <si>
+    <t>AUTODSR_10D23</t>
+  </si>
+  <si>
+    <t>03423054900</t>
+  </si>
+  <si>
+    <t>EMPAC0B1E</t>
+  </si>
+  <si>
+    <t>08514-2346810-0</t>
+  </si>
+  <si>
+    <t>DSR_134E3</t>
+  </si>
+  <si>
+    <t>AUTODSR_D5DC3</t>
+  </si>
+  <si>
+    <t>03669973400</t>
+  </si>
+  <si>
+    <t>EMP72E28D</t>
+  </si>
+  <si>
+    <t>10116-7056740-0</t>
+  </si>
+  <si>
+    <t>DSR_CC096</t>
+  </si>
+  <si>
+    <t>AUTODSR_99E4E</t>
+  </si>
+  <si>
+    <t>03671717100</t>
+  </si>
+  <si>
+    <t>EMPD2DAAF</t>
+  </si>
+  <si>
+    <t>10116-7224440-0</t>
+  </si>
+  <si>
+    <t>DSR_349B9</t>
+  </si>
+  <si>
+    <t>AUTODSR_23C60</t>
+  </si>
+  <si>
+    <t>03673022600</t>
+  </si>
+  <si>
+    <t>EMP511E49</t>
+  </si>
+  <si>
+    <t>10116-7352020-0</t>
+  </si>
+  <si>
+    <t>DSR_955BC</t>
+  </si>
+  <si>
+    <t>AUTODSR_8A9C4</t>
+  </si>
+  <si>
+    <t>03674439500</t>
+  </si>
+  <si>
+    <t>EMP0F1B9B</t>
+  </si>
+  <si>
+    <t>10116-7514890-0</t>
+  </si>
+  <si>
+    <t>DSR_70BED</t>
+  </si>
+  <si>
+    <t>AUTODSR_36BFA</t>
+  </si>
+  <si>
+    <t>03676263700</t>
+  </si>
+  <si>
+    <t>EMP71DD29</t>
+  </si>
+  <si>
+    <t>10116-7681500-0</t>
+  </si>
+  <si>
+    <t>DSR_8059A</t>
+  </si>
+  <si>
+    <t>AUTODSR_D7F20</t>
+  </si>
+  <si>
+    <t>03774229000</t>
+  </si>
+  <si>
+    <t>EMP14EEF3</t>
+  </si>
+  <si>
+    <t>12667-7511560-0</t>
+  </si>
+  <si>
+    <t>DSR_1E065</t>
+  </si>
+  <si>
+    <t>AUTODSR_2BB93</t>
+  </si>
+  <si>
+    <t>03776341900</t>
+  </si>
+  <si>
+    <t>EMP5E08EA</t>
+  </si>
+  <si>
+    <t>12667-7685160-0</t>
+  </si>
+  <si>
+    <t>DSR_56C77</t>
+  </si>
+  <si>
+    <t>AUTODSR_2C55D</t>
+  </si>
+  <si>
+    <t>03777570500</t>
+  </si>
+  <si>
+    <t>EMP649A97</t>
+  </si>
+  <si>
+    <t>12667-7799520-0</t>
+  </si>
+  <si>
+    <t>DSR_D1D99</t>
+  </si>
+  <si>
+    <t>AUTODSR_93BDE</t>
+  </si>
+  <si>
+    <t>03778653800</t>
+  </si>
+  <si>
+    <t>EMPBDECBF</t>
+  </si>
+  <si>
+    <t>12667-7906890-0</t>
+  </si>
+  <si>
+    <t>DSR_F8E24</t>
+  </si>
+  <si>
+    <t>AUTODSR_0C419</t>
+  </si>
+  <si>
+    <t>03779716900</t>
+  </si>
+  <si>
+    <t>EMP1C6CC9</t>
+  </si>
+  <si>
+    <t>12667-8013180-0</t>
+  </si>
+  <si>
+    <t>DSR_5907F</t>
+  </si>
+  <si>
+    <t>AUTODSR_EE934</t>
+  </si>
+  <si>
+    <t>03849507500</t>
+  </si>
+  <si>
+    <t>EMPC82ABF</t>
+  </si>
+  <si>
+    <t>14908-5047420-0</t>
+  </si>
+  <si>
+    <t>DSR_83DB0</t>
+  </si>
+  <si>
+    <t>AUTODSR_3A691</t>
+  </si>
+  <si>
+    <t>03851693900</t>
+  </si>
+  <si>
+    <t>EMP58F7CE</t>
+  </si>
+  <si>
+    <t>14908-5234220-0</t>
+  </si>
+  <si>
+    <t>DSR_91744</t>
+  </si>
+  <si>
+    <t>AUTODSR_01DAE</t>
+  </si>
+  <si>
+    <t>03853260900</t>
+  </si>
+  <si>
+    <t>EMP9A88FC</t>
+  </si>
+  <si>
+    <t>14908-5392870-0</t>
+  </si>
+  <si>
+    <t>DSR_57D0B</t>
+  </si>
+  <si>
+    <t>AUTODSR_1DE6B</t>
+  </si>
+  <si>
+    <t>03854728900</t>
+  </si>
+  <si>
+    <t>EMPC5A1D6</t>
+  </si>
+  <si>
+    <t>14908-5521870-0</t>
+  </si>
+  <si>
+    <t>DSR_41898</t>
+  </si>
+  <si>
+    <t>AUTODSR_2F99E</t>
+  </si>
+  <si>
+    <t>03856182400</t>
+  </si>
+  <si>
+    <t>EMP2FC314</t>
+  </si>
+  <si>
+    <t>14908-5667650-0</t>
+  </si>
+  <si>
+    <t>DSR_A6A3F</t>
+  </si>
+  <si>
+    <t>AUTODSR_B5A64</t>
+  </si>
+  <si>
+    <t>03513218000</t>
+  </si>
+  <si>
+    <t>EMPAA3AB2</t>
+  </si>
+  <si>
+    <t>20935-1420200-0</t>
+  </si>
+  <si>
+    <t>DSR_73B85</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B8CB</t>
+  </si>
+  <si>
+    <t>03515347400</t>
+  </si>
+  <si>
+    <t>EMP3C9C41</t>
+  </si>
+  <si>
+    <t>20935-1591610-0</t>
+  </si>
+  <si>
+    <t>DSR_39522</t>
+  </si>
+  <si>
+    <t>AUTODSR_4AD55</t>
+  </si>
+  <si>
+    <t>03517010800</t>
+  </si>
+  <si>
+    <t>EMP8AAF00</t>
+  </si>
+  <si>
+    <t>20935-1763190-0</t>
+  </si>
+  <si>
+    <t>DSR_F4E9E</t>
+  </si>
+  <si>
+    <t>AUTODSR_AFCD4</t>
+  </si>
+  <si>
+    <t>03518766500</t>
+  </si>
+  <si>
+    <t>EMPFA15F3</t>
+  </si>
+  <si>
+    <t>20935-1949300-0</t>
+  </si>
+  <si>
+    <t>DSR_4FD31</t>
+  </si>
+  <si>
+    <t>AUTODSR_76256</t>
+  </si>
+  <si>
+    <t>03520284300</t>
+  </si>
+  <si>
+    <t>EMP28B47C</t>
+  </si>
+  <si>
+    <t>20935-2070890-0</t>
+  </si>
+  <si>
+    <t>DSR_23A16</t>
+  </si>
+  <si>
+    <t>AUTODSR_9BAB5</t>
+  </si>
+  <si>
+    <t>03158201400</t>
+  </si>
+  <si>
+    <t>EMP5D1332</t>
+  </si>
+  <si>
+    <t>60071-5956690-0</t>
+  </si>
+  <si>
+    <t>DSR_8192C</t>
+  </si>
+  <si>
+    <t>AUTODSR_5F811</t>
+  </si>
+  <si>
+    <t>03165284000</t>
+  </si>
+  <si>
+    <t>EMP259678</t>
+  </si>
+  <si>
+    <t>60071-6586700-0</t>
+  </si>
+  <si>
+    <t>DSR_276A6</t>
+  </si>
+  <si>
+    <t>AUTODSR_5341A</t>
+  </si>
+  <si>
+    <t>03166885200</t>
+  </si>
+  <si>
+    <t>EMPB7C3A6</t>
+  </si>
+  <si>
+    <t>60071-6749680-0</t>
+  </si>
+  <si>
+    <t>DSR_1C434</t>
+  </si>
+  <si>
+    <t>AUTODSR_CEDF9</t>
+  </si>
+  <si>
+    <t>03168645000</t>
+  </si>
+  <si>
+    <t>EMP47FC9F</t>
+  </si>
+  <si>
+    <t>60071-6914690-0</t>
+  </si>
+  <si>
+    <t>DSR_ADACF</t>
+  </si>
+  <si>
+    <t>AUTODSR_B531B</t>
+  </si>
+  <si>
+    <t>03170047900</t>
+  </si>
+  <si>
+    <t>EMPCC62C1</t>
+  </si>
+  <si>
+    <t>60071-7054750-0</t>
+  </si>
+  <si>
+    <t>DSR_DC62C</t>
+  </si>
+  <si>
+    <t>AUTODSR_6D048</t>
+  </si>
+  <si>
+    <t>03877868400</t>
+  </si>
+  <si>
+    <t>EMPA8BF6D</t>
+  </si>
+  <si>
+    <t>65248-7817880-0</t>
+  </si>
+  <si>
+    <t>DSR_A20C3</t>
+  </si>
+  <si>
+    <t>AUTODSR_BC3AE</t>
+  </si>
+  <si>
+    <t>03878602200</t>
+  </si>
+  <si>
+    <t>EMP72CB2B</t>
+  </si>
+  <si>
+    <t>65248-7889670-0</t>
+  </si>
+  <si>
+    <t>DSR_A963A</t>
+  </si>
+  <si>
+    <t>AUTODSR_3B8D4</t>
+  </si>
+  <si>
+    <t>03879373000</t>
+  </si>
+  <si>
+    <t>EMPCE553C</t>
+  </si>
+  <si>
+    <t>65248-7958210-0</t>
+  </si>
+  <si>
+    <t>DSR_1D2DA</t>
+  </si>
+  <si>
+    <t>AUTODSR_297EC</t>
+  </si>
+  <si>
+    <t>03879888600</t>
+  </si>
+  <si>
+    <t>EMP7D88F3</t>
+  </si>
+  <si>
+    <t>65248-8010160-0</t>
+  </si>
+  <si>
+    <t>DSR_37858</t>
+  </si>
+  <si>
+    <t>AUTODSR_9781A</t>
+  </si>
+  <si>
+    <t>03880509000</t>
+  </si>
+  <si>
+    <t>EMP5AFF6F</t>
+  </si>
+  <si>
+    <t>65248-8077790-0</t>
+  </si>
+  <si>
+    <t>DSR_94D8C</t>
+  </si>
+  <si>
+    <t>AUTODSR_D2759</t>
+  </si>
+  <si>
+    <t>03584011100</t>
+  </si>
+  <si>
+    <t>EMP9E25F3</t>
+  </si>
+  <si>
+    <t>98165-8559540-0</t>
+  </si>
+  <si>
+    <t>DSR_090F1</t>
+  </si>
+  <si>
+    <t>AUTODSR_AA73A</t>
+  </si>
+  <si>
+    <t>03587610000</t>
+  </si>
+  <si>
+    <t>EMP021999</t>
+  </si>
+  <si>
+    <t>98165-8813360-0</t>
+  </si>
+  <si>
+    <t>DSR_FCA10</t>
+  </si>
+  <si>
+    <t>AUTODSR_15B6E</t>
+  </si>
+  <si>
+    <t>03588994600</t>
+  </si>
+  <si>
+    <t>EMP71DBDC</t>
+  </si>
+  <si>
+    <t>98165-8956620-0</t>
+  </si>
+  <si>
+    <t>DSR_F36C5</t>
+  </si>
+  <si>
+    <t>AUTODSR_B236A</t>
+  </si>
+  <si>
+    <t>03590630800</t>
+  </si>
+  <si>
+    <t>EMP674339</t>
+  </si>
+  <si>
+    <t>98165-9120900-0</t>
+  </si>
+  <si>
+    <t>DSR_CAD53</t>
+  </si>
+  <si>
+    <t>AUTODSR_5D4F3</t>
+  </si>
+  <si>
+    <t>03593133700</t>
+  </si>
+  <si>
+    <t>EMP03C5D1</t>
+  </si>
+  <si>
+    <t>98165-9469080-0</t>
+  </si>
+  <si>
+    <t>DSR_253C4</t>
+  </si>
+  <si>
+    <t>AUTODSR_E4A94</t>
+  </si>
+  <si>
+    <t>03289237300</t>
+  </si>
+  <si>
+    <t>EMP929A03</t>
+  </si>
+  <si>
+    <t>06762-9074320-0</t>
+  </si>
+  <si>
+    <t>DSR_22B58</t>
+  </si>
+  <si>
+    <t>AUTODSR_3383C</t>
+  </si>
+  <si>
+    <t>03292361200</t>
+  </si>
+  <si>
+    <t>EMPD17D68</t>
+  </si>
+  <si>
+    <t>06762-9300720-0</t>
+  </si>
+  <si>
+    <t>DSR_31156</t>
+  </si>
+  <si>
+    <t>AUTODSR_8178A</t>
+  </si>
+  <si>
+    <t>03296758800</t>
+  </si>
+  <si>
+    <t>EMPB74428</t>
+  </si>
+  <si>
+    <t>06762-9844070-0</t>
+  </si>
+  <si>
+    <t>DSR_0C499</t>
+  </si>
+  <si>
+    <t>AUTODSR_C53DF</t>
+  </si>
+  <si>
+    <t>03299996800</t>
+  </si>
+  <si>
+    <t>EMP72507C</t>
+  </si>
+  <si>
+    <t>06763-0097160-0</t>
+  </si>
+  <si>
+    <t>DSR_E1C8F</t>
+  </si>
+  <si>
+    <t>AUTODSR_F4B18</t>
+  </si>
+  <si>
+    <t>03302841800</t>
+  </si>
+  <si>
+    <t>EMP20D990</t>
+  </si>
+  <si>
+    <t>06763-0364840-0</t>
+  </si>
+  <si>
+    <t>DSR_6E76A</t>
+  </si>
+  <si>
+    <t>AUTODSR_63AF7</t>
+  </si>
+  <si>
+    <t>03585461000</t>
+  </si>
+  <si>
+    <t>EMP2E9AB0</t>
+  </si>
+  <si>
+    <t>17535-8642640-0</t>
+  </si>
+  <si>
+    <t>DSR_78C22</t>
+  </si>
+  <si>
+    <t>AUTODSR_53909</t>
+  </si>
+  <si>
+    <t>03587408600</t>
+  </si>
+  <si>
+    <t>EMP766375</t>
+  </si>
+  <si>
+    <t>17535-8806760-0</t>
+  </si>
+  <si>
+    <t>DSR_268A1</t>
+  </si>
+  <si>
+    <t>AUTODSR_9EFDD</t>
+  </si>
+  <si>
+    <t>03589123400</t>
+  </si>
+  <si>
+    <t>EMPBE2FB1</t>
+  </si>
+  <si>
+    <t>17535-8979840-0</t>
+  </si>
+  <si>
+    <t>DSR_E0F88</t>
+  </si>
+  <si>
+    <t>AUTODSR_44ED9</t>
+  </si>
+  <si>
+    <t>03590688700</t>
+  </si>
+  <si>
+    <t>EMPF10D6A</t>
+  </si>
+  <si>
+    <t>17535-9122490-0</t>
+  </si>
+  <si>
+    <t>DSR_18047</t>
+  </si>
+  <si>
+    <t>AUTODSR_A5CEA</t>
+  </si>
+  <si>
+    <t>03592146300</t>
+  </si>
+  <si>
+    <t>EMP3896F6</t>
+  </si>
+  <si>
+    <t>17535-9322080-0</t>
+  </si>
+  <si>
+    <t>DSR_FE766</t>
+  </si>
+  <si>
+    <t>AUTODSR_1144F</t>
+  </si>
+  <si>
+    <t>03497674000</t>
+  </si>
+  <si>
+    <t>EMP4F33B6</t>
+  </si>
+  <si>
+    <t>22984-9920870-0</t>
+  </si>
+  <si>
+    <t>DSR_B1A99</t>
+  </si>
+  <si>
+    <t>AUTODSR_1C3C6</t>
+  </si>
+  <si>
+    <t>03500971700</t>
+  </si>
+  <si>
+    <t>EMP695B22</t>
+  </si>
+  <si>
+    <t>22985-0193620-0</t>
+  </si>
+  <si>
+    <t>DSR_FF963</t>
+  </si>
+  <si>
+    <t>AUTODSR_5AA71</t>
+  </si>
+  <si>
+    <t>03503321900</t>
+  </si>
+  <si>
+    <t>EMP0FE382</t>
+  </si>
+  <si>
+    <t>22985-0400350-0</t>
+  </si>
+  <si>
+    <t>DSR_715E0</t>
+  </si>
+  <si>
+    <t>AUTODSR_208DA</t>
+  </si>
+  <si>
+    <t>03505021600</t>
+  </si>
+  <si>
+    <t>EMP54F43D</t>
+  </si>
+  <si>
+    <t>22985-0557060-0</t>
+  </si>
+  <si>
+    <t>DSR_A094D</t>
+  </si>
+  <si>
+    <t>AUTODSR_0FB3D</t>
+  </si>
+  <si>
+    <t>03506448000</t>
+  </si>
+  <si>
+    <t>EMP799016</t>
+  </si>
+  <si>
+    <t>22985-0707950-0</t>
   </si>
 </sst>
 </file>
@@ -7347,19 +14646,19 @@
         <v>30</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>51</v>
+        <v>4700</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>2272</v>
+        <v>4701</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>2273</v>
+        <v>4702</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>2274</v>
+        <v>4703</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -7419,7 +14718,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>2275</v>
+        <v>4704</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -7442,19 +14741,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>53</v>
+        <v>4705</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>2276</v>
+        <v>4706</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>2277</v>
+        <v>4707</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>2278</v>
+        <v>4708</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -7514,7 +14813,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>2279</v>
+        <v>4709</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -7537,19 +14836,19 @@
         <v>30</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>56</v>
+        <v>4710</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>2280</v>
+        <v>4711</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>2281</v>
+        <v>4712</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>2282</v>
+        <v>4713</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -7609,7 +14908,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>2283</v>
+        <v>4714</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -7632,19 +14931,19 @@
         <v>30</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>60</v>
+        <v>4715</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>2284</v>
+        <v>4716</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>2285</v>
+        <v>4717</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>2286</v>
+        <v>4718</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -7704,7 +15003,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>2287</v>
+        <v>4719</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -7727,19 +15026,19 @@
         <v>30</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>62</v>
+        <v>4720</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>2288</v>
+        <v>4721</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>2289</v>
+        <v>4722</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>2290</v>
+        <v>4723</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -7799,7 +15098,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>2291</v>
+        <v>4724</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>

--- a/ResourcesPK/dsrProfileData.xlsx
+++ b/ResourcesPK/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4820" uniqueCount="4725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4870" uniqueCount="4775">
   <si>
     <t>DT Code*</t>
   </si>
@@ -14194,6 +14194,156 @@
   </si>
   <si>
     <t>22985-0707950-0</t>
+  </si>
+  <si>
+    <t>DSR_94B6A</t>
+  </si>
+  <si>
+    <t>AUTODSR_527F0</t>
+  </si>
+  <si>
+    <t>03158045100</t>
+  </si>
+  <si>
+    <t>EMP738EF6</t>
+  </si>
+  <si>
+    <t>90191-6047990-0</t>
+  </si>
+  <si>
+    <t>DSR_32896</t>
+  </si>
+  <si>
+    <t>AUTODSR_E173D</t>
+  </si>
+  <si>
+    <t>03163775200</t>
+  </si>
+  <si>
+    <t>EMP4A5CB9</t>
+  </si>
+  <si>
+    <t>90191-6876980-0</t>
+  </si>
+  <si>
+    <t>DSR_56020</t>
+  </si>
+  <si>
+    <t>AUTODSR_DB095</t>
+  </si>
+  <si>
+    <t>03170351200</t>
+  </si>
+  <si>
+    <t>EMPBD038A</t>
+  </si>
+  <si>
+    <t>90191-7113310-0</t>
+  </si>
+  <si>
+    <t>DSR_0517F</t>
+  </si>
+  <si>
+    <t>AUTODSR_E9FF4</t>
+  </si>
+  <si>
+    <t>03172419600</t>
+  </si>
+  <si>
+    <t>EMP512874</t>
+  </si>
+  <si>
+    <t>90191-7396750-0</t>
+  </si>
+  <si>
+    <t>DSR_810F1</t>
+  </si>
+  <si>
+    <t>AUTODSR_2F396</t>
+  </si>
+  <si>
+    <t>03175413700</t>
+  </si>
+  <si>
+    <t>EMP682BC2</t>
+  </si>
+  <si>
+    <t>90191-7634560-0</t>
+  </si>
+  <si>
+    <t>DSR_6FAC2</t>
+  </si>
+  <si>
+    <t>AUTODSR_AA7E2</t>
+  </si>
+  <si>
+    <t>03409642300</t>
+  </si>
+  <si>
+    <t>EMPC11F6B</t>
+  </si>
+  <si>
+    <t>15514-1096070-0</t>
+  </si>
+  <si>
+    <t>DSR_C4D41</t>
+  </si>
+  <si>
+    <t>AUTODSR_42F40</t>
+  </si>
+  <si>
+    <t>03412635700</t>
+  </si>
+  <si>
+    <t>EMP2FC142</t>
+  </si>
+  <si>
+    <t>15514-1326780-0</t>
+  </si>
+  <si>
+    <t>DSR_951D2</t>
+  </si>
+  <si>
+    <t>AUTODSR_43E95</t>
+  </si>
+  <si>
+    <t>03414482000</t>
+  </si>
+  <si>
+    <t>EMPF1AD87</t>
+  </si>
+  <si>
+    <t>15514-1599410-0</t>
+  </si>
+  <si>
+    <t>DSR_74A69</t>
+  </si>
+  <si>
+    <t>AUTODSR_31BBB</t>
+  </si>
+  <si>
+    <t>03417347700</t>
+  </si>
+  <si>
+    <t>EMP238127</t>
+  </si>
+  <si>
+    <t>15514-1826260-0</t>
+  </si>
+  <si>
+    <t>DSR_20AFD</t>
+  </si>
+  <si>
+    <t>AUTODSR_4BD3D</t>
+  </si>
+  <si>
+    <t>03419913200</t>
+  </si>
+  <si>
+    <t>EMP968A8C</t>
+  </si>
+  <si>
+    <t>15514-2072930-0</t>
   </si>
 </sst>
 </file>
@@ -14646,19 +14796,19 @@
         <v>30</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>4700</v>
+        <v>4750</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>4701</v>
+        <v>4751</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>4702</v>
+        <v>4752</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>4703</v>
+        <v>4753</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>39</v>
@@ -14718,7 +14868,7 @@
         <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>4704</v>
+        <v>4754</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>46</v>
@@ -14741,19 +14891,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>4705</v>
+        <v>4755</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>4706</v>
+        <v>4756</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>4707</v>
+        <v>4757</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>4708</v>
+        <v>4758</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>39</v>
@@ -14813,7 +14963,7 @@
         <v>31</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>4709</v>
+        <v>4759</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>46</v>
@@ -14836,19 +14986,19 @@
         <v>30</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>4710</v>
+        <v>4760</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>4711</v>
+        <v>4761</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>4712</v>
+        <v>4762</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>4713</v>
+        <v>4763</v>
       </c>
       <c r="G4" t="s" s="0">
         <v>33</v>
@@ -14908,7 +15058,7 @@
         <v>31</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>4714</v>
+        <v>4764</v>
       </c>
       <c r="AA4" t="s" s="0">
         <v>46</v>
@@ -14931,19 +15081,19 @@
         <v>30</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>4715</v>
+        <v>4765</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>4716</v>
+        <v>4766</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>4717</v>
+        <v>4767</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>32</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>4718</v>
+        <v>4768</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>39</v>
@@ -15003,7 +15153,7 @@
         <v>31</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>4719</v>
+        <v>4769</v>
       </c>
       <c r="AA5" t="s" s="0">
         <v>47</v>
@@ -15026,19 +15176,19 @@
         <v>30</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>4720</v>
+        <v>4770</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>4721</v>
+        <v>4771</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>4722</v>
+        <v>4772</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>37</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>4723</v>
+        <v>4773</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>39</v>
@@ -15098,7 +15248,7 @@
         <v>31</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>4724</v>
+        <v>4774</v>
       </c>
       <c r="AA6" t="s" s="0">
         <v>47</v>
